--- a/assets/data/fred/catalog/catalogo_dataset_web_ove_fred.xlsx
+++ b/assets/data/fred/catalog/catalogo_dataset_web_ove_fred.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="catalogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="catalogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -88,11 +88,79 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -107,13 +175,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -122,7 +190,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -137,13 +205,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1042,20 +1110,26 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
       <c r="J13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="4" t="inlineStr"/>
-      <c r="L13" s="4" t="inlineStr"/>
-      <c r="M13" s="4" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>1776.7</v>
+      </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/AVHWPEVEA065NRUG</t>
@@ -1261,20 +1335,26 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
       <c r="J16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="4" t="inlineStr"/>
-      <c r="L16" s="4" t="inlineStr"/>
-      <c r="M16" s="4" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>15.92</v>
+      </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/BARTERICMP25UPZSVEN</t>
@@ -1334,20 +1414,26 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr"/>
       <c r="J17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="4" t="inlineStr"/>
-      <c r="L17" s="4" t="inlineStr"/>
-      <c r="M17" s="4" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>1990-01-01</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>95.9703157644156</v>
+      </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CASHBLVEA188A</t>
@@ -1553,20 +1639,26 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr"/>
       <c r="J20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="4" t="inlineStr"/>
-      <c r="L20" s="4" t="inlineStr"/>
-      <c r="M20" s="4" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>2523.1025390625</v>
+      </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CGDPESVEA666NRUG</t>
@@ -1626,20 +1718,26 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr"/>
       <c r="J21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="4" t="inlineStr"/>
-      <c r="L21" s="4" t="inlineStr"/>
-      <c r="M21" s="4" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>4408.41650390625</v>
+      </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CGDPOSVEA666NRUG</t>
@@ -1845,20 +1943,26 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr"/>
       <c r="J24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="4" t="inlineStr"/>
-      <c r="L24" s="4" t="inlineStr"/>
-      <c r="M24" s="4" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>120241.203125</v>
+      </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CKSPPPVEA666NRUG</t>
@@ -2210,20 +2314,26 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr"/>
       <c r="J29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="4" t="inlineStr"/>
-      <c r="L29" s="4" t="inlineStr"/>
-      <c r="M29" s="4" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="n">
+        <v>0.0565520189702511</v>
+      </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CSHICPVEA156NRUG</t>
@@ -2575,20 +2685,26 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr"/>
       <c r="J34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="4" t="inlineStr"/>
-      <c r="L34" s="4" t="inlineStr"/>
-      <c r="M34" s="4" t="n"/>
+        <v>70</v>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>1954-01-01</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="n">
+        <v>0.0518108420073986</v>
+      </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CTFPPPVEA669NRUG</t>
@@ -2940,20 +3056,26 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr"/>
       <c r="J39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="4" t="inlineStr"/>
-      <c r="L39" s="4" t="inlineStr"/>
-      <c r="M39" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="n">
+        <v>16.533233</v>
+      </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDAI02VEA643NWDB</t>
@@ -3816,20 +3938,26 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr"/>
       <c r="J51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="4" t="inlineStr"/>
-      <c r="L51" s="4" t="inlineStr"/>
-      <c r="M51" s="4" t="n"/>
+        <v>54</v>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>2013-01-01</t>
+        </is>
+      </c>
+      <c r="M51" s="4" t="n">
+        <v>20.13813</v>
+      </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDI06VEA156NWDB</t>
@@ -4254,20 +4382,26 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I57" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr"/>
       <c r="J57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" s="4" t="inlineStr"/>
-      <c r="L57" s="4" t="inlineStr"/>
-      <c r="M57" s="4" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>1993-01-01</t>
+        </is>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>2002-01-01</t>
+        </is>
+      </c>
+      <c r="M57" s="4" t="n">
+        <v>4.28404</v>
+      </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDM01VEA156NWDB</t>
@@ -4619,20 +4753,26 @@
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I62" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr"/>
       <c r="J62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" s="4" t="inlineStr"/>
-      <c r="L62" s="4" t="inlineStr"/>
-      <c r="M62" s="4" t="n"/>
+        <v>41</v>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>1980-01-01</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="M62" s="4" t="n">
+        <v>22.39961</v>
+      </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDM06VEA156NWDB</t>
@@ -4692,20 +4832,26 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I63" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr"/>
       <c r="J63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" s="4" t="inlineStr"/>
-      <c r="L63" s="4" t="inlineStr"/>
-      <c r="M63" s="4" t="n"/>
+        <v>41</v>
+      </c>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>1980-01-01</t>
+        </is>
+      </c>
+      <c r="L63" s="4" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="M63" s="4" t="n">
+        <v>32.15886</v>
+      </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDM07VEA156NWDB</t>
@@ -4911,20 +5057,26 @@
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I66" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr"/>
       <c r="J66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" s="4" t="inlineStr"/>
-      <c r="L66" s="4" t="inlineStr"/>
-      <c r="M66" s="4" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>2016-01-01</t>
+        </is>
+      </c>
+      <c r="M66" s="4" t="n">
+        <v>0.8002833</v>
+      </c>
       <c r="N66" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDM10VEA156NWDB</t>
@@ -5057,20 +5209,26 @@
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I68" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr"/>
       <c r="J68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" s="4" t="inlineStr"/>
-      <c r="L68" s="4" t="inlineStr"/>
-      <c r="M68" s="4" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>1990-01-01</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>2017-01-01</t>
+        </is>
+      </c>
+      <c r="M68" s="4" t="n">
+        <v>6.326667</v>
+      </c>
       <c r="N68" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDEI02VEA156NWDB</t>
@@ -5276,20 +5434,26 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I71" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr"/>
       <c r="J71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="4" t="inlineStr"/>
-      <c r="L71" s="4" t="inlineStr"/>
-      <c r="M71" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>2000-01-01</t>
+        </is>
+      </c>
+      <c r="L71" s="4" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="M71" s="4" t="n">
+        <v>1.153893</v>
+      </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDEI05VEA156NWDB</t>
@@ -5495,20 +5659,26 @@
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I74" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr"/>
       <c r="J74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" s="4" t="inlineStr"/>
-      <c r="L74" s="4" t="inlineStr"/>
-      <c r="M74" s="4" t="n"/>
+        <v>36</v>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>1980-01-01</t>
+        </is>
+      </c>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M74" s="4" t="n">
+        <v>7.325303999999998</v>
+      </c>
       <c r="N74" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDEI08VEA156NWDB</t>
@@ -5629,20 +5799,26 @@
       <c r="G76" s="4" t="inlineStr"/>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I76" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr"/>
       <c r="J76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" s="4" t="inlineStr"/>
-      <c r="L76" s="4" t="inlineStr"/>
-      <c r="M76" s="4" t="n"/>
+        <v>57</v>
+      </c>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L76" s="4" t="inlineStr">
+        <is>
+          <t>2016-01-01</t>
+        </is>
+      </c>
+      <c r="M76" s="4" t="n">
+        <v>4665.79</v>
+      </c>
       <c r="N76" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOE01VEA086NWDB</t>
@@ -5702,20 +5878,26 @@
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I77" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr"/>
       <c r="J77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" s="4" t="inlineStr"/>
-      <c r="L77" s="4" t="inlineStr"/>
-      <c r="M77" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>2000-01-01</t>
+        </is>
+      </c>
+      <c r="L77" s="4" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="M77" s="4" t="n">
+        <v>84.4594</v>
+      </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOI01VEA156NWDB</t>
@@ -6140,20 +6322,26 @@
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I83" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr"/>
       <c r="J83" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" s="4" t="inlineStr"/>
-      <c r="L83" s="4" t="inlineStr"/>
-      <c r="M83" s="4" t="n"/>
+        <v>54</v>
+      </c>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L83" s="4" t="inlineStr">
+        <is>
+          <t>2013-01-01</t>
+        </is>
+      </c>
+      <c r="M83" s="4" t="n">
+        <v>184310.5</v>
+      </c>
       <c r="N83" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOI07VEA648NWDB</t>
@@ -6432,20 +6620,26 @@
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I87" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="inlineStr"/>
       <c r="J87" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="4" t="inlineStr"/>
-      <c r="L87" s="4" t="inlineStr"/>
-      <c r="M87" s="4" t="n"/>
+        <v>30</v>
+      </c>
+      <c r="K87" s="4" t="inlineStr">
+        <is>
+          <t>1985-01-01</t>
+        </is>
+      </c>
+      <c r="L87" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M87" s="4" t="n">
+        <v>0.026536</v>
+      </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOI11VEA156NWDB</t>
@@ -6797,20 +6991,26 @@
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I92" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr"/>
       <c r="J92" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" s="4" t="inlineStr"/>
-      <c r="L92" s="4" t="inlineStr"/>
-      <c r="M92" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>2000-01-01</t>
+        </is>
+      </c>
+      <c r="L92" s="4" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="M92" s="4" t="n">
+        <v>12.70259</v>
+      </c>
       <c r="N92" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDSI01VEA645NWDB</t>
@@ -7308,20 +7508,26 @@
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I99" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I99" s="4" t="inlineStr"/>
       <c r="J99" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" s="4" t="inlineStr"/>
-      <c r="L99" s="4" t="inlineStr"/>
-      <c r="M99" s="4" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="K99" s="4" t="inlineStr">
+        <is>
+          <t>2018-01-01</t>
+        </is>
+      </c>
+      <c r="L99" s="4" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="M99" s="4" t="n">
+        <v>60.53188000000001</v>
+      </c>
       <c r="N99" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDSM01VEA066NWDB</t>
@@ -7523,20 +7729,26 @@
       <c r="G102" s="4" t="inlineStr"/>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I102" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr"/>
       <c r="J102" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" s="4" t="inlineStr"/>
-      <c r="L102" s="4" t="inlineStr"/>
-      <c r="M102" s="4" t="n"/>
+        <v>6643</v>
+      </c>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t>2000-01-03</t>
+        </is>
+      </c>
+      <c r="L102" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="M102" s="4" t="n">
+        <v>707.9193</v>
+      </c>
       <c r="N102" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DEXVZUS</t>
@@ -7596,20 +7808,26 @@
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I103" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I103" s="4" t="inlineStr"/>
       <c r="J103" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" s="4" t="inlineStr"/>
-      <c r="L103" s="4" t="inlineStr"/>
-      <c r="M103" s="4" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K103" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L103" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M103" s="4" t="n">
+        <v>15.3156814575195</v>
+      </c>
       <c r="N103" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/EMPENGVEA148NRUG</t>
@@ -7669,20 +7887,26 @@
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I104" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr"/>
       <c r="J104" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" s="4" t="inlineStr"/>
-      <c r="L104" s="4" t="inlineStr"/>
-      <c r="M104" s="4" t="n"/>
+        <v>497</v>
+      </c>
+      <c r="K104" s="4" t="inlineStr">
+        <is>
+          <t>1985-01-01</t>
+        </is>
+      </c>
+      <c r="L104" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M104" s="4" t="n">
+        <v>497.812779</v>
+      </c>
       <c r="N104" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/EXP3070</t>
@@ -9202,20 +9426,26 @@
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I125" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I125" s="4" t="inlineStr"/>
       <c r="J125" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K125" s="4" t="inlineStr"/>
-      <c r="L125" s="4" t="inlineStr"/>
-      <c r="M125" s="4" t="n"/>
+        <v>280</v>
+      </c>
+      <c r="K125" s="4" t="inlineStr">
+        <is>
+          <t>2003-02-01</t>
+        </is>
+      </c>
+      <c r="L125" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M125" s="4" t="n">
+        <v>672</v>
+      </c>
       <c r="N125" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORTREASPOS32719</t>
@@ -9275,20 +9505,26 @@
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I126" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I126" s="4" t="inlineStr"/>
       <c r="J126" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K126" s="4" t="inlineStr"/>
-      <c r="L126" s="4" t="inlineStr"/>
-      <c r="M126" s="4" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="K126" s="4" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="L126" s="4" t="inlineStr">
+        <is>
+          <t>2016-01-01</t>
+        </is>
+      </c>
+      <c r="M126" s="4" t="n">
+        <v>254.948534781816</v>
+      </c>
       <c r="N126" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FPCPITOTLZGVEN</t>
@@ -9348,20 +9584,26 @@
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I127" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I127" s="4" t="inlineStr"/>
       <c r="J127" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K127" s="4" t="inlineStr"/>
-      <c r="L127" s="4" t="inlineStr"/>
-      <c r="M127" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K127" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L127" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M127" s="4" t="n">
+        <v>2.585625</v>
+      </c>
       <c r="N127" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FXRATEVEA618NUPN</t>
@@ -9567,20 +9809,26 @@
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I130" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I130" s="4" t="inlineStr"/>
       <c r="J130" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K130" s="4" t="inlineStr"/>
-      <c r="L130" s="4" t="inlineStr"/>
-      <c r="M130" s="4" t="n"/>
+        <v>51</v>
+      </c>
+      <c r="K130" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L130" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M130" s="4" t="n">
+        <v>98.88050698000001</v>
+      </c>
       <c r="N130" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/GNPGDPVEA156NUPN</t>
@@ -9640,20 +9888,26 @@
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I131" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I131" s="4" t="inlineStr"/>
       <c r="J131" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K131" s="4" t="inlineStr"/>
-      <c r="L131" s="4" t="inlineStr"/>
-      <c r="M131" s="4" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K131" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L131" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M131" s="4" t="n">
+        <v>3.09922003746033</v>
+      </c>
       <c r="N131" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/HCIYISVEA066NRUG</t>
@@ -10516,20 +10770,26 @@
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I143" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I143" s="4" t="inlineStr"/>
       <c r="J143" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K143" s="4" t="inlineStr"/>
-      <c r="L143" s="4" t="inlineStr"/>
-      <c r="M143" s="4" t="n"/>
+        <v>214</v>
+      </c>
+      <c r="K143" s="4" t="inlineStr">
+        <is>
+          <t>1972-10-01</t>
+        </is>
+      </c>
+      <c r="L143" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M143" s="4" t="n">
+        <v>3000</v>
+      </c>
       <c r="N143" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDS1MNIAOAIVE</t>
@@ -10954,20 +11214,26 @@
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I149" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I149" s="4" t="inlineStr"/>
       <c r="J149" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K149" s="4" t="inlineStr"/>
-      <c r="L149" s="4" t="inlineStr"/>
-      <c r="M149" s="4" t="n"/>
+        <v>214</v>
+      </c>
+      <c r="K149" s="4" t="inlineStr">
+        <is>
+          <t>1972-10-01</t>
+        </is>
+      </c>
+      <c r="L149" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M149" s="4" t="n">
+        <v>3000</v>
+      </c>
       <c r="N149" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDS1YMAORIGGVE</t>
@@ -11173,20 +11439,26 @@
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I152" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I152" s="4" t="inlineStr"/>
       <c r="J152" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K152" s="4" t="inlineStr"/>
-      <c r="L152" s="4" t="inlineStr"/>
-      <c r="M152" s="4" t="n"/>
+        <v>146</v>
+      </c>
+      <c r="K152" s="4" t="inlineStr">
+        <is>
+          <t>1972-10-01</t>
+        </is>
+      </c>
+      <c r="L152" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M152" s="4" t="n">
+        <v>2397</v>
+      </c>
       <c r="N152" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSAMRINIVE</t>
@@ -11392,20 +11664,26 @@
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I155" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I155" s="4" t="inlineStr"/>
       <c r="J155" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K155" s="4" t="inlineStr"/>
-      <c r="L155" s="4" t="inlineStr"/>
-      <c r="M155" s="4" t="n"/>
+        <v>214</v>
+      </c>
+      <c r="K155" s="4" t="inlineStr">
+        <is>
+          <t>1972-10-01</t>
+        </is>
+      </c>
+      <c r="L155" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M155" s="4" t="n">
+        <v>23802</v>
+      </c>
       <c r="N155" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSGAMNIAOVE</t>
@@ -11611,20 +11889,26 @@
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I158" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I158" s="4" t="inlineStr"/>
       <c r="J158" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K158" s="4" t="inlineStr"/>
-      <c r="L158" s="4" t="inlineStr"/>
-      <c r="M158" s="4" t="n"/>
+        <v>109</v>
+      </c>
+      <c r="K158" s="4" t="inlineStr">
+        <is>
+          <t>1972-10-01</t>
+        </is>
+      </c>
+      <c r="L158" s="4" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="M158" s="4" t="n">
+        <v>-1600</v>
+      </c>
       <c r="N158" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSGAMRINIVE</t>
@@ -12195,20 +12479,26 @@
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I166" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I166" s="4" t="inlineStr"/>
       <c r="J166" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K166" s="4" t="inlineStr"/>
-      <c r="L166" s="4" t="inlineStr"/>
-      <c r="M166" s="4" t="n"/>
+        <v>37</v>
+      </c>
+      <c r="K166" s="4" t="inlineStr">
+        <is>
+          <t>1993-07-01</t>
+        </is>
+      </c>
+      <c r="L166" s="4" t="inlineStr">
+        <is>
+          <t>2014-10-01</t>
+        </is>
+      </c>
+      <c r="M166" s="4" t="n">
+        <v>-1.3</v>
+      </c>
       <c r="N166" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSGNFAMNINIVE</t>
@@ -13290,20 +13580,26 @@
       </c>
       <c r="H181" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I181" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I181" s="4" t="inlineStr"/>
       <c r="J181" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K181" s="4" t="inlineStr"/>
-      <c r="L181" s="4" t="inlineStr"/>
-      <c r="M181" s="4" t="n"/>
+        <v>497</v>
+      </c>
+      <c r="K181" s="4" t="inlineStr">
+        <is>
+          <t>1985-01-01</t>
+        </is>
+      </c>
+      <c r="L181" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M181" s="4" t="n">
+        <v>1525.18625</v>
+      </c>
       <c r="N181" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IMP3070</t>
@@ -13509,20 +13805,26 @@
       </c>
       <c r="H184" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I184" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I184" s="4" t="inlineStr"/>
       <c r="J184" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K184" s="4" t="inlineStr"/>
-      <c r="L184" s="4" t="inlineStr"/>
-      <c r="M184" s="4" t="n"/>
+        <v>53</v>
+      </c>
+      <c r="K184" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L184" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="M184" s="4" t="n">
+        <v>71.00759172250289</v>
+      </c>
       <c r="N184" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/ITCELSETSP2VEN</t>
@@ -13655,20 +13957,26 @@
       </c>
       <c r="H186" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I186" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I186" s="4" t="inlineStr"/>
       <c r="J186" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K186" s="4" t="inlineStr"/>
-      <c r="L186" s="4" t="inlineStr"/>
-      <c r="M186" s="4" t="n"/>
+        <v>32</v>
+      </c>
+      <c r="K186" s="4" t="inlineStr">
+        <is>
+          <t>1990-01-01</t>
+        </is>
+      </c>
+      <c r="L186" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="M186" s="4" t="n">
+        <v>76.67890167</v>
+      </c>
       <c r="N186" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/ITNETUSERP2VEN</t>
@@ -14239,20 +14547,26 @@
       </c>
       <c r="H194" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I194" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I194" s="4" t="inlineStr"/>
       <c r="J194" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K194" s="4" t="inlineStr"/>
-      <c r="L194" s="4" t="inlineStr"/>
-      <c r="M194" s="4" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K194" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L194" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M194" s="4" t="n">
+        <v>0.08436375111341481</v>
+      </c>
       <c r="N194" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/LABSHPVEA156NRUG</t>
@@ -15042,20 +15356,26 @@
       </c>
       <c r="H205" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I205" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I205" s="4" t="inlineStr"/>
       <c r="J205" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K205" s="4" t="inlineStr"/>
-      <c r="L205" s="4" t="inlineStr"/>
-      <c r="M205" s="4" t="n"/>
+        <v>66</v>
+      </c>
+      <c r="K205" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L205" s="4" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M205" s="4" t="n">
+        <v>99661244155.6306</v>
+      </c>
       <c r="N205" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MKTGDPVEA646NWDB</t>
@@ -15115,20 +15435,26 @@
       </c>
       <c r="H206" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I206" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I206" s="4" t="inlineStr"/>
       <c r="J206" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K206" s="4" t="inlineStr"/>
-      <c r="L206" s="4" t="inlineStr"/>
-      <c r="M206" s="4" t="n"/>
+        <v>66</v>
+      </c>
+      <c r="K206" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L206" s="4" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M206" s="4" t="n">
+        <v>98061244155.6306</v>
+      </c>
       <c r="N206" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MKTGNIVEA646NWDB</t>
@@ -15772,20 +16098,26 @@
       </c>
       <c r="H215" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I215" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I215" s="4" t="inlineStr"/>
       <c r="J215" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K215" s="4" t="inlineStr"/>
-      <c r="L215" s="4" t="inlineStr"/>
-      <c r="M215" s="4" t="n"/>
+        <v>302</v>
+      </c>
+      <c r="K215" s="4" t="inlineStr">
+        <is>
+          <t>1994-01-01</t>
+        </is>
+      </c>
+      <c r="L215" s="4" t="inlineStr">
+        <is>
+          <t>2019-02-01</t>
+        </is>
+      </c>
+      <c r="M215" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="N215" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NBVEBIS</t>
@@ -16867,20 +17199,26 @@
       </c>
       <c r="H230" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I230" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I230" s="4" t="inlineStr"/>
       <c r="J230" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K230" s="4" t="inlineStr"/>
-      <c r="L230" s="4" t="inlineStr"/>
-      <c r="M230" s="4" t="n"/>
+        <v>55</v>
+      </c>
+      <c r="K230" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L230" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M230" s="4" t="n">
+        <v>14026.3664129191</v>
+      </c>
       <c r="N230" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NYGDPPCAPKDVEN</t>
@@ -18181,20 +18519,26 @@
       </c>
       <c r="H248" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I248" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I248" s="4" t="inlineStr"/>
       <c r="J248" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K248" s="4" t="inlineStr"/>
-      <c r="L248" s="4" t="inlineStr"/>
-      <c r="M248" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K248" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L248" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M248" s="4" t="n">
+        <v>11809.94057</v>
+      </c>
       <c r="N248" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PC2GDPVEA620NUPN</t>
@@ -18254,20 +18598,26 @@
       </c>
       <c r="H249" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I249" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I249" s="4" t="inlineStr"/>
       <c r="J249" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K249" s="4" t="inlineStr"/>
-      <c r="L249" s="4" t="inlineStr"/>
-      <c r="M249" s="4" t="n"/>
+        <v>66</v>
+      </c>
+      <c r="K249" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L249" s="4" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M249" s="4" t="n">
+        <v>3494.8138870244</v>
+      </c>
       <c r="N249" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PCAGDPVEA646NWDB</t>
@@ -18473,20 +18823,26 @@
       </c>
       <c r="H252" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I252" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I252" s="4" t="inlineStr"/>
       <c r="J252" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K252" s="4" t="inlineStr"/>
-      <c r="L252" s="4" t="inlineStr"/>
-      <c r="M252" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K252" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L252" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M252" s="4" t="n">
+        <v>25.29171848</v>
+      </c>
       <c r="N252" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PGDPUSVEA621NUPN</t>
@@ -18546,20 +18902,26 @@
       </c>
       <c r="H253" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I253" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I253" s="4" t="inlineStr"/>
       <c r="J253" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K253" s="4" t="inlineStr"/>
-      <c r="L253" s="4" t="inlineStr"/>
-      <c r="M253" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K253" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L253" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M253" s="4" t="n">
+        <v>121.3461635</v>
+      </c>
       <c r="N253" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PL2GDPVEA621NUPN</t>
@@ -18619,20 +18981,26 @@
       </c>
       <c r="H254" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I254" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I254" s="4" t="inlineStr"/>
       <c r="J254" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K254" s="4" t="inlineStr"/>
-      <c r="L254" s="4" t="inlineStr"/>
-      <c r="M254" s="4" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K254" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L254" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M254" s="4" t="n">
+        <v>65.5449341102796</v>
+      </c>
       <c r="N254" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLCCPPVEA670NRUG</t>
@@ -18692,20 +19060,26 @@
       </c>
       <c r="H255" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I255" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I255" s="4" t="inlineStr"/>
       <c r="J255" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K255" s="4" t="inlineStr"/>
-      <c r="L255" s="4" t="inlineStr"/>
-      <c r="M255" s="4" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K255" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L255" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M255" s="4" t="n">
+        <v>23.2163643183614</v>
+      </c>
       <c r="N255" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLGCPPVEA670NRUG</t>
@@ -18984,20 +19358,26 @@
       </c>
       <c r="H259" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I259" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I259" s="4" t="inlineStr"/>
       <c r="J259" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K259" s="4" t="inlineStr"/>
-      <c r="L259" s="4" t="inlineStr"/>
-      <c r="M259" s="4" t="n"/>
+        <v>70</v>
+      </c>
+      <c r="K259" s="4" t="inlineStr">
+        <is>
+          <t>1954-01-01</t>
+        </is>
+      </c>
+      <c r="L259" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M259" s="4" t="n">
+        <v>15.1081390380859</v>
+      </c>
       <c r="N259" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLKCPPVEA670NRUG</t>
@@ -19349,20 +19729,26 @@
       </c>
       <c r="H264" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I264" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I264" s="4" t="inlineStr"/>
       <c r="J264" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K264" s="4" t="inlineStr"/>
-      <c r="L264" s="4" t="inlineStr"/>
-      <c r="M264" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K264" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L264" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M264" s="4" t="n">
+        <v>119.0453568</v>
+      </c>
       <c r="N264" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLOINVVEA624NUPN</t>
@@ -19422,20 +19808,26 @@
       </c>
       <c r="H265" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I265" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I265" s="4" t="inlineStr"/>
       <c r="J265" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K265" s="4" t="inlineStr"/>
-      <c r="L265" s="4" t="inlineStr"/>
-      <c r="M265" s="4" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K265" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L265" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M265" s="4" t="n">
+        <v>0.206251129508019</v>
+      </c>
       <c r="N265" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLXCPPVEA670NRUG</t>
@@ -19491,20 +19883,26 @@
       <c r="G266" s="4" t="inlineStr"/>
       <c r="H266" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I266" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I266" s="4" t="inlineStr"/>
       <c r="J266" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K266" s="4" t="inlineStr"/>
-      <c r="L266" s="4" t="inlineStr"/>
-      <c r="M266" s="4" t="n"/>
+        <v>66</v>
+      </c>
+      <c r="K266" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L266" s="4" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M266" s="4" t="n">
+        <v>28516896</v>
+      </c>
       <c r="N266" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/POPTOTVEA647NWDB</t>
@@ -19564,20 +19962,26 @@
       </c>
       <c r="H267" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I267" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I267" s="4" t="inlineStr"/>
       <c r="J267" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K267" s="4" t="inlineStr"/>
-      <c r="L267" s="4" t="inlineStr"/>
-      <c r="M267" s="4" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K267" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L267" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M267" s="4" t="n">
+        <v>28.300854</v>
+      </c>
       <c r="N267" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/POPTTLVEA148NRUG</t>
@@ -19637,20 +20041,26 @@
       </c>
       <c r="H268" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I268" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I268" s="4" t="inlineStr"/>
       <c r="J268" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K268" s="4" t="inlineStr"/>
-      <c r="L268" s="4" t="inlineStr"/>
-      <c r="M268" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K268" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L268" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M268" s="4" t="n">
+        <v>27223.228</v>
+      </c>
       <c r="N268" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/POPTTLVEA173NUPN</t>
@@ -19710,20 +20120,26 @@
       </c>
       <c r="H269" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I269" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I269" s="4" t="inlineStr"/>
       <c r="J269" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K269" s="4" t="inlineStr"/>
-      <c r="L269" s="4" t="inlineStr"/>
-      <c r="M269" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K269" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L269" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M269" s="4" t="n">
+        <v>11777.99098</v>
+      </c>
       <c r="N269" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PPCGDPVEA620NUPN</t>
@@ -19856,20 +20272,26 @@
       </c>
       <c r="H271" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I271" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I271" s="4" t="inlineStr"/>
       <c r="J271" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K271" s="4" t="inlineStr"/>
-      <c r="L271" s="4" t="inlineStr"/>
-      <c r="M271" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K271" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L271" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M271" s="4" t="n">
+        <v>3.155532204</v>
+      </c>
       <c r="N271" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PPPTTLVEA618NUPN</t>
@@ -19929,20 +20351,26 @@
       </c>
       <c r="H272" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I272" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I272" s="4" t="inlineStr"/>
       <c r="J272" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K272" s="4" t="inlineStr"/>
-      <c r="L272" s="4" t="inlineStr"/>
-      <c r="M272" s="4" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="K272" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L272" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M272" s="4" t="n">
+        <v>4890168</v>
+      </c>
       <c r="N272" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PRVENA052SCEN</t>
@@ -20075,20 +20503,26 @@
       </c>
       <c r="H274" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I274" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I274" s="4" t="inlineStr"/>
       <c r="J274" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K274" s="4" t="inlineStr"/>
-      <c r="L274" s="4" t="inlineStr"/>
-      <c r="M274" s="4" t="n"/>
+        <v>302</v>
+      </c>
+      <c r="K274" s="4" t="inlineStr">
+        <is>
+          <t>1994-01-01</t>
+        </is>
+      </c>
+      <c r="L274" s="4" t="inlineStr">
+        <is>
+          <t>2019-02-01</t>
+        </is>
+      </c>
+      <c r="M274" s="4" t="n">
+        <v>0.68</v>
+      </c>
       <c r="N274" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RBVEBIS</t>
@@ -20148,20 +20582,26 @@
       </c>
       <c r="H275" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I275" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I275" s="4" t="inlineStr"/>
       <c r="J275" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K275" s="4" t="inlineStr"/>
-      <c r="L275" s="4" t="inlineStr"/>
-      <c r="M275" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K275" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L275" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M275" s="4" t="n">
+        <v>9070.606092</v>
+      </c>
       <c r="N275" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RGDPCHVEA625NUPN</t>
@@ -20294,20 +20734,26 @@
       </c>
       <c r="H277" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I277" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I277" s="4" t="inlineStr"/>
       <c r="J277" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K277" s="4" t="inlineStr"/>
-      <c r="L277" s="4" t="inlineStr"/>
-      <c r="M277" s="4" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K277" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L277" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M277" s="4" t="n">
+        <v>2528.005859375</v>
+      </c>
       <c r="N277" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RGDPESVEA666NRUG</t>
@@ -20367,20 +20813,26 @@
       </c>
       <c r="H278" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I278" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I278" s="4" t="inlineStr"/>
       <c r="J278" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K278" s="4" t="inlineStr"/>
-      <c r="L278" s="4" t="inlineStr"/>
-      <c r="M278" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K278" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L278" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M278" s="4" t="n">
+        <v>9061.718438</v>
+      </c>
       <c r="N278" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RGDPL2VEA625NUPN</t>
@@ -20440,20 +20892,26 @@
       </c>
       <c r="H279" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I279" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I279" s="4" t="inlineStr"/>
       <c r="J279" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K279" s="4" t="inlineStr"/>
-      <c r="L279" s="4" t="inlineStr"/>
-      <c r="M279" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K279" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L279" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M279" s="4" t="n">
+        <v>9070.929923</v>
+      </c>
       <c r="N279" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RGDPLPVEA625NUPN</t>
@@ -20586,20 +21044,26 @@
       </c>
       <c r="H281" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I281" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I281" s="4" t="inlineStr"/>
       <c r="J281" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K281" s="4" t="inlineStr"/>
-      <c r="L281" s="4" t="inlineStr"/>
-      <c r="M281" s="4" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K281" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L281" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M281" s="4" t="n">
+        <v>5304.27978515625</v>
+      </c>
       <c r="N281" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RGDPNAVEA666NRUG</t>
@@ -20659,20 +21123,26 @@
       </c>
       <c r="H282" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I282" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I282" s="4" t="inlineStr"/>
       <c r="J282" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K282" s="4" t="inlineStr"/>
-      <c r="L282" s="4" t="inlineStr"/>
-      <c r="M282" s="4" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K282" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L282" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M282" s="4" t="n">
+        <v>4501.99462890625</v>
+      </c>
       <c r="N282" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RGDPOSVEA666NRUG</t>
@@ -21170,20 +21640,26 @@
       </c>
       <c r="H289" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I289" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I289" s="4" t="inlineStr"/>
       <c r="J289" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K289" s="4" t="inlineStr"/>
-      <c r="L289" s="4" t="inlineStr"/>
-      <c r="M289" s="4" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K289" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L289" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M289" s="4" t="n">
+        <v>119927.1796875</v>
+      </c>
       <c r="N289" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RKNANPVEA666NRUG</t>
@@ -21243,20 +21719,26 @@
       </c>
       <c r="H290" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I290" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I290" s="4" t="inlineStr"/>
       <c r="J290" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K290" s="4" t="inlineStr"/>
-      <c r="L290" s="4" t="inlineStr"/>
-      <c r="M290" s="4" t="n"/>
+        <v>70</v>
+      </c>
+      <c r="K290" s="4" t="inlineStr">
+        <is>
+          <t>1954-01-01</t>
+        </is>
+      </c>
+      <c r="L290" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M290" s="4" t="n">
+        <v>1.22892010211945</v>
+      </c>
       <c r="N290" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RTFPNAVEA632NRUG</t>
@@ -21608,20 +22090,26 @@
       </c>
       <c r="H295" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I295" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I295" s="4" t="inlineStr"/>
       <c r="J295" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K295" s="4" t="inlineStr"/>
-      <c r="L295" s="4" t="inlineStr"/>
-      <c r="M295" s="4" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="K295" s="4" t="inlineStr">
+        <is>
+          <t>1981-01-01</t>
+        </is>
+      </c>
+      <c r="L295" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M295" s="4" t="n">
+        <v>97.59999847412109</v>
+      </c>
       <c r="N295" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SEADTLITRZSVEN</t>
@@ -21900,20 +22388,26 @@
       </c>
       <c r="H299" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I299" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I299" s="4" t="inlineStr"/>
       <c r="J299" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K299" s="4" t="inlineStr"/>
-      <c r="L299" s="4" t="inlineStr"/>
-      <c r="M299" s="4" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="K299" s="4" t="inlineStr">
+        <is>
+          <t>1981-01-01</t>
+        </is>
+      </c>
+      <c r="L299" s="4" t="inlineStr">
+        <is>
+          <t>2006-01-01</t>
+        </is>
+      </c>
+      <c r="M299" s="4" t="n">
+        <v>44.7</v>
+      </c>
       <c r="N299" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SIPOVGINIVEN</t>
@@ -21973,20 +22467,26 @@
       </c>
       <c r="H300" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I300" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I300" s="4" t="inlineStr"/>
       <c r="J300" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K300" s="4" t="inlineStr"/>
-      <c r="L300" s="4" t="inlineStr"/>
-      <c r="M300" s="4" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="K300" s="4" t="inlineStr">
+        <is>
+          <t>1991-01-01</t>
+        </is>
+      </c>
+      <c r="L300" s="4" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M300" s="4" t="n">
+        <v>49.171</v>
+      </c>
       <c r="N300" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SLEMPTOTLSPZSVEN</t>
@@ -22046,20 +22546,26 @@
       </c>
       <c r="H301" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I301" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I301" s="4" t="inlineStr"/>
       <c r="J301" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K301" s="4" t="inlineStr"/>
-      <c r="L301" s="4" t="inlineStr"/>
-      <c r="M301" s="4" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="K301" s="4" t="inlineStr">
+        <is>
+          <t>1991-01-01</t>
+        </is>
+      </c>
+      <c r="L301" s="4" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M301" s="4" t="n">
+        <v>10.444</v>
+      </c>
       <c r="N301" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SLUEM1524ZSVEN</t>
@@ -22119,20 +22625,26 @@
       </c>
       <c r="H302" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I302" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I302" s="4" t="inlineStr"/>
       <c r="J302" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K302" s="4" t="inlineStr"/>
-      <c r="L302" s="4" t="inlineStr"/>
-      <c r="M302" s="4" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="K302" s="4" t="inlineStr">
+        <is>
+          <t>1962-01-01</t>
+        </is>
+      </c>
+      <c r="L302" s="4" t="inlineStr">
+        <is>
+          <t>2017-01-01</t>
+        </is>
+      </c>
+      <c r="M302" s="4" t="n">
+        <v>-3266243</v>
+      </c>
       <c r="N302" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SMPOPNETMVEN</t>
@@ -22192,20 +22704,26 @@
       </c>
       <c r="H303" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I303" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I303" s="4" t="inlineStr"/>
       <c r="J303" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K303" s="4" t="inlineStr"/>
-      <c r="L303" s="4" t="inlineStr"/>
-      <c r="M303" s="4" t="n"/>
+        <v>53</v>
+      </c>
+      <c r="K303" s="4" t="inlineStr">
+        <is>
+          <t>1969-01-01</t>
+        </is>
+      </c>
+      <c r="L303" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M303" s="4" t="n">
+        <v>29336</v>
+      </c>
       <c r="N303" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SMPOPREFGVEN</t>
@@ -22338,20 +22856,26 @@
       </c>
       <c r="H305" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I305" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I305" s="4" t="inlineStr"/>
       <c r="J305" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K305" s="4" t="inlineStr"/>
-      <c r="L305" s="4" t="inlineStr"/>
-      <c r="M305" s="4" t="n"/>
+        <v>65</v>
+      </c>
+      <c r="K305" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L305" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="M305" s="4" t="n">
+        <v>73.18899999999999</v>
+      </c>
       <c r="N305" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SPADOTFRTVEN</t>
@@ -22411,20 +22935,26 @@
       </c>
       <c r="H306" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I306" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I306" s="4" t="inlineStr"/>
       <c r="J306" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K306" s="4" t="inlineStr"/>
-      <c r="L306" s="4" t="inlineStr"/>
-      <c r="M306" s="4" t="n"/>
+        <v>65</v>
+      </c>
+      <c r="K306" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L306" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="M306" s="4" t="n">
+        <v>15.231</v>
+      </c>
       <c r="N306" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SPDYNCBRTINVEN</t>
@@ -22484,20 +23014,26 @@
       </c>
       <c r="H307" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I307" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I307" s="4" t="inlineStr"/>
       <c r="J307" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K307" s="4" t="inlineStr"/>
-      <c r="L307" s="4" t="inlineStr"/>
-      <c r="M307" s="4" t="n"/>
+        <v>65</v>
+      </c>
+      <c r="K307" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L307" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="M307" s="4" t="n">
+        <v>21.2</v>
+      </c>
       <c r="N307" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SPDYNIMRTINVEN</t>
@@ -22557,20 +23093,26 @@
       </c>
       <c r="H308" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I308" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I308" s="4" t="inlineStr"/>
       <c r="J308" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K308" s="4" t="inlineStr"/>
-      <c r="L308" s="4" t="inlineStr"/>
-      <c r="M308" s="4" t="n"/>
+        <v>65</v>
+      </c>
+      <c r="K308" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L308" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="M308" s="4" t="n">
+        <v>72.673</v>
+      </c>
       <c r="N308" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SPDYNLE00INVEN</t>
@@ -22630,20 +23172,26 @@
       </c>
       <c r="H309" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I309" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I309" s="4" t="inlineStr"/>
       <c r="J309" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K309" s="4" t="inlineStr"/>
-      <c r="L309" s="4" t="inlineStr"/>
-      <c r="M309" s="4" t="n"/>
+        <v>65</v>
+      </c>
+      <c r="K309" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L309" s="4" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="M309" s="4" t="n">
+        <v>2.077</v>
+      </c>
       <c r="N309" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SPDYNTFRTINVEN</t>
@@ -22849,20 +23397,26 @@
       </c>
       <c r="H312" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I312" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I312" s="4" t="inlineStr"/>
       <c r="J312" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K312" s="4" t="inlineStr"/>
-      <c r="L312" s="4" t="inlineStr"/>
-      <c r="M312" s="4" t="n"/>
+        <v>66</v>
+      </c>
+      <c r="K312" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L312" s="4" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M312" s="4" t="n">
+        <v>10.0182554931645</v>
+      </c>
       <c r="N312" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SPPOP65UPTOZSVEN</t>
@@ -22922,20 +23476,26 @@
       </c>
       <c r="H313" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I313" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I313" s="4" t="inlineStr"/>
       <c r="J313" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K313" s="4" t="inlineStr"/>
-      <c r="L313" s="4" t="inlineStr"/>
-      <c r="M313" s="4" t="n"/>
+        <v>66</v>
+      </c>
+      <c r="K313" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L313" s="4" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M313" s="4" t="n">
+        <v>15.397128883349</v>
+      </c>
       <c r="N313" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SPPOPDPNDOLVEN</t>
@@ -22995,20 +23555,26 @@
       </c>
       <c r="H314" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I314" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I314" s="4" t="inlineStr"/>
       <c r="J314" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K314" s="4" t="inlineStr"/>
-      <c r="L314" s="4" t="inlineStr"/>
-      <c r="M314" s="4" t="n"/>
+        <v>65</v>
+      </c>
+      <c r="K314" s="4" t="inlineStr">
+        <is>
+          <t>1961-01-01</t>
+        </is>
+      </c>
+      <c r="L314" s="4" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M314" s="4" t="n">
+        <v>0.39124515392802</v>
+      </c>
       <c r="N314" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SPPOPGROWVEN</t>
@@ -23871,20 +24437,26 @@
       </c>
       <c r="H326" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I326" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I326" s="4" t="inlineStr"/>
       <c r="J326" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K326" s="4" t="inlineStr"/>
-      <c r="L326" s="4" t="inlineStr"/>
-      <c r="M326" s="4" t="n"/>
+        <v>387</v>
+      </c>
+      <c r="K326" s="4" t="inlineStr">
+        <is>
+          <t>1994-03-01</t>
+        </is>
+      </c>
+      <c r="L326" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M326" s="4" t="n">
+        <v>7</v>
+      </c>
       <c r="N326" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTEQTYPOS32719</t>
@@ -25331,20 +25903,26 @@
       </c>
       <c r="H346" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I346" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I346" s="4" t="inlineStr"/>
       <c r="J346" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K346" s="4" t="inlineStr"/>
-      <c r="L346" s="4" t="inlineStr"/>
-      <c r="M346" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K346" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L346" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M346" s="4" t="n">
+        <v>1769451</v>
+      </c>
       <c r="N346" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCAOFILNNUM</t>
@@ -26718,20 +27296,26 @@
       </c>
       <c r="H365" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I365" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I365" s="4" t="inlineStr"/>
       <c r="J365" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K365" s="4" t="inlineStr"/>
-      <c r="L365" s="4" t="inlineStr"/>
-      <c r="M365" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K365" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L365" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M365" s="4" t="n">
+        <v>26</v>
+      </c>
       <c r="N365" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCIODCNUM</t>
@@ -27010,20 +27594,26 @@
       </c>
       <c r="H369" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I369" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I369" s="4" t="inlineStr"/>
       <c r="J369" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K369" s="4" t="inlineStr"/>
-      <c r="L369" s="4" t="inlineStr"/>
-      <c r="M369" s="4" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="K369" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L369" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M369" s="4" t="n">
+        <v>68.50582168130001</v>
+      </c>
       <c r="N369" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCLODCGGDPPT</t>
@@ -27521,20 +28111,26 @@
       </c>
       <c r="H376" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I376" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I376" s="4" t="inlineStr"/>
       <c r="J376" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K376" s="4" t="inlineStr"/>
-      <c r="L376" s="4" t="inlineStr"/>
-      <c r="M376" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K376" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L376" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M376" s="4" t="n">
+        <v>37322701822.99</v>
+      </c>
       <c r="N376" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCLODMFXDC</t>
@@ -27886,20 +28482,26 @@
       </c>
       <c r="H381" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I381" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I381" s="4" t="inlineStr"/>
       <c r="J381" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K381" s="4" t="inlineStr"/>
-      <c r="L381" s="4" t="inlineStr"/>
-      <c r="M381" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K381" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L381" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M381" s="4" t="n">
+        <v>23665733</v>
+      </c>
       <c r="N381" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCNODCNUM</t>
@@ -29784,20 +30386,26 @@
       </c>
       <c r="H407" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I407" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I407" s="4" t="inlineStr"/>
       <c r="J407" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K407" s="4" t="inlineStr"/>
-      <c r="L407" s="4" t="inlineStr"/>
-      <c r="M407" s="4" t="n"/>
+        <v>291</v>
+      </c>
+      <c r="K407" s="4" t="inlineStr">
+        <is>
+          <t>1953-07-01</t>
+        </is>
+      </c>
+      <c r="L407" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M407" s="4" t="n">
+        <v>1.178428</v>
+      </c>
       <c r="N407" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/WUIVEN</t>
@@ -30003,20 +30611,26 @@
       </c>
       <c r="H410" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I410" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I410" s="4" t="inlineStr"/>
       <c r="J410" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K410" s="4" t="inlineStr"/>
-      <c r="L410" s="4" t="inlineStr"/>
-      <c r="M410" s="4" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="K410" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L410" s="4" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="M410" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="N410" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/WVVENA475SCEN</t>
@@ -30222,20 +30836,26 @@
       </c>
       <c r="H413" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I413" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I413" s="4" t="inlineStr"/>
       <c r="J413" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K413" s="4" t="inlineStr"/>
-      <c r="L413" s="4" t="inlineStr"/>
-      <c r="M413" s="4" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K413" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L413" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M413" s="4" t="n">
+        <v>8.67714612014831</v>
+      </c>
       <c r="N413" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/XRNCUSVEA618NRUG</t>
@@ -30394,7 +31014,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15">
@@ -30404,7 +31024,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>0</v>
+        <v>13983</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/fred/catalog/catalogo_dataset_web_ove_fred.xlsx
+++ b/assets/data/fred/catalog/catalogo_dataset_web_ove_fred.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="catalogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="catalogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="[$-es-ES]#,##0"/>
+    <numFmt numFmtId="165" formatCode="[$-es-ES]#,##0.00"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -69,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -83,84 +86,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -175,13 +116,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -190,7 +134,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -205,13 +149,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -680,7 +627,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="J7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K7" s="4" t="inlineStr"/>
@@ -753,7 +700,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="J8" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K8" s="4" t="inlineStr"/>
@@ -826,7 +773,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="J9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K9" s="4" t="inlineStr"/>
@@ -899,7 +846,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J10" s="4" t="n">
+      <c r="J10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K10" s="4" t="inlineStr"/>
@@ -972,7 +919,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J11" s="4" t="n">
+      <c r="J11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K11" s="4" t="inlineStr"/>
@@ -1045,7 +992,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J12" s="4" t="n">
+      <c r="J12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="4" t="inlineStr"/>
@@ -1114,7 +1061,7 @@
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr"/>
-      <c r="J13" s="4" t="n">
+      <c r="J13" s="7" t="n">
         <v>74</v>
       </c>
       <c r="K13" s="4" t="inlineStr">
@@ -1127,7 +1074,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M13" s="4" t="n">
+      <c r="M13" s="8" t="n">
         <v>1776.7</v>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1197,7 +1144,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J14" s="4" t="n">
+      <c r="J14" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K14" s="4" t="inlineStr"/>
@@ -1270,7 +1217,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J15" s="4" t="n">
+      <c r="J15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K15" s="4" t="inlineStr"/>
@@ -1339,7 +1286,7 @@
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr"/>
-      <c r="J16" s="4" t="n">
+      <c r="J16" s="7" t="n">
         <v>9</v>
       </c>
       <c r="K16" s="4" t="inlineStr">
@@ -1352,7 +1299,7 @@
           <t>2010-01-01</t>
         </is>
       </c>
-      <c r="M16" s="4" t="n">
+      <c r="M16" s="8" t="n">
         <v>15.92</v>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -1418,7 +1365,7 @@
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr"/>
-      <c r="J17" s="4" t="n">
+      <c r="J17" s="7" t="n">
         <v>16</v>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1431,7 +1378,7 @@
           <t>2005-01-01</t>
         </is>
       </c>
-      <c r="M17" s="4" t="n">
+      <c r="M17" s="8" t="n">
         <v>95.9703157644156</v>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -1501,7 +1448,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J18" s="4" t="n">
+      <c r="J18" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K18" s="4" t="inlineStr"/>
@@ -1574,7 +1521,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J19" s="4" t="n">
+      <c r="J19" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K19" s="4" t="inlineStr"/>
@@ -1643,7 +1590,7 @@
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr"/>
-      <c r="J20" s="4" t="n">
+      <c r="J20" s="7" t="n">
         <v>74</v>
       </c>
       <c r="K20" s="4" t="inlineStr">
@@ -1656,7 +1603,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M20" s="4" t="n">
+      <c r="M20" s="8" t="n">
         <v>2523.1025390625</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -1722,7 +1669,7 @@
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr"/>
-      <c r="J21" s="4" t="n">
+      <c r="J21" s="7" t="n">
         <v>74</v>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -1735,7 +1682,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M21" s="4" t="n">
+      <c r="M21" s="8" t="n">
         <v>4408.41650390625</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -1805,7 +1752,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J22" s="4" t="n">
+      <c r="J22" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
@@ -1878,7 +1825,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J23" s="4" t="n">
+      <c r="J23" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K23" s="4" t="inlineStr"/>
@@ -1947,7 +1894,7 @@
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr"/>
-      <c r="J24" s="4" t="n">
+      <c r="J24" s="7" t="n">
         <v>74</v>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -1960,7 +1907,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M24" s="4" t="n">
+      <c r="M24" s="8" t="n">
         <v>120241.203125</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -2030,7 +1977,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J25" s="4" t="n">
+      <c r="J25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K25" s="4" t="inlineStr"/>
@@ -2103,7 +2050,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J26" s="4" t="n">
+      <c r="J26" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K26" s="4" t="inlineStr"/>
@@ -2176,7 +2123,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J27" s="4" t="n">
+      <c r="J27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K27" s="4" t="inlineStr"/>
@@ -2249,7 +2196,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J28" s="4" t="n">
+      <c r="J28" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K28" s="4" t="inlineStr"/>
@@ -2318,7 +2265,7 @@
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr"/>
-      <c r="J29" s="4" t="n">
+      <c r="J29" s="7" t="n">
         <v>74</v>
       </c>
       <c r="K29" s="4" t="inlineStr">
@@ -2331,7 +2278,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M29" s="4" t="n">
+      <c r="M29" s="8" t="n">
         <v>0.0565520189702511</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -2401,7 +2348,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J30" s="4" t="n">
+      <c r="J30" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="4" t="inlineStr"/>
@@ -2474,7 +2421,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J31" s="4" t="n">
+      <c r="J31" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K31" s="4" t="inlineStr"/>
@@ -2547,7 +2494,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J32" s="4" t="n">
+      <c r="J32" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K32" s="4" t="inlineStr"/>
@@ -2620,7 +2567,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J33" s="4" t="n">
+      <c r="J33" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K33" s="4" t="inlineStr"/>
@@ -2689,7 +2636,7 @@
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr"/>
-      <c r="J34" s="4" t="n">
+      <c r="J34" s="7" t="n">
         <v>70</v>
       </c>
       <c r="K34" s="4" t="inlineStr">
@@ -2702,7 +2649,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M34" s="4" t="n">
+      <c r="M34" s="8" t="n">
         <v>0.0518108420073986</v>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -2772,7 +2719,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J35" s="4" t="n">
+      <c r="J35" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K35" s="4" t="inlineStr"/>
@@ -2845,7 +2792,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J36" s="4" t="n">
+      <c r="J36" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K36" s="4" t="inlineStr"/>
@@ -2918,7 +2865,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J37" s="4" t="n">
+      <c r="J37" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K37" s="4" t="inlineStr"/>
@@ -2991,7 +2938,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J38" s="4" t="n">
+      <c r="J38" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K38" s="4" t="inlineStr"/>
@@ -3060,7 +3007,7 @@
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr"/>
-      <c r="J39" s="4" t="n">
+      <c r="J39" s="7" t="n">
         <v>11</v>
       </c>
       <c r="K39" s="4" t="inlineStr">
@@ -3073,7 +3020,7 @@
           <t>2015-01-01</t>
         </is>
       </c>
-      <c r="M39" s="4" t="n">
+      <c r="M39" s="8" t="n">
         <v>16.533233</v>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -3143,7 +3090,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J40" s="4" t="n">
+      <c r="J40" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K40" s="4" t="inlineStr"/>
@@ -3216,7 +3163,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J41" s="4" t="n">
+      <c r="J41" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K41" s="4" t="inlineStr"/>
@@ -3289,7 +3236,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J42" s="4" t="n">
+      <c r="J42" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K42" s="4" t="inlineStr"/>
@@ -3362,7 +3309,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J43" s="4" t="n">
+      <c r="J43" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K43" s="4" t="inlineStr"/>
@@ -3435,7 +3382,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J44" s="4" t="n">
+      <c r="J44" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K44" s="4" t="inlineStr"/>
@@ -3508,7 +3455,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J45" s="4" t="n">
+      <c r="J45" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K45" s="4" t="inlineStr"/>
@@ -3581,7 +3528,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J46" s="4" t="n">
+      <c r="J46" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K46" s="4" t="inlineStr"/>
@@ -3654,7 +3601,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J47" s="4" t="n">
+      <c r="J47" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K47" s="4" t="inlineStr"/>
@@ -3727,7 +3674,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J48" s="4" t="n">
+      <c r="J48" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K48" s="4" t="inlineStr"/>
@@ -3800,7 +3747,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J49" s="4" t="n">
+      <c r="J49" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K49" s="4" t="inlineStr"/>
@@ -3873,7 +3820,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J50" s="4" t="n">
+      <c r="J50" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K50" s="4" t="inlineStr"/>
@@ -3942,7 +3889,7 @@
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr"/>
-      <c r="J51" s="4" t="n">
+      <c r="J51" s="7" t="n">
         <v>54</v>
       </c>
       <c r="K51" s="4" t="inlineStr">
@@ -3955,7 +3902,7 @@
           <t>2013-01-01</t>
         </is>
       </c>
-      <c r="M51" s="4" t="n">
+      <c r="M51" s="8" t="n">
         <v>20.13813</v>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -4025,7 +3972,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J52" s="4" t="n">
+      <c r="J52" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K52" s="4" t="inlineStr"/>
@@ -4098,7 +4045,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J53" s="4" t="n">
+      <c r="J53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K53" s="4" t="inlineStr"/>
@@ -4171,7 +4118,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J54" s="4" t="n">
+      <c r="J54" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K54" s="4" t="inlineStr"/>
@@ -4244,7 +4191,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J55" s="4" t="n">
+      <c r="J55" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K55" s="4" t="inlineStr"/>
@@ -4317,7 +4264,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J56" s="4" t="n">
+      <c r="J56" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K56" s="4" t="inlineStr"/>
@@ -4386,7 +4333,7 @@
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr"/>
-      <c r="J57" s="4" t="n">
+      <c r="J57" s="7" t="n">
         <v>10</v>
       </c>
       <c r="K57" s="4" t="inlineStr">
@@ -4399,7 +4346,7 @@
           <t>2002-01-01</t>
         </is>
       </c>
-      <c r="M57" s="4" t="n">
+      <c r="M57" s="8" t="n">
         <v>4.28404</v>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -4469,7 +4416,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J58" s="4" t="n">
+      <c r="J58" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K58" s="4" t="inlineStr"/>
@@ -4542,7 +4489,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J59" s="4" t="n">
+      <c r="J59" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K59" s="4" t="inlineStr"/>
@@ -4615,7 +4562,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J60" s="4" t="n">
+      <c r="J60" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K60" s="4" t="inlineStr"/>
@@ -4688,7 +4635,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J61" s="4" t="n">
+      <c r="J61" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K61" s="4" t="inlineStr"/>
@@ -4757,7 +4704,7 @@
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr"/>
-      <c r="J62" s="4" t="n">
+      <c r="J62" s="7" t="n">
         <v>41</v>
       </c>
       <c r="K62" s="4" t="inlineStr">
@@ -4770,7 +4717,7 @@
           <t>2020-01-01</t>
         </is>
       </c>
-      <c r="M62" s="4" t="n">
+      <c r="M62" s="8" t="n">
         <v>22.39961</v>
       </c>
       <c r="N62" s="4" t="inlineStr">
@@ -4836,7 +4783,7 @@
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr"/>
-      <c r="J63" s="4" t="n">
+      <c r="J63" s="7" t="n">
         <v>41</v>
       </c>
       <c r="K63" s="4" t="inlineStr">
@@ -4849,7 +4796,7 @@
           <t>2020-01-01</t>
         </is>
       </c>
-      <c r="M63" s="4" t="n">
+      <c r="M63" s="8" t="n">
         <v>32.15886</v>
       </c>
       <c r="N63" s="4" t="inlineStr">
@@ -4919,7 +4866,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J64" s="4" t="n">
+      <c r="J64" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K64" s="4" t="inlineStr"/>
@@ -4992,7 +4939,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J65" s="4" t="n">
+      <c r="J65" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K65" s="4" t="inlineStr"/>
@@ -5061,7 +5008,7 @@
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr"/>
-      <c r="J66" s="4" t="n">
+      <c r="J66" s="7" t="n">
         <v>18</v>
       </c>
       <c r="K66" s="4" t="inlineStr">
@@ -5074,7 +5021,7 @@
           <t>2016-01-01</t>
         </is>
       </c>
-      <c r="M66" s="4" t="n">
+      <c r="M66" s="8" t="n">
         <v>0.8002833</v>
       </c>
       <c r="N66" s="4" t="inlineStr">
@@ -5144,7 +5091,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J67" s="4" t="n">
+      <c r="J67" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K67" s="4" t="inlineStr"/>
@@ -5213,7 +5160,7 @@
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr"/>
-      <c r="J68" s="4" t="n">
+      <c r="J68" s="7" t="n">
         <v>28</v>
       </c>
       <c r="K68" s="4" t="inlineStr">
@@ -5226,7 +5173,7 @@
           <t>2017-01-01</t>
         </is>
       </c>
-      <c r="M68" s="4" t="n">
+      <c r="M68" s="8" t="n">
         <v>6.326667</v>
       </c>
       <c r="N68" s="4" t="inlineStr">
@@ -5296,7 +5243,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J69" s="4" t="n">
+      <c r="J69" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K69" s="4" t="inlineStr"/>
@@ -5369,7 +5316,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J70" s="4" t="n">
+      <c r="J70" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K70" s="4" t="inlineStr"/>
@@ -5438,7 +5385,7 @@
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr"/>
-      <c r="J71" s="4" t="n">
+      <c r="J71" s="7" t="n">
         <v>22</v>
       </c>
       <c r="K71" s="4" t="inlineStr">
@@ -5451,7 +5398,7 @@
           <t>2021-01-01</t>
         </is>
       </c>
-      <c r="M71" s="4" t="n">
+      <c r="M71" s="8" t="n">
         <v>1.153893</v>
       </c>
       <c r="N71" s="4" t="inlineStr">
@@ -5521,7 +5468,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J72" s="4" t="n">
+      <c r="J72" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K72" s="4" t="inlineStr"/>
@@ -5594,7 +5541,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J73" s="4" t="n">
+      <c r="J73" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K73" s="4" t="inlineStr"/>
@@ -5663,7 +5610,7 @@
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr"/>
-      <c r="J74" s="4" t="n">
+      <c r="J74" s="7" t="n">
         <v>36</v>
       </c>
       <c r="K74" s="4" t="inlineStr">
@@ -5676,7 +5623,7 @@
           <t>2015-01-01</t>
         </is>
       </c>
-      <c r="M74" s="4" t="n">
+      <c r="M74" s="8" t="n">
         <v>7.325303999999998</v>
       </c>
       <c r="N74" s="4" t="inlineStr">
@@ -5746,7 +5693,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J75" s="4" t="n">
+      <c r="J75" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K75" s="4" t="inlineStr"/>
@@ -5803,7 +5750,7 @@
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr"/>
-      <c r="J76" s="4" t="n">
+      <c r="J76" s="7" t="n">
         <v>57</v>
       </c>
       <c r="K76" s="4" t="inlineStr">
@@ -5816,7 +5763,7 @@
           <t>2016-01-01</t>
         </is>
       </c>
-      <c r="M76" s="4" t="n">
+      <c r="M76" s="8" t="n">
         <v>4665.79</v>
       </c>
       <c r="N76" s="4" t="inlineStr">
@@ -5882,7 +5829,7 @@
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr"/>
-      <c r="J77" s="4" t="n">
+      <c r="J77" s="7" t="n">
         <v>22</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
@@ -5895,7 +5842,7 @@
           <t>2021-01-01</t>
         </is>
       </c>
-      <c r="M77" s="4" t="n">
+      <c r="M77" s="8" t="n">
         <v>84.4594</v>
       </c>
       <c r="N77" s="4" t="inlineStr">
@@ -5965,7 +5912,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J78" s="4" t="n">
+      <c r="J78" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K78" s="4" t="inlineStr"/>
@@ -6038,7 +5985,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J79" s="4" t="n">
+      <c r="J79" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K79" s="4" t="inlineStr"/>
@@ -6111,7 +6058,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J80" s="4" t="n">
+      <c r="J80" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K80" s="4" t="inlineStr"/>
@@ -6184,7 +6131,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J81" s="4" t="n">
+      <c r="J81" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K81" s="4" t="inlineStr"/>
@@ -6257,7 +6204,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J82" s="4" t="n">
+      <c r="J82" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K82" s="4" t="inlineStr"/>
@@ -6326,7 +6273,7 @@
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr"/>
-      <c r="J83" s="4" t="n">
+      <c r="J83" s="7" t="n">
         <v>54</v>
       </c>
       <c r="K83" s="4" t="inlineStr">
@@ -6339,7 +6286,7 @@
           <t>2013-01-01</t>
         </is>
       </c>
-      <c r="M83" s="4" t="n">
+      <c r="M83" s="8" t="n">
         <v>184310.5</v>
       </c>
       <c r="N83" s="4" t="inlineStr">
@@ -6409,7 +6356,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J84" s="4" t="n">
+      <c r="J84" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K84" s="4" t="inlineStr"/>
@@ -6482,7 +6429,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J85" s="4" t="n">
+      <c r="J85" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K85" s="4" t="inlineStr"/>
@@ -6555,7 +6502,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J86" s="4" t="n">
+      <c r="J86" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K86" s="4" t="inlineStr"/>
@@ -6624,7 +6571,7 @@
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr"/>
-      <c r="J87" s="4" t="n">
+      <c r="J87" s="7" t="n">
         <v>30</v>
       </c>
       <c r="K87" s="4" t="inlineStr">
@@ -6637,7 +6584,7 @@
           <t>2014-01-01</t>
         </is>
       </c>
-      <c r="M87" s="4" t="n">
+      <c r="M87" s="8" t="n">
         <v>0.026536</v>
       </c>
       <c r="N87" s="4" t="inlineStr">
@@ -6707,7 +6654,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J88" s="4" t="n">
+      <c r="J88" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K88" s="4" t="inlineStr"/>
@@ -6780,7 +6727,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J89" s="4" t="n">
+      <c r="J89" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K89" s="4" t="inlineStr"/>
@@ -6853,7 +6800,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J90" s="4" t="n">
+      <c r="J90" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K90" s="4" t="inlineStr"/>
@@ -6926,7 +6873,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J91" s="4" t="n">
+      <c r="J91" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K91" s="4" t="inlineStr"/>
@@ -6995,7 +6942,7 @@
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr"/>
-      <c r="J92" s="4" t="n">
+      <c r="J92" s="7" t="n">
         <v>22</v>
       </c>
       <c r="K92" s="4" t="inlineStr">
@@ -7008,7 +6955,7 @@
           <t>2021-01-01</t>
         </is>
       </c>
-      <c r="M92" s="4" t="n">
+      <c r="M92" s="8" t="n">
         <v>12.70259</v>
       </c>
       <c r="N92" s="4" t="inlineStr">
@@ -7078,7 +7025,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J93" s="4" t="n">
+      <c r="J93" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K93" s="4" t="inlineStr"/>
@@ -7151,7 +7098,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J94" s="4" t="n">
+      <c r="J94" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K94" s="4" t="inlineStr"/>
@@ -7224,7 +7171,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J95" s="4" t="n">
+      <c r="J95" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K95" s="4" t="inlineStr"/>
@@ -7297,7 +7244,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J96" s="4" t="n">
+      <c r="J96" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K96" s="4" t="inlineStr"/>
@@ -7370,7 +7317,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J97" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K97" s="4" t="inlineStr"/>
@@ -7443,7 +7390,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J98" s="4" t="n">
+      <c r="J98" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K98" s="4" t="inlineStr"/>
@@ -7512,7 +7459,7 @@
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr"/>
-      <c r="J99" s="4" t="n">
+      <c r="J99" s="7" t="n">
         <v>4</v>
       </c>
       <c r="K99" s="4" t="inlineStr">
@@ -7525,7 +7472,7 @@
           <t>2021-01-01</t>
         </is>
       </c>
-      <c r="M99" s="4" t="n">
+      <c r="M99" s="8" t="n">
         <v>60.53188000000001</v>
       </c>
       <c r="N99" s="4" t="inlineStr">
@@ -7595,7 +7542,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J100" s="4" t="n">
+      <c r="J100" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K100" s="4" t="inlineStr"/>
@@ -7668,7 +7615,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J101" s="4" t="n">
+      <c r="J101" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K101" s="4" t="inlineStr"/>
@@ -7733,7 +7680,7 @@
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr"/>
-      <c r="J102" s="4" t="n">
+      <c r="J102" s="7" t="n">
         <v>6643</v>
       </c>
       <c r="K102" s="4" t="inlineStr">
@@ -7746,7 +7693,7 @@
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="M102" s="4" t="n">
+      <c r="M102" s="8" t="n">
         <v>707.9193</v>
       </c>
       <c r="N102" s="4" t="inlineStr">
@@ -7812,7 +7759,7 @@
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr"/>
-      <c r="J103" s="4" t="n">
+      <c r="J103" s="7" t="n">
         <v>74</v>
       </c>
       <c r="K103" s="4" t="inlineStr">
@@ -7825,7 +7772,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M103" s="4" t="n">
+      <c r="M103" s="8" t="n">
         <v>15.3156814575195</v>
       </c>
       <c r="N103" s="4" t="inlineStr">
@@ -7891,7 +7838,7 @@
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr"/>
-      <c r="J104" s="4" t="n">
+      <c r="J104" s="7" t="n">
         <v>497</v>
       </c>
       <c r="K104" s="4" t="inlineStr">
@@ -7904,7 +7851,7 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="M104" s="4" t="n">
+      <c r="M104" s="8" t="n">
         <v>497.812779</v>
       </c>
       <c r="N104" s="4" t="inlineStr">
@@ -7974,7 +7921,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J105" s="4" t="n">
+      <c r="J105" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K105" s="4" t="inlineStr"/>
@@ -8047,7 +7994,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J106" s="4" t="n">
+      <c r="J106" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K106" s="4" t="inlineStr"/>
@@ -8120,7 +8067,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J107" s="4" t="n">
+      <c r="J107" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K107" s="4" t="inlineStr"/>
@@ -8193,7 +8140,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J108" s="4" t="n">
+      <c r="J108" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K108" s="4" t="inlineStr"/>
@@ -8266,7 +8213,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J109" s="4" t="n">
+      <c r="J109" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K109" s="4" t="inlineStr"/>
@@ -8339,7 +8286,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J110" s="4" t="n">
+      <c r="J110" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K110" s="4" t="inlineStr"/>
@@ -8412,7 +8359,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J111" s="4" t="n">
+      <c r="J111" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K111" s="4" t="inlineStr"/>
@@ -8485,7 +8432,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J112" s="4" t="n">
+      <c r="J112" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K112" s="4" t="inlineStr"/>
@@ -8558,7 +8505,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J113" s="4" t="n">
+      <c r="J113" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K113" s="4" t="inlineStr"/>
@@ -8631,7 +8578,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J114" s="4" t="n">
+      <c r="J114" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K114" s="4" t="inlineStr"/>
@@ -8704,7 +8651,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J115" s="4" t="n">
+      <c r="J115" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K115" s="4" t="inlineStr"/>
@@ -8777,7 +8724,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J116" s="4" t="n">
+      <c r="J116" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K116" s="4" t="inlineStr"/>
@@ -8850,7 +8797,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J117" s="4" t="n">
+      <c r="J117" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K117" s="4" t="inlineStr"/>
@@ -8923,7 +8870,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J118" s="4" t="n">
+      <c r="J118" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K118" s="4" t="inlineStr"/>
@@ -8996,7 +8943,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J119" s="4" t="n">
+      <c r="J119" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K119" s="4" t="inlineStr"/>
@@ -9069,7 +9016,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J120" s="4" t="n">
+      <c r="J120" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K120" s="4" t="inlineStr"/>
@@ -9142,7 +9089,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J121" s="4" t="n">
+      <c r="J121" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K121" s="4" t="inlineStr"/>
@@ -9215,7 +9162,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J122" s="4" t="n">
+      <c r="J122" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K122" s="4" t="inlineStr"/>
@@ -9288,7 +9235,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J123" s="4" t="n">
+      <c r="J123" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K123" s="4" t="inlineStr"/>
@@ -9361,7 +9308,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J124" s="4" t="n">
+      <c r="J124" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K124" s="4" t="inlineStr"/>
@@ -9430,7 +9377,7 @@
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr"/>
-      <c r="J125" s="4" t="n">
+      <c r="J125" s="7" t="n">
         <v>280</v>
       </c>
       <c r="K125" s="4" t="inlineStr">
@@ -9443,7 +9390,7 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="M125" s="4" t="n">
+      <c r="M125" s="7" t="n">
         <v>672</v>
       </c>
       <c r="N125" s="4" t="inlineStr">
@@ -9509,7 +9456,7 @@
         </is>
       </c>
       <c r="I126" s="4" t="inlineStr"/>
-      <c r="J126" s="4" t="n">
+      <c r="J126" s="7" t="n">
         <v>8</v>
       </c>
       <c r="K126" s="4" t="inlineStr">
@@ -9522,7 +9469,7 @@
           <t>2016-01-01</t>
         </is>
       </c>
-      <c r="M126" s="4" t="n">
+      <c r="M126" s="8" t="n">
         <v>254.948534781816</v>
       </c>
       <c r="N126" s="4" t="inlineStr">
@@ -9588,7 +9535,7 @@
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr"/>
-      <c r="J127" s="4" t="n">
+      <c r="J127" s="7" t="n">
         <v>61</v>
       </c>
       <c r="K127" s="4" t="inlineStr">
@@ -9601,7 +9548,7 @@
           <t>2010-01-01</t>
         </is>
       </c>
-      <c r="M127" s="4" t="n">
+      <c r="M127" s="8" t="n">
         <v>2.585625</v>
       </c>
       <c r="N127" s="4" t="inlineStr">
@@ -9671,7 +9618,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J128" s="4" t="n">
+      <c r="J128" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K128" s="4" t="inlineStr"/>
@@ -9744,7 +9691,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J129" s="4" t="n">
+      <c r="J129" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K129" s="4" t="inlineStr"/>
@@ -9813,7 +9760,7 @@
         </is>
       </c>
       <c r="I130" s="4" t="inlineStr"/>
-      <c r="J130" s="4" t="n">
+      <c r="J130" s="7" t="n">
         <v>51</v>
       </c>
       <c r="K130" s="4" t="inlineStr">
@@ -9826,7 +9773,7 @@
           <t>2010-01-01</t>
         </is>
       </c>
-      <c r="M130" s="4" t="n">
+      <c r="M130" s="8" t="n">
         <v>98.88050698000001</v>
       </c>
       <c r="N130" s="4" t="inlineStr">
@@ -9892,7 +9839,7 @@
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr"/>
-      <c r="J131" s="4" t="n">
+      <c r="J131" s="7" t="n">
         <v>74</v>
       </c>
       <c r="K131" s="4" t="inlineStr">
@@ -9905,7 +9852,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M131" s="4" t="n">
+      <c r="M131" s="8" t="n">
         <v>3.09922003746033</v>
       </c>
       <c r="N131" s="4" t="inlineStr">
@@ -9975,7 +9922,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J132" s="4" t="n">
+      <c r="J132" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K132" s="4" t="inlineStr"/>
@@ -10048,7 +9995,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J133" s="4" t="n">
+      <c r="J133" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K133" s="4" t="inlineStr"/>
@@ -10121,7 +10068,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J134" s="4" t="n">
+      <c r="J134" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K134" s="4" t="inlineStr"/>
@@ -10194,7 +10141,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J135" s="4" t="n">
+      <c r="J135" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K135" s="4" t="inlineStr"/>
@@ -10267,7 +10214,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J136" s="4" t="n">
+      <c r="J136" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K136" s="4" t="inlineStr"/>
@@ -10340,7 +10287,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J137" s="4" t="n">
+      <c r="J137" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K137" s="4" t="inlineStr"/>
@@ -10413,7 +10360,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J138" s="4" t="n">
+      <c r="J138" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K138" s="4" t="inlineStr"/>
@@ -10486,7 +10433,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J139" s="4" t="n">
+      <c r="J139" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K139" s="4" t="inlineStr"/>
@@ -10559,7 +10506,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J140" s="4" t="n">
+      <c r="J140" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K140" s="4" t="inlineStr"/>
@@ -10632,7 +10579,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J141" s="4" t="n">
+      <c r="J141" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K141" s="4" t="inlineStr"/>
@@ -10705,7 +10652,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J142" s="4" t="n">
+      <c r="J142" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K142" s="4" t="inlineStr"/>
@@ -10774,7 +10721,7 @@
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr"/>
-      <c r="J143" s="4" t="n">
+      <c r="J143" s="7" t="n">
         <v>214</v>
       </c>
       <c r="K143" s="4" t="inlineStr">
@@ -10787,7 +10734,7 @@
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="M143" s="4" t="n">
+      <c r="M143" s="7" t="n">
         <v>3000</v>
       </c>
       <c r="N143" s="4" t="inlineStr">
@@ -10857,7 +10804,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J144" s="4" t="n">
+      <c r="J144" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K144" s="4" t="inlineStr"/>
@@ -10930,7 +10877,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J145" s="4" t="n">
+      <c r="J145" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K145" s="4" t="inlineStr"/>
@@ -11003,7 +10950,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J146" s="4" t="n">
+      <c r="J146" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K146" s="4" t="inlineStr"/>
@@ -11076,7 +11023,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J147" s="4" t="n">
+      <c r="J147" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K147" s="4" t="inlineStr"/>
@@ -11149,7 +11096,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J148" s="4" t="n">
+      <c r="J148" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K148" s="4" t="inlineStr"/>
@@ -11218,7 +11165,7 @@
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr"/>
-      <c r="J149" s="4" t="n">
+      <c r="J149" s="7" t="n">
         <v>214</v>
       </c>
       <c r="K149" s="4" t="inlineStr">
@@ -11231,7 +11178,7 @@
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="M149" s="4" t="n">
+      <c r="M149" s="7" t="n">
         <v>3000</v>
       </c>
       <c r="N149" s="4" t="inlineStr">
@@ -11301,7 +11248,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J150" s="4" t="n">
+      <c r="J150" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K150" s="4" t="inlineStr"/>
@@ -11374,7 +11321,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J151" s="4" t="n">
+      <c r="J151" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K151" s="4" t="inlineStr"/>
@@ -11443,7 +11390,7 @@
         </is>
       </c>
       <c r="I152" s="4" t="inlineStr"/>
-      <c r="J152" s="4" t="n">
+      <c r="J152" s="7" t="n">
         <v>146</v>
       </c>
       <c r="K152" s="4" t="inlineStr">
@@ -11456,7 +11403,7 @@
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="M152" s="4" t="n">
+      <c r="M152" s="7" t="n">
         <v>2397</v>
       </c>
       <c r="N152" s="4" t="inlineStr">
@@ -11526,7 +11473,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J153" s="4" t="n">
+      <c r="J153" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K153" s="4" t="inlineStr"/>
@@ -11599,7 +11546,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J154" s="4" t="n">
+      <c r="J154" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K154" s="4" t="inlineStr"/>
@@ -11668,7 +11615,7 @@
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr"/>
-      <c r="J155" s="4" t="n">
+      <c r="J155" s="7" t="n">
         <v>214</v>
       </c>
       <c r="K155" s="4" t="inlineStr">
@@ -11681,7 +11628,7 @@
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="M155" s="4" t="n">
+      <c r="M155" s="7" t="n">
         <v>23802</v>
       </c>
       <c r="N155" s="4" t="inlineStr">
@@ -11751,7 +11698,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J156" s="4" t="n">
+      <c r="J156" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K156" s="4" t="inlineStr"/>
@@ -11824,7 +11771,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J157" s="4" t="n">
+      <c r="J157" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K157" s="4" t="inlineStr"/>
@@ -11893,7 +11840,7 @@
         </is>
       </c>
       <c r="I158" s="4" t="inlineStr"/>
-      <c r="J158" s="4" t="n">
+      <c r="J158" s="7" t="n">
         <v>109</v>
       </c>
       <c r="K158" s="4" t="inlineStr">
@@ -11906,7 +11853,7 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="M158" s="4" t="n">
+      <c r="M158" s="7" t="n">
         <v>-1600</v>
       </c>
       <c r="N158" s="4" t="inlineStr">
@@ -11976,7 +11923,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J159" s="4" t="n">
+      <c r="J159" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K159" s="4" t="inlineStr"/>
@@ -12049,7 +11996,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J160" s="4" t="n">
+      <c r="J160" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K160" s="4" t="inlineStr"/>
@@ -12122,7 +12069,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J161" s="4" t="n">
+      <c r="J161" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K161" s="4" t="inlineStr"/>
@@ -12195,7 +12142,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J162" s="4" t="n">
+      <c r="J162" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K162" s="4" t="inlineStr"/>
@@ -12268,7 +12215,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J163" s="4" t="n">
+      <c r="J163" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K163" s="4" t="inlineStr"/>
@@ -12341,7 +12288,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J164" s="4" t="n">
+      <c r="J164" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K164" s="4" t="inlineStr"/>
@@ -12414,7 +12361,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J165" s="4" t="n">
+      <c r="J165" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K165" s="4" t="inlineStr"/>
@@ -12483,7 +12430,7 @@
         </is>
       </c>
       <c r="I166" s="4" t="inlineStr"/>
-      <c r="J166" s="4" t="n">
+      <c r="J166" s="7" t="n">
         <v>37</v>
       </c>
       <c r="K166" s="4" t="inlineStr">
@@ -12496,7 +12443,7 @@
           <t>2014-10-01</t>
         </is>
       </c>
-      <c r="M166" s="4" t="n">
+      <c r="M166" s="8" t="n">
         <v>-1.3</v>
       </c>
       <c r="N166" s="4" t="inlineStr">
@@ -12566,7 +12513,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J167" s="4" t="n">
+      <c r="J167" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K167" s="4" t="inlineStr"/>
@@ -12639,7 +12586,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J168" s="4" t="n">
+      <c r="J168" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K168" s="4" t="inlineStr"/>
@@ -12712,7 +12659,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J169" s="4" t="n">
+      <c r="J169" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K169" s="4" t="inlineStr"/>
@@ -12785,7 +12732,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J170" s="4" t="n">
+      <c r="J170" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K170" s="4" t="inlineStr"/>
@@ -12858,7 +12805,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J171" s="4" t="n">
+      <c r="J171" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K171" s="4" t="inlineStr"/>
@@ -12931,7 +12878,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J172" s="4" t="n">
+      <c r="J172" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K172" s="4" t="inlineStr"/>
@@ -13004,7 +12951,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J173" s="4" t="n">
+      <c r="J173" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K173" s="4" t="inlineStr"/>
@@ -13077,7 +13024,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J174" s="4" t="n">
+      <c r="J174" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K174" s="4" t="inlineStr"/>
@@ -13150,7 +13097,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J175" s="4" t="n">
+      <c r="J175" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K175" s="4" t="inlineStr"/>
@@ -13223,7 +13170,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J176" s="4" t="n">
+      <c r="J176" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K176" s="4" t="inlineStr"/>
@@ -13296,7 +13243,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J177" s="4" t="n">
+      <c r="J177" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K177" s="4" t="inlineStr"/>
@@ -13369,7 +13316,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J178" s="4" t="n">
+      <c r="J178" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K178" s="4" t="inlineStr"/>
@@ -13442,7 +13389,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J179" s="4" t="n">
+      <c r="J179" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K179" s="4" t="inlineStr"/>
@@ -13515,7 +13462,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J180" s="4" t="n">
+      <c r="J180" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K180" s="4" t="inlineStr"/>
@@ -13584,7 +13531,7 @@
         </is>
       </c>
       <c r="I181" s="4" t="inlineStr"/>
-      <c r="J181" s="4" t="n">
+      <c r="J181" s="7" t="n">
         <v>497</v>
       </c>
       <c r="K181" s="4" t="inlineStr">
@@ -13597,7 +13544,7 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="M181" s="4" t="n">
+      <c r="M181" s="8" t="n">
         <v>1525.18625</v>
       </c>
       <c r="N181" s="4" t="inlineStr">
@@ -13667,7 +13614,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J182" s="4" t="n">
+      <c r="J182" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K182" s="4" t="inlineStr"/>
@@ -13740,7 +13687,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J183" s="4" t="n">
+      <c r="J183" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K183" s="4" t="inlineStr"/>
@@ -13809,7 +13756,7 @@
         </is>
       </c>
       <c r="I184" s="4" t="inlineStr"/>
-      <c r="J184" s="4" t="n">
+      <c r="J184" s="7" t="n">
         <v>53</v>
       </c>
       <c r="K184" s="4" t="inlineStr">
@@ -13822,7 +13769,7 @@
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="M184" s="4" t="n">
+      <c r="M184" s="8" t="n">
         <v>71.00759172250289</v>
       </c>
       <c r="N184" s="4" t="inlineStr">
@@ -13892,7 +13839,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J185" s="4" t="n">
+      <c r="J185" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K185" s="4" t="inlineStr"/>
@@ -13961,7 +13908,7 @@
         </is>
       </c>
       <c r="I186" s="4" t="inlineStr"/>
-      <c r="J186" s="4" t="n">
+      <c r="J186" s="7" t="n">
         <v>32</v>
       </c>
       <c r="K186" s="4" t="inlineStr">
@@ -13974,7 +13921,7 @@
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="M186" s="4" t="n">
+      <c r="M186" s="8" t="n">
         <v>76.67890167</v>
       </c>
       <c r="N186" s="4" t="inlineStr">
@@ -14044,7 +13991,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J187" s="4" t="n">
+      <c r="J187" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K187" s="4" t="inlineStr"/>
@@ -14117,7 +14064,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J188" s="4" t="n">
+      <c r="J188" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K188" s="4" t="inlineStr"/>
@@ -14190,7 +14137,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J189" s="4" t="n">
+      <c r="J189" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K189" s="4" t="inlineStr"/>
@@ -14263,7 +14210,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J190" s="4" t="n">
+      <c r="J190" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K190" s="4" t="inlineStr"/>
@@ -14336,7 +14283,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J191" s="4" t="n">
+      <c r="J191" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K191" s="4" t="inlineStr"/>
@@ -14409,7 +14356,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J192" s="4" t="n">
+      <c r="J192" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K192" s="4" t="inlineStr"/>
@@ -14482,7 +14429,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J193" s="4" t="n">
+      <c r="J193" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K193" s="4" t="inlineStr"/>
@@ -14551,7 +14498,7 @@
         </is>
       </c>
       <c r="I194" s="4" t="inlineStr"/>
-      <c r="J194" s="4" t="n">
+      <c r="J194" s="7" t="n">
         <v>74</v>
       </c>
       <c r="K194" s="4" t="inlineStr">
@@ -14564,7 +14511,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M194" s="4" t="n">
+      <c r="M194" s="8" t="n">
         <v>0.08436375111341481</v>
       </c>
       <c r="N194" s="4" t="inlineStr">
@@ -14634,7 +14581,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J195" s="4" t="n">
+      <c r="J195" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K195" s="4" t="inlineStr"/>
@@ -14707,7 +14654,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J196" s="4" t="n">
+      <c r="J196" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K196" s="4" t="inlineStr"/>
@@ -14780,7 +14727,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J197" s="4" t="n">
+      <c r="J197" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K197" s="4" t="inlineStr"/>
@@ -14853,7 +14800,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J198" s="4" t="n">
+      <c r="J198" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K198" s="4" t="inlineStr"/>
@@ -14926,7 +14873,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J199" s="4" t="n">
+      <c r="J199" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K199" s="4" t="inlineStr"/>
@@ -14999,7 +14946,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J200" s="4" t="n">
+      <c r="J200" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K200" s="4" t="inlineStr"/>
@@ -15072,7 +15019,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J201" s="4" t="n">
+      <c r="J201" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K201" s="4" t="inlineStr"/>
@@ -15145,7 +15092,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J202" s="4" t="n">
+      <c r="J202" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K202" s="4" t="inlineStr"/>
@@ -15218,7 +15165,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J203" s="4" t="n">
+      <c r="J203" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K203" s="4" t="inlineStr"/>
@@ -15291,7 +15238,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J204" s="4" t="n">
+      <c r="J204" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K204" s="4" t="inlineStr"/>
@@ -15360,7 +15307,7 @@
         </is>
       </c>
       <c r="I205" s="4" t="inlineStr"/>
-      <c r="J205" s="4" t="n">
+      <c r="J205" s="7" t="n">
         <v>66</v>
       </c>
       <c r="K205" s="4" t="inlineStr">
@@ -15373,7 +15320,7 @@
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="M205" s="4" t="n">
+      <c r="M205" s="8" t="n">
         <v>99661244155.6306</v>
       </c>
       <c r="N205" s="4" t="inlineStr">
@@ -15439,7 +15386,7 @@
         </is>
       </c>
       <c r="I206" s="4" t="inlineStr"/>
-      <c r="J206" s="4" t="n">
+      <c r="J206" s="7" t="n">
         <v>66</v>
       </c>
       <c r="K206" s="4" t="inlineStr">
@@ -15452,7 +15399,7 @@
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="M206" s="4" t="n">
+      <c r="M206" s="8" t="n">
         <v>98061244155.6306</v>
       </c>
       <c r="N206" s="4" t="inlineStr">
@@ -15522,7 +15469,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J207" s="4" t="n">
+      <c r="J207" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K207" s="4" t="inlineStr"/>
@@ -15595,7 +15542,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J208" s="4" t="n">
+      <c r="J208" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K208" s="4" t="inlineStr"/>
@@ -15668,7 +15615,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J209" s="4" t="n">
+      <c r="J209" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K209" s="4" t="inlineStr"/>
@@ -15741,7 +15688,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J210" s="4" t="n">
+      <c r="J210" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K210" s="4" t="inlineStr"/>
@@ -15814,7 +15761,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J211" s="4" t="n">
+      <c r="J211" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K211" s="4" t="inlineStr"/>
@@ -15887,7 +15834,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J212" s="4" t="n">
+      <c r="J212" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K212" s="4" t="inlineStr"/>
@@ -15960,7 +15907,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J213" s="4" t="n">
+      <c r="J213" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K213" s="4" t="inlineStr"/>
@@ -16033,7 +15980,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J214" s="4" t="n">
+      <c r="J214" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K214" s="4" t="inlineStr"/>
@@ -16102,7 +16049,7 @@
         </is>
       </c>
       <c r="I215" s="4" t="inlineStr"/>
-      <c r="J215" s="4" t="n">
+      <c r="J215" s="7" t="n">
         <v>302</v>
       </c>
       <c r="K215" s="4" t="inlineStr">
@@ -16115,7 +16062,7 @@
           <t>2019-02-01</t>
         </is>
       </c>
-      <c r="M215" s="4" t="n">
+      <c r="M215" s="7" t="n">
         <v>0</v>
       </c>
       <c r="N215" s="4" t="inlineStr">
@@ -16185,7 +16132,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J216" s="4" t="n">
+      <c r="J216" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K216" s="4" t="inlineStr"/>
@@ -16258,7 +16205,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J217" s="4" t="n">
+      <c r="J217" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K217" s="4" t="inlineStr"/>
@@ -16331,7 +16278,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J218" s="4" t="n">
+      <c r="J218" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K218" s="4" t="inlineStr"/>
@@ -16404,7 +16351,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J219" s="4" t="n">
+      <c r="J219" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K219" s="4" t="inlineStr"/>
@@ -16477,7 +16424,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J220" s="4" t="n">
+      <c r="J220" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K220" s="4" t="inlineStr"/>
@@ -16550,7 +16497,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J221" s="4" t="n">
+      <c r="J221" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K221" s="4" t="inlineStr"/>
@@ -16623,7 +16570,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J222" s="4" t="n">
+      <c r="J222" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K222" s="4" t="inlineStr"/>
@@ -16696,7 +16643,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J223" s="4" t="n">
+      <c r="J223" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K223" s="4" t="inlineStr"/>
@@ -16769,7 +16716,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J224" s="4" t="n">
+      <c r="J224" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K224" s="4" t="inlineStr"/>
@@ -16842,7 +16789,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J225" s="4" t="n">
+      <c r="J225" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K225" s="4" t="inlineStr"/>
@@ -16915,7 +16862,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J226" s="4" t="n">
+      <c r="J226" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K226" s="4" t="inlineStr"/>
@@ -16988,7 +16935,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J227" s="4" t="n">
+      <c r="J227" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K227" s="4" t="inlineStr"/>
@@ -17061,7 +17008,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J228" s="4" t="n">
+      <c r="J228" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K228" s="4" t="inlineStr"/>
@@ -17134,7 +17081,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J229" s="4" t="n">
+      <c r="J229" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K229" s="4" t="inlineStr"/>
@@ -17203,7 +17150,7 @@
         </is>
       </c>
       <c r="I230" s="4" t="inlineStr"/>
-      <c r="J230" s="4" t="n">
+      <c r="J230" s="7" t="n">
         <v>55</v>
       </c>
       <c r="K230" s="4" t="inlineStr">
@@ -17216,7 +17163,7 @@
           <t>2014-01-01</t>
         </is>
       </c>
-      <c r="M230" s="4" t="n">
+      <c r="M230" s="8" t="n">
         <v>14026.3664129191</v>
       </c>
       <c r="N230" s="4" t="inlineStr">
@@ -17286,7 +17233,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J231" s="4" t="n">
+      <c r="J231" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K231" s="4" t="inlineStr"/>
@@ -17359,7 +17306,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J232" s="4" t="n">
+      <c r="J232" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K232" s="4" t="inlineStr"/>
@@ -17432,7 +17379,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J233" s="4" t="n">
+      <c r="J233" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K233" s="4" t="inlineStr"/>
@@ -17505,7 +17452,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J234" s="4" t="n">
+      <c r="J234" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K234" s="4" t="inlineStr"/>
@@ -17578,7 +17525,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J235" s="4" t="n">
+      <c r="J235" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K235" s="4" t="inlineStr"/>
@@ -17651,7 +17598,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J236" s="4" t="n">
+      <c r="J236" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K236" s="4" t="inlineStr"/>
@@ -17724,7 +17671,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J237" s="4" t="n">
+      <c r="J237" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K237" s="4" t="inlineStr"/>
@@ -17797,7 +17744,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J238" s="4" t="n">
+      <c r="J238" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K238" s="4" t="inlineStr"/>
@@ -17870,7 +17817,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J239" s="4" t="n">
+      <c r="J239" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K239" s="4" t="inlineStr"/>
@@ -17943,7 +17890,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J240" s="4" t="n">
+      <c r="J240" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K240" s="4" t="inlineStr"/>
@@ -18016,7 +17963,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J241" s="4" t="n">
+      <c r="J241" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K241" s="4" t="inlineStr"/>
@@ -18089,7 +18036,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J242" s="4" t="n">
+      <c r="J242" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K242" s="4" t="inlineStr"/>
@@ -18162,7 +18109,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J243" s="4" t="n">
+      <c r="J243" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K243" s="4" t="inlineStr"/>
@@ -18235,7 +18182,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J244" s="4" t="n">
+      <c r="J244" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K244" s="4" t="inlineStr"/>
@@ -18308,7 +18255,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J245" s="4" t="n">
+      <c r="J245" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K245" s="4" t="inlineStr"/>
@@ -18381,7 +18328,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J246" s="4" t="n">
+      <c r="J246" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K246" s="4" t="inlineStr"/>
@@ -18454,7 +18401,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J247" s="4" t="n">
+      <c r="J247" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K247" s="4" t="inlineStr"/>
@@ -18523,7 +18470,7 @@
         </is>
       </c>
       <c r="I248" s="4" t="inlineStr"/>
-      <c r="J248" s="4" t="n">
+      <c r="J248" s="7" t="n">
         <v>61</v>
       </c>
       <c r="K248" s="4" t="inlineStr">
@@ -18536,7 +18483,7 @@
           <t>2010-01-01</t>
         </is>
       </c>
-      <c r="M248" s="4" t="n">
+      <c r="M248" s="8" t="n">
         <v>11809.94057</v>
       </c>
       <c r="N248" s="4" t="inlineStr">
@@ -18602,7 +18549,7 @@
         </is>
       </c>
       <c r="I249" s="4" t="inlineStr"/>
-      <c r="J249" s="4" t="n">
+      <c r="J249" s="7" t="n">
         <v>66</v>
       </c>
       <c r="K249" s="4" t="inlineStr">
@@ -18615,7 +18562,7 @@
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="M249" s="4" t="n">
+      <c r="M249" s="8" t="n">
         <v>3494.8138870244</v>
       </c>
       <c r="N249" s="4" t="inlineStr">
@@ -18685,7 +18632,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J250" s="4" t="n">
+      <c r="J250" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K250" s="4" t="inlineStr"/>
@@ -18758,7 +18705,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J251" s="4" t="n">
+      <c r="J251" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K251" s="4" t="inlineStr"/>
@@ -18827,7 +18774,7 @@
         </is>
       </c>
       <c r="I252" s="4" t="inlineStr"/>
-      <c r="J252" s="4" t="n">
+      <c r="J252" s="7" t="n">
         <v>61</v>
       </c>
       <c r="K252" s="4" t="inlineStr">
@@ -18840,7 +18787,7 @@
           <t>2010-01-01</t>
         </is>
       </c>
-      <c r="M252" s="4" t="n">
+      <c r="M252" s="8" t="n">
         <v>25.29171848</v>
       </c>
       <c r="N252" s="4" t="inlineStr">
@@ -18906,7 +18853,7 @@
         </is>
       </c>
       <c r="I253" s="4" t="inlineStr"/>
-      <c r="J253" s="4" t="n">
+      <c r="J253" s="7" t="n">
         <v>61</v>
       </c>
       <c r="K253" s="4" t="inlineStr">
@@ -18919,7 +18866,7 @@
           <t>2010-01-01</t>
         </is>
       </c>
-      <c r="M253" s="4" t="n">
+      <c r="M253" s="8" t="n">
         <v>121.3461635</v>
       </c>
       <c r="N253" s="4" t="inlineStr">
@@ -18985,7 +18932,7 @@
         </is>
       </c>
       <c r="I254" s="4" t="inlineStr"/>
-      <c r="J254" s="4" t="n">
+      <c r="J254" s="7" t="n">
         <v>74</v>
       </c>
       <c r="K254" s="4" t="inlineStr">
@@ -18998,7 +18945,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M254" s="4" t="n">
+      <c r="M254" s="8" t="n">
         <v>65.5449341102796</v>
       </c>
       <c r="N254" s="4" t="inlineStr">
@@ -19064,7 +19011,7 @@
         </is>
       </c>
       <c r="I255" s="4" t="inlineStr"/>
-      <c r="J255" s="4" t="n">
+      <c r="J255" s="7" t="n">
         <v>74</v>
       </c>
       <c r="K255" s="4" t="inlineStr">
@@ -19077,7 +19024,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M255" s="4" t="n">
+      <c r="M255" s="8" t="n">
         <v>23.2163643183614</v>
       </c>
       <c r="N255" s="4" t="inlineStr">
@@ -19147,7 +19094,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J256" s="4" t="n">
+      <c r="J256" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K256" s="4" t="inlineStr"/>
@@ -19220,7 +19167,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J257" s="4" t="n">
+      <c r="J257" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K257" s="4" t="inlineStr"/>
@@ -19293,7 +19240,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J258" s="4" t="n">
+      <c r="J258" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K258" s="4" t="inlineStr"/>
@@ -19362,7 +19309,7 @@
         </is>
       </c>
       <c r="I259" s="4" t="inlineStr"/>
-      <c r="J259" s="4" t="n">
+      <c r="J259" s="7" t="n">
         <v>70</v>
       </c>
       <c r="K259" s="4" t="inlineStr">
@@ -19375,7 +19322,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M259" s="4" t="n">
+      <c r="M259" s="8" t="n">
         <v>15.1081390380859</v>
       </c>
       <c r="N259" s="4" t="inlineStr">
@@ -19445,7 +19392,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J260" s="4" t="n">
+      <c r="J260" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K260" s="4" t="inlineStr"/>
@@ -19518,7 +19465,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J261" s="4" t="n">
+      <c r="J261" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K261" s="4" t="inlineStr"/>
@@ -19591,7 +19538,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J262" s="4" t="n">
+      <c r="J262" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K262" s="4" t="inlineStr"/>
@@ -19664,7 +19611,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J263" s="4" t="n">
+      <c r="J263" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K263" s="4" t="inlineStr"/>
@@ -19733,7 +19680,7 @@
         </is>
       </c>
       <c r="I264" s="4" t="inlineStr"/>
-      <c r="J264" s="4" t="n">
+      <c r="J264" s="7" t="n">
         <v>61</v>
       </c>
       <c r="K264" s="4" t="inlineStr">
@@ -19746,7 +19693,7 @@
           <t>2010-01-01</t>
         </is>
       </c>
-      <c r="M264" s="4" t="n">
+      <c r="M264" s="8" t="n">
         <v>119.0453568</v>
       </c>
       <c r="N264" s="4" t="inlineStr">
@@ -19812,7 +19759,7 @@
         </is>
       </c>
       <c r="I265" s="4" t="inlineStr"/>
-      <c r="J265" s="4" t="n">
+      <c r="J265" s="7" t="n">
         <v>74</v>
       </c>
       <c r="K265" s="4" t="inlineStr">
@@ -19825,7 +19772,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M265" s="4" t="n">
+      <c r="M265" s="8" t="n">
         <v>0.206251129508019</v>
       </c>
       <c r="N265" s="4" t="inlineStr">
@@ -19887,7 +19834,7 @@
         </is>
       </c>
       <c r="I266" s="4" t="inlineStr"/>
-      <c r="J266" s="4" t="n">
+      <c r="J266" s="7" t="n">
         <v>66</v>
       </c>
       <c r="K266" s="4" t="inlineStr">
@@ -19900,7 +19847,7 @@
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="M266" s="4" t="n">
+      <c r="M266" s="7" t="n">
         <v>28516896</v>
       </c>
       <c r="N266" s="4" t="inlineStr">
@@ -19966,7 +19913,7 @@
         </is>
       </c>
       <c r="I267" s="4" t="inlineStr"/>
-      <c r="J267" s="4" t="n">
+      <c r="J267" s="7" t="n">
         <v>74</v>
       </c>
       <c r="K267" s="4" t="inlineStr">
@@ -19979,7 +19926,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M267" s="4" t="n">
+      <c r="M267" s="8" t="n">
         <v>28.300854</v>
       </c>
       <c r="N267" s="4" t="inlineStr">
@@ -20045,7 +19992,7 @@
         </is>
       </c>
       <c r="I268" s="4" t="inlineStr"/>
-      <c r="J268" s="4" t="n">
+      <c r="J268" s="7" t="n">
         <v>61</v>
       </c>
       <c r="K268" s="4" t="inlineStr">
@@ -20058,7 +20005,7 @@
           <t>2010-01-01</t>
         </is>
       </c>
-      <c r="M268" s="4" t="n">
+      <c r="M268" s="8" t="n">
         <v>27223.228</v>
       </c>
       <c r="N268" s="4" t="inlineStr">
@@ -20124,7 +20071,7 @@
         </is>
       </c>
       <c r="I269" s="4" t="inlineStr"/>
-      <c r="J269" s="4" t="n">
+      <c r="J269" s="7" t="n">
         <v>61</v>
       </c>
       <c r="K269" s="4" t="inlineStr">
@@ -20137,7 +20084,7 @@
           <t>2010-01-01</t>
         </is>
       </c>
-      <c r="M269" s="4" t="n">
+      <c r="M269" s="8" t="n">
         <v>11777.99098</v>
       </c>
       <c r="N269" s="4" t="inlineStr">
@@ -20207,7 +20154,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J270" s="4" t="n">
+      <c r="J270" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K270" s="4" t="inlineStr"/>
@@ -20276,7 +20223,7 @@
         </is>
       </c>
       <c r="I271" s="4" t="inlineStr"/>
-      <c r="J271" s="4" t="n">
+      <c r="J271" s="7" t="n">
         <v>61</v>
       </c>
       <c r="K271" s="4" t="inlineStr">
@@ -20289,7 +20236,7 @@
           <t>2010-01-01</t>
         </is>
       </c>
-      <c r="M271" s="4" t="n">
+      <c r="M271" s="8" t="n">
         <v>3.155532204</v>
       </c>
       <c r="N271" s="4" t="inlineStr">
@@ -20355,7 +20302,7 @@
         </is>
       </c>
       <c r="I272" s="4" t="inlineStr"/>
-      <c r="J272" s="4" t="n">
+      <c r="J272" s="7" t="n">
         <v>21</v>
       </c>
       <c r="K272" s="4" t="inlineStr">
@@ -20368,7 +20315,7 @@
           <t>2022-01-01</t>
         </is>
       </c>
-      <c r="M272" s="4" t="n">
+      <c r="M272" s="7" t="n">
         <v>4890168</v>
       </c>
       <c r="N272" s="4" t="inlineStr">
@@ -20438,7 +20385,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J273" s="4" t="n">
+      <c r="J273" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K273" s="4" t="inlineStr"/>
@@ -20507,7 +20454,7 @@
         </is>
       </c>
       <c r="I274" s="4" t="inlineStr"/>
-      <c r="J274" s="4" t="n">
+      <c r="J274" s="7" t="n">
         <v>302</v>
       </c>
       <c r="K274" s="4" t="inlineStr">
@@ -20520,7 +20467,7 @@
           <t>2019-02-01</t>
         </is>
       </c>
-      <c r="M274" s="4" t="n">
+      <c r="M274" s="8" t="n">
         <v>0.68</v>
       </c>
       <c r="N274" s="4" t="inlineStr">
@@ -20586,7 +20533,7 @@
         </is>
       </c>
       <c r="I275" s="4" t="inlineStr"/>
-      <c r="J275" s="4" t="n">
+      <c r="J275" s="7" t="n">
         <v>61</v>
       </c>
       <c r="K275" s="4" t="inlineStr">
@@ -20599,7 +20546,7 @@
           <t>2010-01-01</t>
         </is>
       </c>
-      <c r="M275" s="4" t="n">
+      <c r="M275" s="8" t="n">
         <v>9070.606092</v>
       </c>
       <c r="N275" s="4" t="inlineStr">
@@ -20669,7 +20616,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J276" s="4" t="n">
+      <c r="J276" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K276" s="4" t="inlineStr"/>
@@ -20738,7 +20685,7 @@
         </is>
       </c>
       <c r="I277" s="4" t="inlineStr"/>
-      <c r="J277" s="4" t="n">
+      <c r="J277" s="7" t="n">
         <v>74</v>
       </c>
       <c r="K277" s="4" t="inlineStr">
@@ -20751,7 +20698,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M277" s="4" t="n">
+      <c r="M277" s="8" t="n">
         <v>2528.005859375</v>
       </c>
       <c r="N277" s="4" t="inlineStr">
@@ -20817,7 +20764,7 @@
         </is>
       </c>
       <c r="I278" s="4" t="inlineStr"/>
-      <c r="J278" s="4" t="n">
+      <c r="J278" s="7" t="n">
         <v>61</v>
       </c>
       <c r="K278" s="4" t="inlineStr">
@@ -20830,7 +20777,7 @@
           <t>2010-01-01</t>
         </is>
       </c>
-      <c r="M278" s="4" t="n">
+      <c r="M278" s="8" t="n">
         <v>9061.718438</v>
       </c>
       <c r="N278" s="4" t="inlineStr">
@@ -20896,7 +20843,7 @@
         </is>
       </c>
       <c r="I279" s="4" t="inlineStr"/>
-      <c r="J279" s="4" t="n">
+      <c r="J279" s="7" t="n">
         <v>61</v>
       </c>
       <c r="K279" s="4" t="inlineStr">
@@ -20909,7 +20856,7 @@
           <t>2010-01-01</t>
         </is>
       </c>
-      <c r="M279" s="4" t="n">
+      <c r="M279" s="8" t="n">
         <v>9070.929923</v>
       </c>
       <c r="N279" s="4" t="inlineStr">
@@ -20979,7 +20926,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J280" s="4" t="n">
+      <c r="J280" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K280" s="4" t="inlineStr"/>
@@ -21048,7 +20995,7 @@
         </is>
       </c>
       <c r="I281" s="4" t="inlineStr"/>
-      <c r="J281" s="4" t="n">
+      <c r="J281" s="7" t="n">
         <v>74</v>
       </c>
       <c r="K281" s="4" t="inlineStr">
@@ -21061,7 +21008,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M281" s="4" t="n">
+      <c r="M281" s="8" t="n">
         <v>5304.27978515625</v>
       </c>
       <c r="N281" s="4" t="inlineStr">
@@ -21127,7 +21074,7 @@
         </is>
       </c>
       <c r="I282" s="4" t="inlineStr"/>
-      <c r="J282" s="4" t="n">
+      <c r="J282" s="7" t="n">
         <v>74</v>
       </c>
       <c r="K282" s="4" t="inlineStr">
@@ -21140,7 +21087,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M282" s="4" t="n">
+      <c r="M282" s="8" t="n">
         <v>4501.99462890625</v>
       </c>
       <c r="N282" s="4" t="inlineStr">
@@ -21210,7 +21157,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J283" s="4" t="n">
+      <c r="J283" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K283" s="4" t="inlineStr"/>
@@ -21283,7 +21230,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J284" s="4" t="n">
+      <c r="J284" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K284" s="4" t="inlineStr"/>
@@ -21356,7 +21303,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J285" s="4" t="n">
+      <c r="J285" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K285" s="4" t="inlineStr"/>
@@ -21429,7 +21376,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J286" s="4" t="n">
+      <c r="J286" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K286" s="4" t="inlineStr"/>
@@ -21502,7 +21449,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J287" s="4" t="n">
+      <c r="J287" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K287" s="4" t="inlineStr"/>
@@ -21575,7 +21522,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J288" s="4" t="n">
+      <c r="J288" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K288" s="4" t="inlineStr"/>
@@ -21644,7 +21591,7 @@
         </is>
       </c>
       <c r="I289" s="4" t="inlineStr"/>
-      <c r="J289" s="4" t="n">
+      <c r="J289" s="7" t="n">
         <v>74</v>
       </c>
       <c r="K289" s="4" t="inlineStr">
@@ -21657,7 +21604,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M289" s="4" t="n">
+      <c r="M289" s="8" t="n">
         <v>119927.1796875</v>
       </c>
       <c r="N289" s="4" t="inlineStr">
@@ -21723,7 +21670,7 @@
         </is>
       </c>
       <c r="I290" s="4" t="inlineStr"/>
-      <c r="J290" s="4" t="n">
+      <c r="J290" s="7" t="n">
         <v>70</v>
       </c>
       <c r="K290" s="4" t="inlineStr">
@@ -21736,7 +21683,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M290" s="4" t="n">
+      <c r="M290" s="8" t="n">
         <v>1.22892010211945</v>
       </c>
       <c r="N290" s="4" t="inlineStr">
@@ -21806,7 +21753,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J291" s="4" t="n">
+      <c r="J291" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K291" s="4" t="inlineStr"/>
@@ -21879,7 +21826,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J292" s="4" t="n">
+      <c r="J292" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K292" s="4" t="inlineStr"/>
@@ -21952,7 +21899,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J293" s="4" t="n">
+      <c r="J293" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K293" s="4" t="inlineStr"/>
@@ -22025,7 +21972,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J294" s="4" t="n">
+      <c r="J294" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K294" s="4" t="inlineStr"/>
@@ -22094,7 +22041,7 @@
         </is>
       </c>
       <c r="I295" s="4" t="inlineStr"/>
-      <c r="J295" s="4" t="n">
+      <c r="J295" s="7" t="n">
         <v>9</v>
       </c>
       <c r="K295" s="4" t="inlineStr">
@@ -22107,7 +22054,7 @@
           <t>2022-01-01</t>
         </is>
       </c>
-      <c r="M295" s="4" t="n">
+      <c r="M295" s="8" t="n">
         <v>97.59999847412109</v>
       </c>
       <c r="N295" s="4" t="inlineStr">
@@ -22177,7 +22124,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J296" s="4" t="n">
+      <c r="J296" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K296" s="4" t="inlineStr"/>
@@ -22250,7 +22197,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J297" s="4" t="n">
+      <c r="J297" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K297" s="4" t="inlineStr"/>
@@ -22323,7 +22270,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J298" s="4" t="n">
+      <c r="J298" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K298" s="4" t="inlineStr"/>
@@ -22392,7 +22339,7 @@
         </is>
       </c>
       <c r="I299" s="4" t="inlineStr"/>
-      <c r="J299" s="4" t="n">
+      <c r="J299" s="7" t="n">
         <v>13</v>
       </c>
       <c r="K299" s="4" t="inlineStr">
@@ -22405,7 +22352,7 @@
           <t>2006-01-01</t>
         </is>
       </c>
-      <c r="M299" s="4" t="n">
+      <c r="M299" s="8" t="n">
         <v>44.7</v>
       </c>
       <c r="N299" s="4" t="inlineStr">
@@ -22471,7 +22418,7 @@
         </is>
       </c>
       <c r="I300" s="4" t="inlineStr"/>
-      <c r="J300" s="4" t="n">
+      <c r="J300" s="7" t="n">
         <v>35</v>
       </c>
       <c r="K300" s="4" t="inlineStr">
@@ -22484,7 +22431,7 @@
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="M300" s="4" t="n">
+      <c r="M300" s="8" t="n">
         <v>49.171</v>
       </c>
       <c r="N300" s="4" t="inlineStr">
@@ -22550,7 +22497,7 @@
         </is>
       </c>
       <c r="I301" s="4" t="inlineStr"/>
-      <c r="J301" s="4" t="n">
+      <c r="J301" s="7" t="n">
         <v>35</v>
       </c>
       <c r="K301" s="4" t="inlineStr">
@@ -22563,7 +22510,7 @@
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="M301" s="4" t="n">
+      <c r="M301" s="8" t="n">
         <v>10.444</v>
       </c>
       <c r="N301" s="4" t="inlineStr">
@@ -22629,7 +22576,7 @@
         </is>
       </c>
       <c r="I302" s="4" t="inlineStr"/>
-      <c r="J302" s="4" t="n">
+      <c r="J302" s="7" t="n">
         <v>12</v>
       </c>
       <c r="K302" s="4" t="inlineStr">
@@ -22642,7 +22589,7 @@
           <t>2017-01-01</t>
         </is>
       </c>
-      <c r="M302" s="4" t="n">
+      <c r="M302" s="7" t="n">
         <v>-3266243</v>
       </c>
       <c r="N302" s="4" t="inlineStr">
@@ -22708,7 +22655,7 @@
         </is>
       </c>
       <c r="I303" s="4" t="inlineStr"/>
-      <c r="J303" s="4" t="n">
+      <c r="J303" s="7" t="n">
         <v>53</v>
       </c>
       <c r="K303" s="4" t="inlineStr">
@@ -22721,7 +22668,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M303" s="4" t="n">
+      <c r="M303" s="7" t="n">
         <v>29336</v>
       </c>
       <c r="N303" s="4" t="inlineStr">
@@ -22791,7 +22738,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J304" s="4" t="n">
+      <c r="J304" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K304" s="4" t="inlineStr"/>
@@ -22860,7 +22807,7 @@
         </is>
       </c>
       <c r="I305" s="4" t="inlineStr"/>
-      <c r="J305" s="4" t="n">
+      <c r="J305" s="7" t="n">
         <v>65</v>
       </c>
       <c r="K305" s="4" t="inlineStr">
@@ -22873,7 +22820,7 @@
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="M305" s="4" t="n">
+      <c r="M305" s="8" t="n">
         <v>73.18899999999999</v>
       </c>
       <c r="N305" s="4" t="inlineStr">
@@ -22939,7 +22886,7 @@
         </is>
       </c>
       <c r="I306" s="4" t="inlineStr"/>
-      <c r="J306" s="4" t="n">
+      <c r="J306" s="7" t="n">
         <v>65</v>
       </c>
       <c r="K306" s="4" t="inlineStr">
@@ -22952,7 +22899,7 @@
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="M306" s="4" t="n">
+      <c r="M306" s="8" t="n">
         <v>15.231</v>
       </c>
       <c r="N306" s="4" t="inlineStr">
@@ -23018,7 +22965,7 @@
         </is>
       </c>
       <c r="I307" s="4" t="inlineStr"/>
-      <c r="J307" s="4" t="n">
+      <c r="J307" s="7" t="n">
         <v>65</v>
       </c>
       <c r="K307" s="4" t="inlineStr">
@@ -23031,7 +22978,7 @@
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="M307" s="4" t="n">
+      <c r="M307" s="8" t="n">
         <v>21.2</v>
       </c>
       <c r="N307" s="4" t="inlineStr">
@@ -23097,7 +23044,7 @@
         </is>
       </c>
       <c r="I308" s="4" t="inlineStr"/>
-      <c r="J308" s="4" t="n">
+      <c r="J308" s="7" t="n">
         <v>65</v>
       </c>
       <c r="K308" s="4" t="inlineStr">
@@ -23110,7 +23057,7 @@
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="M308" s="4" t="n">
+      <c r="M308" s="8" t="n">
         <v>72.673</v>
       </c>
       <c r="N308" s="4" t="inlineStr">
@@ -23176,7 +23123,7 @@
         </is>
       </c>
       <c r="I309" s="4" t="inlineStr"/>
-      <c r="J309" s="4" t="n">
+      <c r="J309" s="7" t="n">
         <v>65</v>
       </c>
       <c r="K309" s="4" t="inlineStr">
@@ -23189,7 +23136,7 @@
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="M309" s="4" t="n">
+      <c r="M309" s="8" t="n">
         <v>2.077</v>
       </c>
       <c r="N309" s="4" t="inlineStr">
@@ -23259,7 +23206,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J310" s="4" t="n">
+      <c r="J310" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K310" s="4" t="inlineStr"/>
@@ -23332,7 +23279,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J311" s="4" t="n">
+      <c r="J311" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K311" s="4" t="inlineStr"/>
@@ -23401,7 +23348,7 @@
         </is>
       </c>
       <c r="I312" s="4" t="inlineStr"/>
-      <c r="J312" s="4" t="n">
+      <c r="J312" s="7" t="n">
         <v>66</v>
       </c>
       <c r="K312" s="4" t="inlineStr">
@@ -23414,7 +23361,7 @@
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="M312" s="4" t="n">
+      <c r="M312" s="8" t="n">
         <v>10.0182554931645</v>
       </c>
       <c r="N312" s="4" t="inlineStr">
@@ -23480,7 +23427,7 @@
         </is>
       </c>
       <c r="I313" s="4" t="inlineStr"/>
-      <c r="J313" s="4" t="n">
+      <c r="J313" s="7" t="n">
         <v>66</v>
       </c>
       <c r="K313" s="4" t="inlineStr">
@@ -23493,7 +23440,7 @@
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="M313" s="4" t="n">
+      <c r="M313" s="8" t="n">
         <v>15.397128883349</v>
       </c>
       <c r="N313" s="4" t="inlineStr">
@@ -23559,7 +23506,7 @@
         </is>
       </c>
       <c r="I314" s="4" t="inlineStr"/>
-      <c r="J314" s="4" t="n">
+      <c r="J314" s="7" t="n">
         <v>65</v>
       </c>
       <c r="K314" s="4" t="inlineStr">
@@ -23572,7 +23519,7 @@
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="M314" s="4" t="n">
+      <c r="M314" s="8" t="n">
         <v>0.39124515392802</v>
       </c>
       <c r="N314" s="4" t="inlineStr">
@@ -23642,7 +23589,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J315" s="4" t="n">
+      <c r="J315" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K315" s="4" t="inlineStr"/>
@@ -23715,7 +23662,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J316" s="4" t="n">
+      <c r="J316" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K316" s="4" t="inlineStr"/>
@@ -23788,7 +23735,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J317" s="4" t="n">
+      <c r="J317" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K317" s="4" t="inlineStr"/>
@@ -23861,7 +23808,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J318" s="4" t="n">
+      <c r="J318" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K318" s="4" t="inlineStr"/>
@@ -23934,7 +23881,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J319" s="4" t="n">
+      <c r="J319" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K319" s="4" t="inlineStr"/>
@@ -24007,7 +23954,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J320" s="4" t="n">
+      <c r="J320" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K320" s="4" t="inlineStr"/>
@@ -24080,7 +24027,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J321" s="4" t="n">
+      <c r="J321" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K321" s="4" t="inlineStr"/>
@@ -24153,7 +24100,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J322" s="4" t="n">
+      <c r="J322" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K322" s="4" t="inlineStr"/>
@@ -24226,7 +24173,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J323" s="4" t="n">
+      <c r="J323" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K323" s="4" t="inlineStr"/>
@@ -24299,7 +24246,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J324" s="4" t="n">
+      <c r="J324" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K324" s="4" t="inlineStr"/>
@@ -24372,7 +24319,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J325" s="4" t="n">
+      <c r="J325" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K325" s="4" t="inlineStr"/>
@@ -24441,7 +24388,7 @@
         </is>
       </c>
       <c r="I326" s="4" t="inlineStr"/>
-      <c r="J326" s="4" t="n">
+      <c r="J326" s="7" t="n">
         <v>387</v>
       </c>
       <c r="K326" s="4" t="inlineStr">
@@ -24454,7 +24401,7 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="M326" s="4" t="n">
+      <c r="M326" s="7" t="n">
         <v>7</v>
       </c>
       <c r="N326" s="4" t="inlineStr">
@@ -24524,7 +24471,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J327" s="4" t="n">
+      <c r="J327" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K327" s="4" t="inlineStr"/>
@@ -24597,7 +24544,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J328" s="4" t="n">
+      <c r="J328" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K328" s="4" t="inlineStr"/>
@@ -24670,7 +24617,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J329" s="4" t="n">
+      <c r="J329" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K329" s="4" t="inlineStr"/>
@@ -24743,7 +24690,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J330" s="4" t="n">
+      <c r="J330" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K330" s="4" t="inlineStr"/>
@@ -24816,7 +24763,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J331" s="4" t="n">
+      <c r="J331" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K331" s="4" t="inlineStr"/>
@@ -24889,7 +24836,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J332" s="4" t="n">
+      <c r="J332" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K332" s="4" t="inlineStr"/>
@@ -24962,7 +24909,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J333" s="4" t="n">
+      <c r="J333" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K333" s="4" t="inlineStr"/>
@@ -25035,7 +24982,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J334" s="4" t="n">
+      <c r="J334" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K334" s="4" t="inlineStr"/>
@@ -25108,7 +25055,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J335" s="4" t="n">
+      <c r="J335" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K335" s="4" t="inlineStr"/>
@@ -25181,7 +25128,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J336" s="4" t="n">
+      <c r="J336" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K336" s="4" t="inlineStr"/>
@@ -25254,7 +25201,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J337" s="4" t="n">
+      <c r="J337" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K337" s="4" t="inlineStr"/>
@@ -25327,7 +25274,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J338" s="4" t="n">
+      <c r="J338" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K338" s="4" t="inlineStr"/>
@@ -25400,7 +25347,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J339" s="4" t="n">
+      <c r="J339" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K339" s="4" t="inlineStr"/>
@@ -25473,7 +25420,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J340" s="4" t="n">
+      <c r="J340" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K340" s="4" t="inlineStr"/>
@@ -25546,7 +25493,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J341" s="4" t="n">
+      <c r="J341" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K341" s="4" t="inlineStr"/>
@@ -25619,7 +25566,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J342" s="4" t="n">
+      <c r="J342" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K342" s="4" t="inlineStr"/>
@@ -25692,7 +25639,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J343" s="4" t="n">
+      <c r="J343" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K343" s="4" t="inlineStr"/>
@@ -25765,7 +25712,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J344" s="4" t="n">
+      <c r="J344" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K344" s="4" t="inlineStr"/>
@@ -25838,7 +25785,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J345" s="4" t="n">
+      <c r="J345" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K345" s="4" t="inlineStr"/>
@@ -25907,7 +25854,7 @@
         </is>
       </c>
       <c r="I346" s="4" t="inlineStr"/>
-      <c r="J346" s="4" t="n">
+      <c r="J346" s="7" t="n">
         <v>11</v>
       </c>
       <c r="K346" s="4" t="inlineStr">
@@ -25920,7 +25867,7 @@
           <t>2014-01-01</t>
         </is>
       </c>
-      <c r="M346" s="4" t="n">
+      <c r="M346" s="7" t="n">
         <v>1769451</v>
       </c>
       <c r="N346" s="4" t="inlineStr">
@@ -25990,7 +25937,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J347" s="4" t="n">
+      <c r="J347" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K347" s="4" t="inlineStr"/>
@@ -26063,7 +26010,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J348" s="4" t="n">
+      <c r="J348" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K348" s="4" t="inlineStr"/>
@@ -26136,7 +26083,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J349" s="4" t="n">
+      <c r="J349" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K349" s="4" t="inlineStr"/>
@@ -26209,7 +26156,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J350" s="4" t="n">
+      <c r="J350" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K350" s="4" t="inlineStr"/>
@@ -26282,7 +26229,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J351" s="4" t="n">
+      <c r="J351" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K351" s="4" t="inlineStr"/>
@@ -26355,7 +26302,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J352" s="4" t="n">
+      <c r="J352" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K352" s="4" t="inlineStr"/>
@@ -26428,7 +26375,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J353" s="4" t="n">
+      <c r="J353" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K353" s="4" t="inlineStr"/>
@@ -26501,7 +26448,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J354" s="4" t="n">
+      <c r="J354" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K354" s="4" t="inlineStr"/>
@@ -26574,7 +26521,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J355" s="4" t="n">
+      <c r="J355" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K355" s="4" t="inlineStr"/>
@@ -26647,7 +26594,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J356" s="4" t="n">
+      <c r="J356" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K356" s="4" t="inlineStr"/>
@@ -26720,7 +26667,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J357" s="4" t="n">
+      <c r="J357" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K357" s="4" t="inlineStr"/>
@@ -26793,7 +26740,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J358" s="4" t="n">
+      <c r="J358" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K358" s="4" t="inlineStr"/>
@@ -26866,7 +26813,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J359" s="4" t="n">
+      <c r="J359" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K359" s="4" t="inlineStr"/>
@@ -26939,7 +26886,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J360" s="4" t="n">
+      <c r="J360" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K360" s="4" t="inlineStr"/>
@@ -27012,7 +26959,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J361" s="4" t="n">
+      <c r="J361" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K361" s="4" t="inlineStr"/>
@@ -27085,7 +27032,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J362" s="4" t="n">
+      <c r="J362" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K362" s="4" t="inlineStr"/>
@@ -27158,7 +27105,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J363" s="4" t="n">
+      <c r="J363" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K363" s="4" t="inlineStr"/>
@@ -27231,7 +27178,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J364" s="4" t="n">
+      <c r="J364" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K364" s="4" t="inlineStr"/>
@@ -27300,7 +27247,7 @@
         </is>
       </c>
       <c r="I365" s="4" t="inlineStr"/>
-      <c r="J365" s="4" t="n">
+      <c r="J365" s="7" t="n">
         <v>11</v>
       </c>
       <c r="K365" s="4" t="inlineStr">
@@ -27313,7 +27260,7 @@
           <t>2015-01-01</t>
         </is>
       </c>
-      <c r="M365" s="4" t="n">
+      <c r="M365" s="7" t="n">
         <v>26</v>
       </c>
       <c r="N365" s="4" t="inlineStr">
@@ -27383,7 +27330,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J366" s="4" t="n">
+      <c r="J366" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K366" s="4" t="inlineStr"/>
@@ -27456,7 +27403,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J367" s="4" t="n">
+      <c r="J367" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K367" s="4" t="inlineStr"/>
@@ -27529,7 +27476,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J368" s="4" t="n">
+      <c r="J368" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K368" s="4" t="inlineStr"/>
@@ -27598,7 +27545,7 @@
         </is>
       </c>
       <c r="I369" s="4" t="inlineStr"/>
-      <c r="J369" s="4" t="n">
+      <c r="J369" s="7" t="n">
         <v>10</v>
       </c>
       <c r="K369" s="4" t="inlineStr">
@@ -27611,7 +27558,7 @@
           <t>2014-01-01</t>
         </is>
       </c>
-      <c r="M369" s="4" t="n">
+      <c r="M369" s="8" t="n">
         <v>68.50582168130001</v>
       </c>
       <c r="N369" s="4" t="inlineStr">
@@ -27681,7 +27628,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J370" s="4" t="n">
+      <c r="J370" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K370" s="4" t="inlineStr"/>
@@ -27754,7 +27701,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J371" s="4" t="n">
+      <c r="J371" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K371" s="4" t="inlineStr"/>
@@ -27827,7 +27774,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J372" s="4" t="n">
+      <c r="J372" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K372" s="4" t="inlineStr"/>
@@ -27900,7 +27847,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J373" s="4" t="n">
+      <c r="J373" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K373" s="4" t="inlineStr"/>
@@ -27973,7 +27920,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J374" s="4" t="n">
+      <c r="J374" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K374" s="4" t="inlineStr"/>
@@ -28046,7 +27993,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J375" s="4" t="n">
+      <c r="J375" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K375" s="4" t="inlineStr"/>
@@ -28115,7 +28062,7 @@
         </is>
       </c>
       <c r="I376" s="4" t="inlineStr"/>
-      <c r="J376" s="4" t="n">
+      <c r="J376" s="7" t="n">
         <v>11</v>
       </c>
       <c r="K376" s="4" t="inlineStr">
@@ -28128,7 +28075,7 @@
           <t>2015-01-01</t>
         </is>
       </c>
-      <c r="M376" s="4" t="n">
+      <c r="M376" s="8" t="n">
         <v>37322701822.99</v>
       </c>
       <c r="N376" s="4" t="inlineStr">
@@ -28198,7 +28145,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J377" s="4" t="n">
+      <c r="J377" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K377" s="4" t="inlineStr"/>
@@ -28271,7 +28218,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J378" s="4" t="n">
+      <c r="J378" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K378" s="4" t="inlineStr"/>
@@ -28344,7 +28291,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J379" s="4" t="n">
+      <c r="J379" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K379" s="4" t="inlineStr"/>
@@ -28417,7 +28364,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J380" s="4" t="n">
+      <c r="J380" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K380" s="4" t="inlineStr"/>
@@ -28486,7 +28433,7 @@
         </is>
       </c>
       <c r="I381" s="4" t="inlineStr"/>
-      <c r="J381" s="4" t="n">
+      <c r="J381" s="7" t="n">
         <v>11</v>
       </c>
       <c r="K381" s="4" t="inlineStr">
@@ -28499,7 +28446,7 @@
           <t>2015-01-01</t>
         </is>
       </c>
-      <c r="M381" s="4" t="n">
+      <c r="M381" s="7" t="n">
         <v>23665733</v>
       </c>
       <c r="N381" s="4" t="inlineStr">
@@ -28569,7 +28516,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J382" s="4" t="n">
+      <c r="J382" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K382" s="4" t="inlineStr"/>
@@ -28642,7 +28589,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J383" s="4" t="n">
+      <c r="J383" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K383" s="4" t="inlineStr"/>
@@ -28715,7 +28662,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J384" s="4" t="n">
+      <c r="J384" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K384" s="4" t="inlineStr"/>
@@ -28788,7 +28735,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J385" s="4" t="n">
+      <c r="J385" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K385" s="4" t="inlineStr"/>
@@ -28861,7 +28808,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J386" s="4" t="n">
+      <c r="J386" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K386" s="4" t="inlineStr"/>
@@ -28934,7 +28881,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J387" s="4" t="n">
+      <c r="J387" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K387" s="4" t="inlineStr"/>
@@ -29007,7 +28954,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J388" s="4" t="n">
+      <c r="J388" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K388" s="4" t="inlineStr"/>
@@ -29080,7 +29027,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J389" s="4" t="n">
+      <c r="J389" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K389" s="4" t="inlineStr"/>
@@ -29153,7 +29100,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J390" s="4" t="n">
+      <c r="J390" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K390" s="4" t="inlineStr"/>
@@ -29226,7 +29173,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J391" s="4" t="n">
+      <c r="J391" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K391" s="4" t="inlineStr"/>
@@ -29299,7 +29246,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J392" s="4" t="n">
+      <c r="J392" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K392" s="4" t="inlineStr"/>
@@ -29372,7 +29319,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J393" s="4" t="n">
+      <c r="J393" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K393" s="4" t="inlineStr"/>
@@ -29445,7 +29392,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J394" s="4" t="n">
+      <c r="J394" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K394" s="4" t="inlineStr"/>
@@ -29518,7 +29465,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J395" s="4" t="n">
+      <c r="J395" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K395" s="4" t="inlineStr"/>
@@ -29591,7 +29538,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J396" s="4" t="n">
+      <c r="J396" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K396" s="4" t="inlineStr"/>
@@ -29664,7 +29611,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J397" s="4" t="n">
+      <c r="J397" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K397" s="4" t="inlineStr"/>
@@ -29737,7 +29684,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J398" s="4" t="n">
+      <c r="J398" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K398" s="4" t="inlineStr"/>
@@ -29810,7 +29757,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J399" s="4" t="n">
+      <c r="J399" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K399" s="4" t="inlineStr"/>
@@ -29883,7 +29830,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J400" s="4" t="n">
+      <c r="J400" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K400" s="4" t="inlineStr"/>
@@ -29956,7 +29903,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J401" s="4" t="n">
+      <c r="J401" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K401" s="4" t="inlineStr"/>
@@ -30029,7 +29976,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J402" s="4" t="n">
+      <c r="J402" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K402" s="4" t="inlineStr"/>
@@ -30102,7 +30049,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J403" s="4" t="n">
+      <c r="J403" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K403" s="4" t="inlineStr"/>
@@ -30175,7 +30122,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J404" s="4" t="n">
+      <c r="J404" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K404" s="4" t="inlineStr"/>
@@ -30248,7 +30195,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J405" s="4" t="n">
+      <c r="J405" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K405" s="4" t="inlineStr"/>
@@ -30321,7 +30268,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J406" s="4" t="n">
+      <c r="J406" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K406" s="4" t="inlineStr"/>
@@ -30390,7 +30337,7 @@
         </is>
       </c>
       <c r="I407" s="4" t="inlineStr"/>
-      <c r="J407" s="4" t="n">
+      <c r="J407" s="7" t="n">
         <v>291</v>
       </c>
       <c r="K407" s="4" t="inlineStr">
@@ -30403,7 +30350,7 @@
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="M407" s="4" t="n">
+      <c r="M407" s="8" t="n">
         <v>1.178428</v>
       </c>
       <c r="N407" s="4" t="inlineStr">
@@ -30473,7 +30420,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J408" s="4" t="n">
+      <c r="J408" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K408" s="4" t="inlineStr"/>
@@ -30546,7 +30493,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J409" s="4" t="n">
+      <c r="J409" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K409" s="4" t="inlineStr"/>
@@ -30615,7 +30562,7 @@
         </is>
       </c>
       <c r="I410" s="4" t="inlineStr"/>
-      <c r="J410" s="4" t="n">
+      <c r="J410" s="7" t="n">
         <v>19</v>
       </c>
       <c r="K410" s="4" t="inlineStr">
@@ -30628,7 +30575,7 @@
           <t>2020-01-01</t>
         </is>
       </c>
-      <c r="M410" s="4" t="n">
+      <c r="M410" s="7" t="n">
         <v>3</v>
       </c>
       <c r="N410" s="4" t="inlineStr">
@@ -30698,7 +30645,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J411" s="4" t="n">
+      <c r="J411" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K411" s="4" t="inlineStr"/>
@@ -30771,7 +30718,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J412" s="4" t="n">
+      <c r="J412" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K412" s="4" t="inlineStr"/>
@@ -30840,7 +30787,7 @@
         </is>
       </c>
       <c r="I413" s="4" t="inlineStr"/>
-      <c r="J413" s="4" t="n">
+      <c r="J413" s="7" t="n">
         <v>74</v>
       </c>
       <c r="K413" s="4" t="inlineStr">
@@ -30853,7 +30800,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M413" s="4" t="n">
+      <c r="M413" s="8" t="n">
         <v>8.67714612014831</v>
       </c>
       <c r="N413" s="4" t="inlineStr">
@@ -31003,7 +30950,7 @@
           <t>Número de series catalogadas</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="7" t="n">
         <v>407</v>
       </c>
     </row>
@@ -31013,7 +30960,7 @@
           <t>Número de series con datos</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="7" t="n">
         <v>92</v>
       </c>
     </row>
@@ -31023,7 +30970,7 @@
           <t>Número de registros</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="7" t="n">
         <v>13983</v>
       </c>
     </row>

--- a/assets/data/fred/catalog/catalogo_dataset_web_ove_fred.xlsx
+++ b/assets/data/fred/catalog/catalogo_dataset_web_ove_fred.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="catalogo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="catalogo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -82,26 +82,94 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -116,16 +184,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -134,7 +199,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -149,16 +214,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -627,7 +689,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J7" s="7" t="n">
+      <c r="J7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K7" s="4" t="inlineStr"/>
@@ -700,7 +762,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J8" s="7" t="n">
+      <c r="J8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K8" s="4" t="inlineStr"/>
@@ -773,7 +835,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J9" s="7" t="n">
+      <c r="J9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K9" s="4" t="inlineStr"/>
@@ -846,7 +908,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J10" s="7" t="n">
+      <c r="J10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K10" s="4" t="inlineStr"/>
@@ -919,7 +981,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J11" s="7" t="n">
+      <c r="J11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K11" s="4" t="inlineStr"/>
@@ -992,7 +1054,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J12" s="7" t="n">
+      <c r="J12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="4" t="inlineStr"/>
@@ -1061,7 +1123,7 @@
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr"/>
-      <c r="J13" s="7" t="n">
+      <c r="J13" s="5" t="n">
         <v>74</v>
       </c>
       <c r="K13" s="4" t="inlineStr">
@@ -1074,7 +1136,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M13" s="8" t="n">
+      <c r="M13" s="6" t="n">
         <v>1776.7</v>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1144,7 +1206,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J14" s="7" t="n">
+      <c r="J14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K14" s="4" t="inlineStr"/>
@@ -1217,7 +1279,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J15" s="7" t="n">
+      <c r="J15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K15" s="4" t="inlineStr"/>
@@ -1286,7 +1348,7 @@
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr"/>
-      <c r="J16" s="7" t="n">
+      <c r="J16" s="5" t="n">
         <v>9</v>
       </c>
       <c r="K16" s="4" t="inlineStr">
@@ -1299,7 +1361,7 @@
           <t>2010-01-01</t>
         </is>
       </c>
-      <c r="M16" s="8" t="n">
+      <c r="M16" s="6" t="n">
         <v>15.92</v>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -1365,7 +1427,7 @@
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr"/>
-      <c r="J17" s="7" t="n">
+      <c r="J17" s="5" t="n">
         <v>16</v>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1378,7 +1440,7 @@
           <t>2005-01-01</t>
         </is>
       </c>
-      <c r="M17" s="8" t="n">
+      <c r="M17" s="6" t="n">
         <v>95.9703157644156</v>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -1448,7 +1510,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J18" s="7" t="n">
+      <c r="J18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K18" s="4" t="inlineStr"/>
@@ -1521,7 +1583,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J19" s="7" t="n">
+      <c r="J19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K19" s="4" t="inlineStr"/>
@@ -1590,7 +1652,7 @@
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr"/>
-      <c r="J20" s="7" t="n">
+      <c r="J20" s="5" t="n">
         <v>74</v>
       </c>
       <c r="K20" s="4" t="inlineStr">
@@ -1603,7 +1665,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M20" s="8" t="n">
+      <c r="M20" s="6" t="n">
         <v>2523.1025390625</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -1669,7 +1731,7 @@
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr"/>
-      <c r="J21" s="7" t="n">
+      <c r="J21" s="5" t="n">
         <v>74</v>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -1682,7 +1744,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M21" s="8" t="n">
+      <c r="M21" s="6" t="n">
         <v>4408.41650390625</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -1752,7 +1814,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J22" s="7" t="n">
+      <c r="J22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
@@ -1817,20 +1879,26 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="4" t="inlineStr"/>
-      <c r="L23" s="4" t="inlineStr"/>
-      <c r="M23" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr"/>
+      <c r="J23" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M23" s="6" t="n">
+        <v>21.34434813</v>
+      </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CIPPPGVEA156NUPN</t>
@@ -1894,7 +1962,7 @@
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr"/>
-      <c r="J24" s="7" t="n">
+      <c r="J24" s="5" t="n">
         <v>74</v>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -1907,7 +1975,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="6" t="n">
         <v>120241.203125</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -1977,7 +2045,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J25" s="7" t="n">
+      <c r="J25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K25" s="4" t="inlineStr"/>
@@ -2050,7 +2118,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J26" s="7" t="n">
+      <c r="J26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K26" s="4" t="inlineStr"/>
@@ -2115,20 +2183,26 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="4" t="inlineStr"/>
-      <c r="L27" s="4" t="inlineStr"/>
-      <c r="M27" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr"/>
+      <c r="J27" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M27" s="6" t="n">
+        <v>0.449208825826645</v>
+      </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CSHCCPVEA156NRUG</t>
@@ -2196,7 +2270,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J28" s="7" t="n">
+      <c r="J28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K28" s="4" t="inlineStr"/>
@@ -2265,7 +2339,7 @@
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr"/>
-      <c r="J29" s="7" t="n">
+      <c r="J29" s="5" t="n">
         <v>74</v>
       </c>
       <c r="K29" s="4" t="inlineStr">
@@ -2278,7 +2352,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M29" s="8" t="n">
+      <c r="M29" s="6" t="n">
         <v>0.0565520189702511</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -2340,20 +2414,26 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="4" t="inlineStr"/>
-      <c r="L30" s="4" t="inlineStr"/>
-      <c r="M30" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr"/>
+      <c r="J30" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>-0.301709741353989</v>
+      </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CSHMCPVEA156NRUG</t>
@@ -2421,7 +2501,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J31" s="7" t="n">
+      <c r="J31" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K31" s="4" t="inlineStr"/>
@@ -2494,7 +2574,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J32" s="7" t="n">
+      <c r="J32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K32" s="4" t="inlineStr"/>
@@ -2567,7 +2647,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J33" s="7" t="n">
+      <c r="J33" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K33" s="4" t="inlineStr"/>
@@ -2636,7 +2716,7 @@
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr"/>
-      <c r="J34" s="7" t="n">
+      <c r="J34" s="5" t="n">
         <v>70</v>
       </c>
       <c r="K34" s="4" t="inlineStr">
@@ -2649,7 +2729,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M34" s="8" t="n">
+      <c r="M34" s="6" t="n">
         <v>0.0518108420073986</v>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -2719,7 +2799,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J35" s="7" t="n">
+      <c r="J35" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K35" s="4" t="inlineStr"/>
@@ -2792,7 +2872,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J36" s="7" t="n">
+      <c r="J36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K36" s="4" t="inlineStr"/>
@@ -2865,7 +2945,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J37" s="7" t="n">
+      <c r="J37" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K37" s="4" t="inlineStr"/>
@@ -2938,7 +3018,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J38" s="7" t="n">
+      <c r="J38" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K38" s="4" t="inlineStr"/>
@@ -3007,7 +3087,7 @@
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr"/>
-      <c r="J39" s="7" t="n">
+      <c r="J39" s="5" t="n">
         <v>11</v>
       </c>
       <c r="K39" s="4" t="inlineStr">
@@ -3020,7 +3100,7 @@
           <t>2015-01-01</t>
         </is>
       </c>
-      <c r="M39" s="8" t="n">
+      <c r="M39" s="6" t="n">
         <v>16.533233</v>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -3090,7 +3170,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J40" s="7" t="n">
+      <c r="J40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K40" s="4" t="inlineStr"/>
@@ -3163,7 +3243,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J41" s="7" t="n">
+      <c r="J41" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K41" s="4" t="inlineStr"/>
@@ -3236,7 +3316,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J42" s="7" t="n">
+      <c r="J42" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K42" s="4" t="inlineStr"/>
@@ -3309,7 +3389,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J43" s="7" t="n">
+      <c r="J43" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K43" s="4" t="inlineStr"/>
@@ -3382,7 +3462,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J44" s="7" t="n">
+      <c r="J44" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K44" s="4" t="inlineStr"/>
@@ -3455,7 +3535,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J45" s="7" t="n">
+      <c r="J45" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K45" s="4" t="inlineStr"/>
@@ -3528,7 +3608,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J46" s="7" t="n">
+      <c r="J46" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K46" s="4" t="inlineStr"/>
@@ -3601,7 +3681,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J47" s="7" t="n">
+      <c r="J47" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K47" s="4" t="inlineStr"/>
@@ -3674,7 +3754,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J48" s="7" t="n">
+      <c r="J48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K48" s="4" t="inlineStr"/>
@@ -3739,20 +3819,26 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I49" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J49" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="4" t="inlineStr"/>
-      <c r="L49" s="4" t="inlineStr"/>
-      <c r="M49" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr"/>
+      <c r="J49" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>2013-01-01</t>
+        </is>
+      </c>
+      <c r="M49" s="6" t="n">
+        <v>69.07484000000001</v>
+      </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDI04VEA156NWDB</t>
@@ -3820,7 +3906,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J50" s="7" t="n">
+      <c r="J50" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K50" s="4" t="inlineStr"/>
@@ -3889,7 +3975,7 @@
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr"/>
-      <c r="J51" s="7" t="n">
+      <c r="J51" s="5" t="n">
         <v>54</v>
       </c>
       <c r="K51" s="4" t="inlineStr">
@@ -3902,7 +3988,7 @@
           <t>2013-01-01</t>
         </is>
       </c>
-      <c r="M51" s="8" t="n">
+      <c r="M51" s="6" t="n">
         <v>20.13813</v>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -3972,7 +4058,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J52" s="7" t="n">
+      <c r="J52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K52" s="4" t="inlineStr"/>
@@ -4045,7 +4131,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J53" s="7" t="n">
+      <c r="J53" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K53" s="4" t="inlineStr"/>
@@ -4118,7 +4204,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J54" s="7" t="n">
+      <c r="J54" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K54" s="4" t="inlineStr"/>
@@ -4183,20 +4269,26 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I55" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J55" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="4" t="inlineStr"/>
-      <c r="L55" s="4" t="inlineStr"/>
-      <c r="M55" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr"/>
+      <c r="J55" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>2016-01-01</t>
+        </is>
+      </c>
+      <c r="M55" s="6" t="n">
+        <v>6.290333400000001</v>
+      </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDI11VEA156NWDB</t>
@@ -4256,20 +4348,26 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I56" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="4" t="inlineStr"/>
-      <c r="L56" s="4" t="inlineStr"/>
-      <c r="M56" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr"/>
+      <c r="J56" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M56" s="6" t="n">
+        <v>39.51449</v>
+      </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDI12VEA156NWDB</t>
@@ -4333,7 +4431,7 @@
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr"/>
-      <c r="J57" s="7" t="n">
+      <c r="J57" s="5" t="n">
         <v>10</v>
       </c>
       <c r="K57" s="4" t="inlineStr">
@@ -4346,7 +4444,7 @@
           <t>2002-01-01</t>
         </is>
       </c>
-      <c r="M57" s="8" t="n">
+      <c r="M57" s="6" t="n">
         <v>4.28404</v>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -4408,20 +4506,26 @@
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I58" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="4" t="inlineStr"/>
-      <c r="L58" s="4" t="inlineStr"/>
-      <c r="M58" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr"/>
+      <c r="J58" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>1993-01-01</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>2002-01-01</t>
+        </is>
+      </c>
+      <c r="M58" s="6" t="n">
+        <v>0.095593</v>
+      </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDM02VEA156NWDB</t>
@@ -4489,7 +4593,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J59" s="7" t="n">
+      <c r="J59" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K59" s="4" t="inlineStr"/>
@@ -4562,7 +4666,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J60" s="7" t="n">
+      <c r="J60" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K60" s="4" t="inlineStr"/>
@@ -4635,7 +4739,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J61" s="7" t="n">
+      <c r="J61" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K61" s="4" t="inlineStr"/>
@@ -4704,7 +4808,7 @@
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr"/>
-      <c r="J62" s="7" t="n">
+      <c r="J62" s="5" t="n">
         <v>41</v>
       </c>
       <c r="K62" s="4" t="inlineStr">
@@ -4717,7 +4821,7 @@
           <t>2020-01-01</t>
         </is>
       </c>
-      <c r="M62" s="8" t="n">
+      <c r="M62" s="6" t="n">
         <v>22.39961</v>
       </c>
       <c r="N62" s="4" t="inlineStr">
@@ -4783,7 +4887,7 @@
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr"/>
-      <c r="J63" s="7" t="n">
+      <c r="J63" s="5" t="n">
         <v>41</v>
       </c>
       <c r="K63" s="4" t="inlineStr">
@@ -4796,7 +4900,7 @@
           <t>2020-01-01</t>
         </is>
       </c>
-      <c r="M63" s="8" t="n">
+      <c r="M63" s="6" t="n">
         <v>32.15886</v>
       </c>
       <c r="N63" s="4" t="inlineStr">
@@ -4866,7 +4970,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J64" s="7" t="n">
+      <c r="J64" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K64" s="4" t="inlineStr"/>
@@ -4939,7 +5043,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J65" s="7" t="n">
+      <c r="J65" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K65" s="4" t="inlineStr"/>
@@ -5008,7 +5112,7 @@
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr"/>
-      <c r="J66" s="7" t="n">
+      <c r="J66" s="5" t="n">
         <v>18</v>
       </c>
       <c r="K66" s="4" t="inlineStr">
@@ -5021,7 +5125,7 @@
           <t>2016-01-01</t>
         </is>
       </c>
-      <c r="M66" s="8" t="n">
+      <c r="M66" s="6" t="n">
         <v>0.8002833</v>
       </c>
       <c r="N66" s="4" t="inlineStr">
@@ -5083,20 +5187,26 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I67" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J67" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="4" t="inlineStr"/>
-      <c r="L67" s="4" t="inlineStr"/>
-      <c r="M67" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr"/>
+      <c r="J67" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>2000-01-01</t>
+        </is>
+      </c>
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="M67" s="6" t="n">
+        <v>2.437905</v>
+      </c>
       <c r="N67" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDEI01VEA156NWDB</t>
@@ -5160,7 +5270,7 @@
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr"/>
-      <c r="J68" s="7" t="n">
+      <c r="J68" s="5" t="n">
         <v>28</v>
       </c>
       <c r="K68" s="4" t="inlineStr">
@@ -5173,7 +5283,7 @@
           <t>2017-01-01</t>
         </is>
       </c>
-      <c r="M68" s="8" t="n">
+      <c r="M68" s="6" t="n">
         <v>6.326667</v>
       </c>
       <c r="N68" s="4" t="inlineStr">
@@ -5243,7 +5353,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J69" s="7" t="n">
+      <c r="J69" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K69" s="4" t="inlineStr"/>
@@ -5308,20 +5418,26 @@
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I70" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J70" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" s="4" t="inlineStr"/>
-      <c r="L70" s="4" t="inlineStr"/>
-      <c r="M70" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr"/>
+      <c r="J70" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>2000-01-01</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="M70" s="6" t="n">
+        <v>6.681727</v>
+      </c>
       <c r="N70" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDEI04VEA156NWDB</t>
@@ -5385,7 +5501,7 @@
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr"/>
-      <c r="J71" s="7" t="n">
+      <c r="J71" s="5" t="n">
         <v>22</v>
       </c>
       <c r="K71" s="4" t="inlineStr">
@@ -5398,7 +5514,7 @@
           <t>2021-01-01</t>
         </is>
       </c>
-      <c r="M71" s="8" t="n">
+      <c r="M71" s="6" t="n">
         <v>1.153893</v>
       </c>
       <c r="N71" s="4" t="inlineStr">
@@ -5468,7 +5584,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J72" s="7" t="n">
+      <c r="J72" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K72" s="4" t="inlineStr"/>
@@ -5541,7 +5657,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J73" s="7" t="n">
+      <c r="J73" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K73" s="4" t="inlineStr"/>
@@ -5610,7 +5726,7 @@
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr"/>
-      <c r="J74" s="7" t="n">
+      <c r="J74" s="5" t="n">
         <v>36</v>
       </c>
       <c r="K74" s="4" t="inlineStr">
@@ -5623,7 +5739,7 @@
           <t>2015-01-01</t>
         </is>
       </c>
-      <c r="M74" s="8" t="n">
+      <c r="M74" s="6" t="n">
         <v>7.325303999999998</v>
       </c>
       <c r="N74" s="4" t="inlineStr">
@@ -5693,7 +5809,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J75" s="7" t="n">
+      <c r="J75" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K75" s="4" t="inlineStr"/>
@@ -5750,7 +5866,7 @@
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr"/>
-      <c r="J76" s="7" t="n">
+      <c r="J76" s="5" t="n">
         <v>57</v>
       </c>
       <c r="K76" s="4" t="inlineStr">
@@ -5763,7 +5879,7 @@
           <t>2016-01-01</t>
         </is>
       </c>
-      <c r="M76" s="8" t="n">
+      <c r="M76" s="6" t="n">
         <v>4665.79</v>
       </c>
       <c r="N76" s="4" t="inlineStr">
@@ -5829,7 +5945,7 @@
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr"/>
-      <c r="J77" s="7" t="n">
+      <c r="J77" s="5" t="n">
         <v>22</v>
       </c>
       <c r="K77" s="4" t="inlineStr">
@@ -5842,7 +5958,7 @@
           <t>2021-01-01</t>
         </is>
       </c>
-      <c r="M77" s="8" t="n">
+      <c r="M77" s="6" t="n">
         <v>84.4594</v>
       </c>
       <c r="N77" s="4" t="inlineStr">
@@ -5904,20 +6020,26 @@
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I78" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J78" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" s="4" t="inlineStr"/>
-      <c r="L78" s="4" t="inlineStr"/>
-      <c r="M78" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr"/>
+      <c r="J78" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L78" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M78" s="6" t="n">
+        <v>62.48232</v>
+      </c>
       <c r="N78" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOI02VEA156NWDB</t>
@@ -5985,7 +6107,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J79" s="7" t="n">
+      <c r="J79" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K79" s="4" t="inlineStr"/>
@@ -6058,7 +6180,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J80" s="7" t="n">
+      <c r="J80" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K80" s="4" t="inlineStr"/>
@@ -6131,7 +6253,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J81" s="7" t="n">
+      <c r="J81" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K81" s="4" t="inlineStr"/>
@@ -6204,7 +6326,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J82" s="7" t="n">
+      <c r="J82" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K82" s="4" t="inlineStr"/>
@@ -6273,7 +6395,7 @@
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr"/>
-      <c r="J83" s="7" t="n">
+      <c r="J83" s="5" t="n">
         <v>54</v>
       </c>
       <c r="K83" s="4" t="inlineStr">
@@ -6286,7 +6408,7 @@
           <t>2013-01-01</t>
         </is>
       </c>
-      <c r="M83" s="8" t="n">
+      <c r="M83" s="6" t="n">
         <v>184310.5</v>
       </c>
       <c r="N83" s="4" t="inlineStr">
@@ -6356,7 +6478,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J84" s="7" t="n">
+      <c r="J84" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K84" s="4" t="inlineStr"/>
@@ -6429,7 +6551,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J85" s="7" t="n">
+      <c r="J85" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K85" s="4" t="inlineStr"/>
@@ -6502,7 +6624,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J86" s="7" t="n">
+      <c r="J86" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K86" s="4" t="inlineStr"/>
@@ -6571,7 +6693,7 @@
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr"/>
-      <c r="J87" s="7" t="n">
+      <c r="J87" s="5" t="n">
         <v>30</v>
       </c>
       <c r="K87" s="4" t="inlineStr">
@@ -6584,7 +6706,7 @@
           <t>2014-01-01</t>
         </is>
       </c>
-      <c r="M87" s="8" t="n">
+      <c r="M87" s="6" t="n">
         <v>0.026536</v>
       </c>
       <c r="N87" s="4" t="inlineStr">
@@ -6654,7 +6776,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J88" s="7" t="n">
+      <c r="J88" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K88" s="4" t="inlineStr"/>
@@ -6727,7 +6849,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J89" s="7" t="n">
+      <c r="J89" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K89" s="4" t="inlineStr"/>
@@ -6800,7 +6922,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J90" s="7" t="n">
+      <c r="J90" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K90" s="4" t="inlineStr"/>
@@ -6865,20 +6987,26 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I91" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J91" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" s="4" t="inlineStr"/>
-      <c r="L91" s="4" t="inlineStr"/>
-      <c r="M91" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="inlineStr"/>
+      <c r="J91" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>1990-01-01</t>
+        </is>
+      </c>
+      <c r="L91" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M91" s="6" t="n">
+        <v>1.231569</v>
+      </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOM01VEA644NWDB</t>
@@ -6942,7 +7070,7 @@
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr"/>
-      <c r="J92" s="7" t="n">
+      <c r="J92" s="5" t="n">
         <v>22</v>
       </c>
       <c r="K92" s="4" t="inlineStr">
@@ -6955,7 +7083,7 @@
           <t>2021-01-01</t>
         </is>
       </c>
-      <c r="M92" s="8" t="n">
+      <c r="M92" s="6" t="n">
         <v>12.70259</v>
       </c>
       <c r="N92" s="4" t="inlineStr">
@@ -7017,20 +7145,26 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I93" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J93" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" s="4" t="inlineStr"/>
-      <c r="L93" s="4" t="inlineStr"/>
-      <c r="M93" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr"/>
+      <c r="J93" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K93" s="4" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="L93" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M93" s="6" t="n">
+        <v>0.83999997</v>
+      </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDSI02VEA156NWDB</t>
@@ -7090,20 +7224,26 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I94" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J94" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" s="4" t="inlineStr"/>
-      <c r="L94" s="4" t="inlineStr"/>
-      <c r="M94" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr"/>
+      <c r="J94" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="L94" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M94" s="6" t="n">
+        <v>10.5</v>
+      </c>
       <c r="N94" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDSI03VEA156NWDB</t>
@@ -7163,20 +7303,26 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I95" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J95" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" s="4" t="inlineStr"/>
-      <c r="L95" s="4" t="inlineStr"/>
-      <c r="M95" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr"/>
+      <c r="J95" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="K95" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L95" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M95" s="6" t="n">
+        <v>63.24106999999999</v>
+      </c>
       <c r="N95" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDSI04VEA156NWDB</t>
@@ -7244,7 +7390,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J96" s="7" t="n">
+      <c r="J96" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K96" s="4" t="inlineStr"/>
@@ -7317,7 +7463,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J97" s="7" t="n">
+      <c r="J97" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K97" s="4" t="inlineStr"/>
@@ -7390,7 +7536,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J98" s="7" t="n">
+      <c r="J98" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K98" s="4" t="inlineStr"/>
@@ -7459,7 +7605,7 @@
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr"/>
-      <c r="J99" s="7" t="n">
+      <c r="J99" s="5" t="n">
         <v>4</v>
       </c>
       <c r="K99" s="4" t="inlineStr">
@@ -7472,7 +7618,7 @@
           <t>2021-01-01</t>
         </is>
       </c>
-      <c r="M99" s="8" t="n">
+      <c r="M99" s="6" t="n">
         <v>60.53188000000001</v>
       </c>
       <c r="N99" s="4" t="inlineStr">
@@ -7542,7 +7688,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J100" s="7" t="n">
+      <c r="J100" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K100" s="4" t="inlineStr"/>
@@ -7615,7 +7761,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J101" s="7" t="n">
+      <c r="J101" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K101" s="4" t="inlineStr"/>
@@ -7680,8 +7826,8 @@
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr"/>
-      <c r="J102" s="7" t="n">
-        <v>6643</v>
+      <c r="J102" s="5" t="n">
+        <v>6648</v>
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
@@ -7690,11 +7836,11 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="M102" s="8" t="n">
-        <v>707.9193</v>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="M102" s="6" t="n">
+        <v>725.6326</v>
       </c>
       <c r="N102" s="4" t="inlineStr">
         <is>
@@ -7759,7 +7905,7 @@
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr"/>
-      <c r="J103" s="7" t="n">
+      <c r="J103" s="5" t="n">
         <v>74</v>
       </c>
       <c r="K103" s="4" t="inlineStr">
@@ -7772,7 +7918,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M103" s="8" t="n">
+      <c r="M103" s="6" t="n">
         <v>15.3156814575195</v>
       </c>
       <c r="N103" s="4" t="inlineStr">
@@ -7838,7 +7984,7 @@
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr"/>
-      <c r="J104" s="7" t="n">
+      <c r="J104" s="5" t="n">
         <v>497</v>
       </c>
       <c r="K104" s="4" t="inlineStr">
@@ -7851,7 +7997,7 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="M104" s="8" t="n">
+      <c r="M104" s="6" t="n">
         <v>497.812779</v>
       </c>
       <c r="N104" s="4" t="inlineStr">
@@ -7921,7 +8067,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J105" s="7" t="n">
+      <c r="J105" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K105" s="4" t="inlineStr"/>
@@ -7994,7 +8140,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J106" s="7" t="n">
+      <c r="J106" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K106" s="4" t="inlineStr"/>
@@ -8067,7 +8213,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J107" s="7" t="n">
+      <c r="J107" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K107" s="4" t="inlineStr"/>
@@ -8140,7 +8286,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J108" s="7" t="n">
+      <c r="J108" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K108" s="4" t="inlineStr"/>
@@ -8213,7 +8359,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J109" s="7" t="n">
+      <c r="J109" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K109" s="4" t="inlineStr"/>
@@ -8286,7 +8432,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J110" s="7" t="n">
+      <c r="J110" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K110" s="4" t="inlineStr"/>
@@ -8359,7 +8505,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J111" s="7" t="n">
+      <c r="J111" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K111" s="4" t="inlineStr"/>
@@ -8432,7 +8578,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J112" s="7" t="n">
+      <c r="J112" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K112" s="4" t="inlineStr"/>
@@ -8505,7 +8651,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J113" s="7" t="n">
+      <c r="J113" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K113" s="4" t="inlineStr"/>
@@ -8570,20 +8716,26 @@
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I114" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J114" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" s="4" t="inlineStr"/>
-      <c r="L114" s="4" t="inlineStr"/>
-      <c r="M114" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I114" s="4" t="inlineStr"/>
+      <c r="J114" s="5" t="n">
+        <v>498</v>
+      </c>
+      <c r="K114" s="4" t="inlineStr">
+        <is>
+          <t>1984-12-01</t>
+        </is>
+      </c>
+      <c r="L114" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M114" s="5" t="n">
+        <v>4050</v>
+      </c>
       <c r="N114" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTEQTYPOS32719</t>
@@ -8651,7 +8803,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J115" s="7" t="n">
+      <c r="J115" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K115" s="4" t="inlineStr"/>
@@ -8724,7 +8876,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J116" s="7" t="n">
+      <c r="J116" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K116" s="4" t="inlineStr"/>
@@ -8797,7 +8949,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J117" s="7" t="n">
+      <c r="J117" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K117" s="4" t="inlineStr"/>
@@ -8870,7 +9022,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J118" s="7" t="n">
+      <c r="J118" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K118" s="4" t="inlineStr"/>
@@ -8943,7 +9095,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J119" s="7" t="n">
+      <c r="J119" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K119" s="4" t="inlineStr"/>
@@ -9016,7 +9168,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J120" s="7" t="n">
+      <c r="J120" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K120" s="4" t="inlineStr"/>
@@ -9089,7 +9241,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J121" s="7" t="n">
+      <c r="J121" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K121" s="4" t="inlineStr"/>
@@ -9154,20 +9306,26 @@
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I122" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J122" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" s="4" t="inlineStr"/>
-      <c r="L122" s="4" t="inlineStr"/>
-      <c r="M122" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I122" s="4" t="inlineStr"/>
+      <c r="J122" s="5" t="n">
+        <v>279</v>
+      </c>
+      <c r="K122" s="4" t="inlineStr">
+        <is>
+          <t>2003-03-01</t>
+        </is>
+      </c>
+      <c r="L122" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M122" s="5" t="n">
+        <v>11</v>
+      </c>
       <c r="N122" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORSTTREASNET32719</t>
@@ -9235,7 +9393,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J123" s="7" t="n">
+      <c r="J123" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K123" s="4" t="inlineStr"/>
@@ -9308,7 +9466,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J124" s="7" t="n">
+      <c r="J124" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K124" s="4" t="inlineStr"/>
@@ -9377,7 +9535,7 @@
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr"/>
-      <c r="J125" s="7" t="n">
+      <c r="J125" s="5" t="n">
         <v>280</v>
       </c>
       <c r="K125" s="4" t="inlineStr">
@@ -9390,7 +9548,7 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="M125" s="7" t="n">
+      <c r="M125" s="5" t="n">
         <v>672</v>
       </c>
       <c r="N125" s="4" t="inlineStr">
@@ -9456,7 +9614,7 @@
         </is>
       </c>
       <c r="I126" s="4" t="inlineStr"/>
-      <c r="J126" s="7" t="n">
+      <c r="J126" s="5" t="n">
         <v>8</v>
       </c>
       <c r="K126" s="4" t="inlineStr">
@@ -9469,7 +9627,7 @@
           <t>2016-01-01</t>
         </is>
       </c>
-      <c r="M126" s="8" t="n">
+      <c r="M126" s="6" t="n">
         <v>254.948534781816</v>
       </c>
       <c r="N126" s="4" t="inlineStr">
@@ -9535,7 +9693,7 @@
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr"/>
-      <c r="J127" s="7" t="n">
+      <c r="J127" s="5" t="n">
         <v>61</v>
       </c>
       <c r="K127" s="4" t="inlineStr">
@@ -9548,7 +9706,7 @@
           <t>2010-01-01</t>
         </is>
       </c>
-      <c r="M127" s="8" t="n">
+      <c r="M127" s="6" t="n">
         <v>2.585625</v>
       </c>
       <c r="N127" s="4" t="inlineStr">
@@ -9618,7 +9776,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J128" s="7" t="n">
+      <c r="J128" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K128" s="4" t="inlineStr"/>
@@ -9691,7 +9849,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J129" s="7" t="n">
+      <c r="J129" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K129" s="4" t="inlineStr"/>
@@ -9760,7 +9918,7 @@
         </is>
       </c>
       <c r="I130" s="4" t="inlineStr"/>
-      <c r="J130" s="7" t="n">
+      <c r="J130" s="5" t="n">
         <v>51</v>
       </c>
       <c r="K130" s="4" t="inlineStr">
@@ -9773,7 +9931,7 @@
           <t>2010-01-01</t>
         </is>
       </c>
-      <c r="M130" s="8" t="n">
+      <c r="M130" s="6" t="n">
         <v>98.88050698000001</v>
       </c>
       <c r="N130" s="4" t="inlineStr">
@@ -9839,7 +9997,7 @@
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr"/>
-      <c r="J131" s="7" t="n">
+      <c r="J131" s="5" t="n">
         <v>74</v>
       </c>
       <c r="K131" s="4" t="inlineStr">
@@ -9852,7 +10010,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M131" s="8" t="n">
+      <c r="M131" s="6" t="n">
         <v>3.09922003746033</v>
       </c>
       <c r="N131" s="4" t="inlineStr">
@@ -9922,7 +10080,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J132" s="7" t="n">
+      <c r="J132" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K132" s="4" t="inlineStr"/>
@@ -9995,7 +10153,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J133" s="7" t="n">
+      <c r="J133" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K133" s="4" t="inlineStr"/>
@@ -10068,7 +10226,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J134" s="7" t="n">
+      <c r="J134" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K134" s="4" t="inlineStr"/>
@@ -10141,7 +10299,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J135" s="7" t="n">
+      <c r="J135" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K135" s="4" t="inlineStr"/>
@@ -10214,7 +10372,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J136" s="7" t="n">
+      <c r="J136" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K136" s="4" t="inlineStr"/>
@@ -10287,7 +10445,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J137" s="7" t="n">
+      <c r="J137" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K137" s="4" t="inlineStr"/>
@@ -10360,7 +10518,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J138" s="7" t="n">
+      <c r="J138" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K138" s="4" t="inlineStr"/>
@@ -10433,7 +10591,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J139" s="7" t="n">
+      <c r="J139" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K139" s="4" t="inlineStr"/>
@@ -10506,7 +10664,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J140" s="7" t="n">
+      <c r="J140" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K140" s="4" t="inlineStr"/>
@@ -10579,7 +10737,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J141" s="7" t="n">
+      <c r="J141" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K141" s="4" t="inlineStr"/>
@@ -10644,20 +10802,26 @@
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I142" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J142" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K142" s="4" t="inlineStr"/>
-      <c r="L142" s="4" t="inlineStr"/>
-      <c r="M142" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I142" s="4" t="inlineStr"/>
+      <c r="J142" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K142" s="4" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="L142" s="4" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="M142" s="5" t="n">
+        <v>188</v>
+      </c>
       <c r="N142" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/ICBUSEASEXQVEN</t>
@@ -10721,7 +10885,7 @@
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr"/>
-      <c r="J143" s="7" t="n">
+      <c r="J143" s="5" t="n">
         <v>214</v>
       </c>
       <c r="K143" s="4" t="inlineStr">
@@ -10734,7 +10898,7 @@
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="M143" s="7" t="n">
+      <c r="M143" s="5" t="n">
         <v>3000</v>
       </c>
       <c r="N143" s="4" t="inlineStr">
@@ -10804,7 +10968,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J144" s="7" t="n">
+      <c r="J144" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K144" s="4" t="inlineStr"/>
@@ -10877,7 +11041,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J145" s="7" t="n">
+      <c r="J145" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K145" s="4" t="inlineStr"/>
@@ -10950,7 +11114,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J146" s="7" t="n">
+      <c r="J146" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K146" s="4" t="inlineStr"/>
@@ -11023,7 +11187,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J147" s="7" t="n">
+      <c r="J147" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K147" s="4" t="inlineStr"/>
@@ -11096,7 +11260,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J148" s="7" t="n">
+      <c r="J148" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K148" s="4" t="inlineStr"/>
@@ -11165,7 +11329,7 @@
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr"/>
-      <c r="J149" s="7" t="n">
+      <c r="J149" s="5" t="n">
         <v>214</v>
       </c>
       <c r="K149" s="4" t="inlineStr">
@@ -11178,7 +11342,7 @@
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="M149" s="7" t="n">
+      <c r="M149" s="5" t="n">
         <v>3000</v>
       </c>
       <c r="N149" s="4" t="inlineStr">
@@ -11248,7 +11412,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J150" s="7" t="n">
+      <c r="J150" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K150" s="4" t="inlineStr"/>
@@ -11321,7 +11485,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J151" s="7" t="n">
+      <c r="J151" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K151" s="4" t="inlineStr"/>
@@ -11390,7 +11554,7 @@
         </is>
       </c>
       <c r="I152" s="4" t="inlineStr"/>
-      <c r="J152" s="7" t="n">
+      <c r="J152" s="5" t="n">
         <v>146</v>
       </c>
       <c r="K152" s="4" t="inlineStr">
@@ -11403,7 +11567,7 @@
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="M152" s="7" t="n">
+      <c r="M152" s="5" t="n">
         <v>2397</v>
       </c>
       <c r="N152" s="4" t="inlineStr">
@@ -11473,7 +11637,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J153" s="7" t="n">
+      <c r="J153" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K153" s="4" t="inlineStr"/>
@@ -11546,7 +11710,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J154" s="7" t="n">
+      <c r="J154" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K154" s="4" t="inlineStr"/>
@@ -11615,7 +11779,7 @@
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr"/>
-      <c r="J155" s="7" t="n">
+      <c r="J155" s="5" t="n">
         <v>214</v>
       </c>
       <c r="K155" s="4" t="inlineStr">
@@ -11628,7 +11792,7 @@
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="M155" s="7" t="n">
+      <c r="M155" s="5" t="n">
         <v>23802</v>
       </c>
       <c r="N155" s="4" t="inlineStr">
@@ -11698,7 +11862,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J156" s="7" t="n">
+      <c r="J156" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K156" s="4" t="inlineStr"/>
@@ -11763,20 +11927,26 @@
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I157" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J157" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K157" s="4" t="inlineStr"/>
-      <c r="L157" s="4" t="inlineStr"/>
-      <c r="M157" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I157" s="4" t="inlineStr"/>
+      <c r="J157" s="5" t="n">
+        <v>214</v>
+      </c>
+      <c r="K157" s="4" t="inlineStr">
+        <is>
+          <t>1972-10-01</t>
+        </is>
+      </c>
+      <c r="L157" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M157" s="5" t="n">
+        <v>15950</v>
+      </c>
       <c r="N157" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSGAMRIAOVE</t>
@@ -11840,7 +12010,7 @@
         </is>
       </c>
       <c r="I158" s="4" t="inlineStr"/>
-      <c r="J158" s="7" t="n">
+      <c r="J158" s="5" t="n">
         <v>109</v>
       </c>
       <c r="K158" s="4" t="inlineStr">
@@ -11853,7 +12023,7 @@
           <t>2025-04-01</t>
         </is>
       </c>
-      <c r="M158" s="7" t="n">
+      <c r="M158" s="5" t="n">
         <v>-1600</v>
       </c>
       <c r="N158" s="4" t="inlineStr">
@@ -11923,7 +12093,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J159" s="7" t="n">
+      <c r="J159" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K159" s="4" t="inlineStr"/>
@@ -11996,7 +12166,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J160" s="7" t="n">
+      <c r="J160" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K160" s="4" t="inlineStr"/>
@@ -12069,7 +12239,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J161" s="7" t="n">
+      <c r="J161" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K161" s="4" t="inlineStr"/>
@@ -12142,7 +12312,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J162" s="7" t="n">
+      <c r="J162" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K162" s="4" t="inlineStr"/>
@@ -12215,7 +12385,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J163" s="7" t="n">
+      <c r="J163" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K163" s="4" t="inlineStr"/>
@@ -12280,20 +12450,26 @@
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I164" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J164" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K164" s="4" t="inlineStr"/>
-      <c r="L164" s="4" t="inlineStr"/>
-      <c r="M164" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I164" s="4" t="inlineStr"/>
+      <c r="J164" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="K164" s="4" t="inlineStr">
+        <is>
+          <t>1993-07-01</t>
+        </is>
+      </c>
+      <c r="L164" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M164" s="6" t="n">
+        <v>-1.12602</v>
+      </c>
       <c r="N164" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSGGGAMNINIVE</t>
@@ -12361,7 +12537,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J165" s="7" t="n">
+      <c r="J165" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K165" s="4" t="inlineStr"/>
@@ -12430,7 +12606,7 @@
         </is>
       </c>
       <c r="I166" s="4" t="inlineStr"/>
-      <c r="J166" s="7" t="n">
+      <c r="J166" s="5" t="n">
         <v>37</v>
       </c>
       <c r="K166" s="4" t="inlineStr">
@@ -12443,7 +12619,7 @@
           <t>2014-10-01</t>
         </is>
       </c>
-      <c r="M166" s="8" t="n">
+      <c r="M166" s="6" t="n">
         <v>-1.3</v>
       </c>
       <c r="N166" s="4" t="inlineStr">
@@ -12513,7 +12689,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J167" s="7" t="n">
+      <c r="J167" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K167" s="4" t="inlineStr"/>
@@ -12586,7 +12762,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J168" s="7" t="n">
+      <c r="J168" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K168" s="4" t="inlineStr"/>
@@ -12659,7 +12835,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J169" s="7" t="n">
+      <c r="J169" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K169" s="4" t="inlineStr"/>
@@ -12732,7 +12908,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J170" s="7" t="n">
+      <c r="J170" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K170" s="4" t="inlineStr"/>
@@ -12805,7 +12981,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J171" s="7" t="n">
+      <c r="J171" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K171" s="4" t="inlineStr"/>
@@ -12878,7 +13054,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J172" s="7" t="n">
+      <c r="J172" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K172" s="4" t="inlineStr"/>
@@ -12951,7 +13127,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J173" s="7" t="n">
+      <c r="J173" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K173" s="4" t="inlineStr"/>
@@ -13024,7 +13200,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J174" s="7" t="n">
+      <c r="J174" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K174" s="4" t="inlineStr"/>
@@ -13089,20 +13265,26 @@
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I175" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J175" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K175" s="4" t="inlineStr"/>
-      <c r="L175" s="4" t="inlineStr"/>
-      <c r="M175" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I175" s="4" t="inlineStr"/>
+      <c r="J175" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="K175" s="4" t="inlineStr">
+        <is>
+          <t>1990-10-01</t>
+        </is>
+      </c>
+      <c r="L175" s="4" t="inlineStr">
+        <is>
+          <t>1997-04-01</t>
+        </is>
+      </c>
+      <c r="M175" s="6" t="n">
+        <v>0.015</v>
+      </c>
       <c r="N175" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IMMINIAIAOVE</t>
@@ -13162,20 +13344,26 @@
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I176" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J176" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K176" s="4" t="inlineStr"/>
-      <c r="L176" s="4" t="inlineStr"/>
-      <c r="M176" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I176" s="4" t="inlineStr"/>
+      <c r="J176" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="K176" s="4" t="inlineStr">
+        <is>
+          <t>1993-10-01</t>
+        </is>
+      </c>
+      <c r="L176" s="4" t="inlineStr">
+        <is>
+          <t>1997-01-01</t>
+        </is>
+      </c>
+      <c r="M176" s="6" t="n">
+        <v>0.015</v>
+      </c>
       <c r="N176" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IMMINIAIGIVE</t>
@@ -13235,20 +13423,26 @@
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I177" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J177" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K177" s="4" t="inlineStr"/>
-      <c r="L177" s="4" t="inlineStr"/>
-      <c r="M177" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I177" s="4" t="inlineStr"/>
+      <c r="J177" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="K177" s="4" t="inlineStr">
+        <is>
+          <t>1993-10-01</t>
+        </is>
+      </c>
+      <c r="L177" s="4" t="inlineStr">
+        <is>
+          <t>1997-07-01</t>
+        </is>
+      </c>
+      <c r="M177" s="6" t="n">
+        <v>-0.015</v>
+      </c>
       <c r="N177" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IMMINIAINIVE</t>
@@ -13316,7 +13510,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J178" s="7" t="n">
+      <c r="J178" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K178" s="4" t="inlineStr"/>
@@ -13389,7 +13583,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J179" s="7" t="n">
+      <c r="J179" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K179" s="4" t="inlineStr"/>
@@ -13462,7 +13656,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J180" s="7" t="n">
+      <c r="J180" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K180" s="4" t="inlineStr"/>
@@ -13531,7 +13725,7 @@
         </is>
       </c>
       <c r="I181" s="4" t="inlineStr"/>
-      <c r="J181" s="7" t="n">
+      <c r="J181" s="5" t="n">
         <v>497</v>
       </c>
       <c r="K181" s="4" t="inlineStr">
@@ -13544,7 +13738,7 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="M181" s="8" t="n">
+      <c r="M181" s="6" t="n">
         <v>1525.18625</v>
       </c>
       <c r="N181" s="4" t="inlineStr">
@@ -13614,7 +13808,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J182" s="7" t="n">
+      <c r="J182" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K182" s="4" t="inlineStr"/>
@@ -13687,7 +13881,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J183" s="7" t="n">
+      <c r="J183" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K183" s="4" t="inlineStr"/>
@@ -13756,7 +13950,7 @@
         </is>
       </c>
       <c r="I184" s="4" t="inlineStr"/>
-      <c r="J184" s="7" t="n">
+      <c r="J184" s="5" t="n">
         <v>53</v>
       </c>
       <c r="K184" s="4" t="inlineStr">
@@ -13769,7 +13963,7 @@
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="M184" s="8" t="n">
+      <c r="M184" s="6" t="n">
         <v>71.00759172250289</v>
       </c>
       <c r="N184" s="4" t="inlineStr">
@@ -13839,7 +14033,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J185" s="7" t="n">
+      <c r="J185" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K185" s="4" t="inlineStr"/>
@@ -13908,7 +14102,7 @@
         </is>
       </c>
       <c r="I186" s="4" t="inlineStr"/>
-      <c r="J186" s="7" t="n">
+      <c r="J186" s="5" t="n">
         <v>32</v>
       </c>
       <c r="K186" s="4" t="inlineStr">
@@ -13921,7 +14115,7 @@
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="M186" s="8" t="n">
+      <c r="M186" s="6" t="n">
         <v>76.67890167</v>
       </c>
       <c r="N186" s="4" t="inlineStr">
@@ -13983,20 +14177,26 @@
       </c>
       <c r="H187" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I187" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J187" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K187" s="4" t="inlineStr"/>
-      <c r="L187" s="4" t="inlineStr"/>
-      <c r="M187" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I187" s="4" t="inlineStr"/>
+      <c r="J187" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="K187" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L187" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M187" s="6" t="n">
+        <v>71.87844938000001</v>
+      </c>
       <c r="N187" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/KCPPPGVEA156NUPN</t>
@@ -14056,20 +14256,26 @@
       </c>
       <c r="H188" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I188" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J188" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K188" s="4" t="inlineStr"/>
-      <c r="L188" s="4" t="inlineStr"/>
-      <c r="M188" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I188" s="4" t="inlineStr"/>
+      <c r="J188" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="K188" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L188" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M188" s="6" t="n">
+        <v>5.389651742</v>
+      </c>
       <c r="N188" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/KGPPPGVEA156NUPN</t>
@@ -14129,20 +14335,26 @@
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I189" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J189" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K189" s="4" t="inlineStr"/>
-      <c r="L189" s="4" t="inlineStr"/>
-      <c r="M189" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I189" s="4" t="inlineStr"/>
+      <c r="J189" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="K189" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L189" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M189" s="6" t="n">
+        <v>24.52833168</v>
+      </c>
       <c r="N189" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/KIPPPGVEA156NUPN</t>
@@ -14210,7 +14422,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J190" s="7" t="n">
+      <c r="J190" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K190" s="4" t="inlineStr"/>
@@ -14283,7 +14495,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J191" s="7" t="n">
+      <c r="J191" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K191" s="4" t="inlineStr"/>
@@ -14356,7 +14568,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J192" s="7" t="n">
+      <c r="J192" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K192" s="4" t="inlineStr"/>
@@ -14429,7 +14641,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J193" s="7" t="n">
+      <c r="J193" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K193" s="4" t="inlineStr"/>
@@ -14498,7 +14710,7 @@
         </is>
       </c>
       <c r="I194" s="4" t="inlineStr"/>
-      <c r="J194" s="7" t="n">
+      <c r="J194" s="5" t="n">
         <v>74</v>
       </c>
       <c r="K194" s="4" t="inlineStr">
@@ -14511,7 +14723,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M194" s="8" t="n">
+      <c r="M194" s="6" t="n">
         <v>0.08436375111341481</v>
       </c>
       <c r="N194" s="4" t="inlineStr">
@@ -14581,7 +14793,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J195" s="7" t="n">
+      <c r="J195" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K195" s="4" t="inlineStr"/>
@@ -14654,7 +14866,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J196" s="7" t="n">
+      <c r="J196" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K196" s="4" t="inlineStr"/>
@@ -14727,7 +14939,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J197" s="7" t="n">
+      <c r="J197" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K197" s="4" t="inlineStr"/>
@@ -14800,7 +15012,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J198" s="7" t="n">
+      <c r="J198" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K198" s="4" t="inlineStr"/>
@@ -14873,7 +15085,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J199" s="7" t="n">
+      <c r="J199" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K199" s="4" t="inlineStr"/>
@@ -14946,7 +15158,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J200" s="7" t="n">
+      <c r="J200" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K200" s="4" t="inlineStr"/>
@@ -15019,7 +15231,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J201" s="7" t="n">
+      <c r="J201" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K201" s="4" t="inlineStr"/>
@@ -15092,7 +15304,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J202" s="7" t="n">
+      <c r="J202" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K202" s="4" t="inlineStr"/>
@@ -15165,7 +15377,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J203" s="7" t="n">
+      <c r="J203" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K203" s="4" t="inlineStr"/>
@@ -15238,7 +15450,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J204" s="7" t="n">
+      <c r="J204" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K204" s="4" t="inlineStr"/>
@@ -15307,7 +15519,7 @@
         </is>
       </c>
       <c r="I205" s="4" t="inlineStr"/>
-      <c r="J205" s="7" t="n">
+      <c r="J205" s="5" t="n">
         <v>66</v>
       </c>
       <c r="K205" s="4" t="inlineStr">
@@ -15320,7 +15532,7 @@
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="M205" s="8" t="n">
+      <c r="M205" s="6" t="n">
         <v>99661244155.6306</v>
       </c>
       <c r="N205" s="4" t="inlineStr">
@@ -15386,7 +15598,7 @@
         </is>
       </c>
       <c r="I206" s="4" t="inlineStr"/>
-      <c r="J206" s="7" t="n">
+      <c r="J206" s="5" t="n">
         <v>66</v>
       </c>
       <c r="K206" s="4" t="inlineStr">
@@ -15399,7 +15611,7 @@
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="M206" s="8" t="n">
+      <c r="M206" s="6" t="n">
         <v>98061244155.6306</v>
       </c>
       <c r="N206" s="4" t="inlineStr">
@@ -15469,7 +15681,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J207" s="7" t="n">
+      <c r="J207" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K207" s="4" t="inlineStr"/>
@@ -15542,7 +15754,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J208" s="7" t="n">
+      <c r="J208" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K208" s="4" t="inlineStr"/>
@@ -15615,7 +15827,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J209" s="7" t="n">
+      <c r="J209" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K209" s="4" t="inlineStr"/>
@@ -15688,7 +15900,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J210" s="7" t="n">
+      <c r="J210" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K210" s="4" t="inlineStr"/>
@@ -15761,7 +15973,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J211" s="7" t="n">
+      <c r="J211" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K211" s="4" t="inlineStr"/>
@@ -15834,7 +16046,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J212" s="7" t="n">
+      <c r="J212" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K212" s="4" t="inlineStr"/>
@@ -15907,7 +16119,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J213" s="7" t="n">
+      <c r="J213" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K213" s="4" t="inlineStr"/>
@@ -15972,20 +16184,26 @@
       </c>
       <c r="H214" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I214" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J214" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K214" s="4" t="inlineStr"/>
-      <c r="L214" s="4" t="inlineStr"/>
-      <c r="M214" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I214" s="4" t="inlineStr"/>
+      <c r="J214" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="K214" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L214" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M214" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="N214" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MTVENA475SCEN</t>
@@ -16049,7 +16267,7 @@
         </is>
       </c>
       <c r="I215" s="4" t="inlineStr"/>
-      <c r="J215" s="7" t="n">
+      <c r="J215" s="5" t="n">
         <v>302</v>
       </c>
       <c r="K215" s="4" t="inlineStr">
@@ -16062,7 +16280,7 @@
           <t>2019-02-01</t>
         </is>
       </c>
-      <c r="M215" s="7" t="n">
+      <c r="M215" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N215" s="4" t="inlineStr">
@@ -16132,7 +16350,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J216" s="7" t="n">
+      <c r="J216" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K216" s="4" t="inlineStr"/>
@@ -16205,7 +16423,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J217" s="7" t="n">
+      <c r="J217" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K217" s="4" t="inlineStr"/>
@@ -16278,7 +16496,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J218" s="7" t="n">
+      <c r="J218" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K218" s="4" t="inlineStr"/>
@@ -16351,7 +16569,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J219" s="7" t="n">
+      <c r="J219" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K219" s="4" t="inlineStr"/>
@@ -16424,7 +16642,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J220" s="7" t="n">
+      <c r="J220" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K220" s="4" t="inlineStr"/>
@@ -16497,7 +16715,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J221" s="7" t="n">
+      <c r="J221" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K221" s="4" t="inlineStr"/>
@@ -16570,7 +16788,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J222" s="7" t="n">
+      <c r="J222" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K222" s="4" t="inlineStr"/>
@@ -16643,7 +16861,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J223" s="7" t="n">
+      <c r="J223" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K223" s="4" t="inlineStr"/>
@@ -16708,20 +16926,26 @@
       </c>
       <c r="H224" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I224" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J224" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K224" s="4" t="inlineStr"/>
-      <c r="L224" s="4" t="inlineStr"/>
-      <c r="M224" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I224" s="4" t="inlineStr"/>
+      <c r="J224" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="K224" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L224" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M224" s="5" t="n">
+        <v>3888969</v>
+      </c>
       <c r="N224" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NJVENA052SCEN</t>
@@ -16789,7 +17013,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J225" s="7" t="n">
+      <c r="J225" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K225" s="4" t="inlineStr"/>
@@ -16862,7 +17086,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J226" s="7" t="n">
+      <c r="J226" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K226" s="4" t="inlineStr"/>
@@ -16935,7 +17159,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J227" s="7" t="n">
+      <c r="J227" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K227" s="4" t="inlineStr"/>
@@ -17000,20 +17224,26 @@
       </c>
       <c r="H228" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I228" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J228" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K228" s="4" t="inlineStr"/>
-      <c r="L228" s="4" t="inlineStr"/>
-      <c r="M228" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I228" s="4" t="inlineStr"/>
+      <c r="J228" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="K228" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L228" s="4" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="M228" s="5" t="n">
+        <v>144707</v>
+      </c>
       <c r="N228" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NVVENA052SCEN</t>
@@ -17081,7 +17311,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J229" s="7" t="n">
+      <c r="J229" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K229" s="4" t="inlineStr"/>
@@ -17150,7 +17380,7 @@
         </is>
       </c>
       <c r="I230" s="4" t="inlineStr"/>
-      <c r="J230" s="7" t="n">
+      <c r="J230" s="5" t="n">
         <v>55</v>
       </c>
       <c r="K230" s="4" t="inlineStr">
@@ -17163,7 +17393,7 @@
           <t>2014-01-01</t>
         </is>
       </c>
-      <c r="M230" s="8" t="n">
+      <c r="M230" s="6" t="n">
         <v>14026.3664129191</v>
       </c>
       <c r="N230" s="4" t="inlineStr">
@@ -17233,7 +17463,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J231" s="7" t="n">
+      <c r="J231" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K231" s="4" t="inlineStr"/>
@@ -17306,7 +17536,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J232" s="7" t="n">
+      <c r="J232" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K232" s="4" t="inlineStr"/>
@@ -17379,7 +17609,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J233" s="7" t="n">
+      <c r="J233" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K233" s="4" t="inlineStr"/>
@@ -17452,7 +17682,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J234" s="7" t="n">
+      <c r="J234" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K234" s="4" t="inlineStr"/>
@@ -17525,7 +17755,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J235" s="7" t="n">
+      <c r="J235" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K235" s="4" t="inlineStr"/>
@@ -17598,7 +17828,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J236" s="7" t="n">
+      <c r="J236" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K236" s="4" t="inlineStr"/>
@@ -17663,20 +17893,26 @@
       </c>
       <c r="H237" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I237" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J237" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K237" s="4" t="inlineStr"/>
-      <c r="L237" s="4" t="inlineStr"/>
-      <c r="M237" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I237" s="4" t="inlineStr"/>
+      <c r="J237" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="K237" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L237" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M237" s="6" t="n">
+        <v>45.86565346</v>
+      </c>
       <c r="N237" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/OPENCPVEA156NUPN</t>
@@ -17744,7 +17980,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J238" s="7" t="n">
+      <c r="J238" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K238" s="4" t="inlineStr"/>
@@ -17809,20 +18045,26 @@
       </c>
       <c r="H239" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I239" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J239" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K239" s="4" t="inlineStr"/>
-      <c r="L239" s="4" t="inlineStr"/>
-      <c r="M239" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I239" s="4" t="inlineStr"/>
+      <c r="J239" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="K239" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L239" s="4" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="M239" s="5" t="n">
+        <v>197417</v>
+      </c>
       <c r="N239" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/ORVENA052SCEN</t>
@@ -17890,7 +18132,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J240" s="7" t="n">
+      <c r="J240" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K240" s="4" t="inlineStr"/>
@@ -17963,7 +18205,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J241" s="7" t="n">
+      <c r="J241" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K241" s="4" t="inlineStr"/>
@@ -18036,7 +18278,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J242" s="7" t="n">
+      <c r="J242" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K242" s="4" t="inlineStr"/>
@@ -18109,7 +18351,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J243" s="7" t="n">
+      <c r="J243" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K243" s="4" t="inlineStr"/>
@@ -18174,20 +18416,26 @@
       </c>
       <c r="H244" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I244" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J244" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K244" s="4" t="inlineStr"/>
-      <c r="L244" s="4" t="inlineStr"/>
-      <c r="M244" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I244" s="4" t="inlineStr"/>
+      <c r="J244" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="K244" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L244" s="4" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="M244" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="N244" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PATENT4NVETOTAL</t>
@@ -18247,20 +18495,26 @@
       </c>
       <c r="H245" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I245" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J245" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K245" s="4" t="inlineStr"/>
-      <c r="L245" s="4" t="inlineStr"/>
-      <c r="M245" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I245" s="4" t="inlineStr"/>
+      <c r="J245" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="K245" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L245" s="4" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="M245" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="N245" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PATENT4NVEUTILITY</t>
@@ -18328,7 +18582,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J246" s="7" t="n">
+      <c r="J246" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K246" s="4" t="inlineStr"/>
@@ -18401,7 +18655,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J247" s="7" t="n">
+      <c r="J247" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K247" s="4" t="inlineStr"/>
@@ -18470,7 +18724,7 @@
         </is>
       </c>
       <c r="I248" s="4" t="inlineStr"/>
-      <c r="J248" s="7" t="n">
+      <c r="J248" s="5" t="n">
         <v>61</v>
       </c>
       <c r="K248" s="4" t="inlineStr">
@@ -18483,7 +18737,7 @@
           <t>2010-01-01</t>
         </is>
       </c>
-      <c r="M248" s="8" t="n">
+      <c r="M248" s="6" t="n">
         <v>11809.94057</v>
       </c>
       <c r="N248" s="4" t="inlineStr">
@@ -18549,7 +18803,7 @@
         </is>
       </c>
       <c r="I249" s="4" t="inlineStr"/>
-      <c r="J249" s="7" t="n">
+      <c r="J249" s="5" t="n">
         <v>66</v>
       </c>
       <c r="K249" s="4" t="inlineStr">
@@ -18562,7 +18816,7 @@
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="M249" s="8" t="n">
+      <c r="M249" s="6" t="n">
         <v>3494.8138870244</v>
       </c>
       <c r="N249" s="4" t="inlineStr">
@@ -18632,7 +18886,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J250" s="7" t="n">
+      <c r="J250" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K250" s="4" t="inlineStr"/>
@@ -18697,20 +18951,26 @@
       </c>
       <c r="H251" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I251" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J251" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K251" s="4" t="inlineStr"/>
-      <c r="L251" s="4" t="inlineStr"/>
-      <c r="M251" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I251" s="4" t="inlineStr"/>
+      <c r="J251" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="K251" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L251" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M251" s="6" t="n">
+        <v>25.36032612</v>
+      </c>
       <c r="N251" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PGD2USVEA621NUPN</t>
@@ -18774,7 +19034,7 @@
         </is>
       </c>
       <c r="I252" s="4" t="inlineStr"/>
-      <c r="J252" s="7" t="n">
+      <c r="J252" s="5" t="n">
         <v>61</v>
       </c>
       <c r="K252" s="4" t="inlineStr">
@@ -18787,7 +19047,7 @@
           <t>2010-01-01</t>
         </is>
       </c>
-      <c r="M252" s="8" t="n">
+      <c r="M252" s="6" t="n">
         <v>25.29171848</v>
       </c>
       <c r="N252" s="4" t="inlineStr">
@@ -18853,7 +19113,7 @@
         </is>
       </c>
       <c r="I253" s="4" t="inlineStr"/>
-      <c r="J253" s="7" t="n">
+      <c r="J253" s="5" t="n">
         <v>61</v>
       </c>
       <c r="K253" s="4" t="inlineStr">
@@ -18866,7 +19126,7 @@
           <t>2010-01-01</t>
         </is>
       </c>
-      <c r="M253" s="8" t="n">
+      <c r="M253" s="6" t="n">
         <v>121.3461635</v>
       </c>
       <c r="N253" s="4" t="inlineStr">
@@ -18932,7 +19192,7 @@
         </is>
       </c>
       <c r="I254" s="4" t="inlineStr"/>
-      <c r="J254" s="7" t="n">
+      <c r="J254" s="5" t="n">
         <v>74</v>
       </c>
       <c r="K254" s="4" t="inlineStr">
@@ -18945,7 +19205,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M254" s="8" t="n">
+      <c r="M254" s="6" t="n">
         <v>65.5449341102796</v>
       </c>
       <c r="N254" s="4" t="inlineStr">
@@ -19011,7 +19271,7 @@
         </is>
       </c>
       <c r="I255" s="4" t="inlineStr"/>
-      <c r="J255" s="7" t="n">
+      <c r="J255" s="5" t="n">
         <v>74</v>
       </c>
       <c r="K255" s="4" t="inlineStr">
@@ -19024,7 +19284,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M255" s="8" t="n">
+      <c r="M255" s="6" t="n">
         <v>23.2163643183614</v>
       </c>
       <c r="N255" s="4" t="inlineStr">
@@ -19094,7 +19354,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J256" s="7" t="n">
+      <c r="J256" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K256" s="4" t="inlineStr"/>
@@ -19167,7 +19427,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J257" s="7" t="n">
+      <c r="J257" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K257" s="4" t="inlineStr"/>
@@ -19240,7 +19500,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J258" s="7" t="n">
+      <c r="J258" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K258" s="4" t="inlineStr"/>
@@ -19309,7 +19569,7 @@
         </is>
       </c>
       <c r="I259" s="4" t="inlineStr"/>
-      <c r="J259" s="7" t="n">
+      <c r="J259" s="5" t="n">
         <v>70</v>
       </c>
       <c r="K259" s="4" t="inlineStr">
@@ -19322,7 +19582,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M259" s="8" t="n">
+      <c r="M259" s="6" t="n">
         <v>15.1081390380859</v>
       </c>
       <c r="N259" s="4" t="inlineStr">
@@ -19384,20 +19644,26 @@
       </c>
       <c r="H260" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I260" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J260" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K260" s="4" t="inlineStr"/>
-      <c r="L260" s="4" t="inlineStr"/>
-      <c r="M260" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I260" s="4" t="inlineStr"/>
+      <c r="J260" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="K260" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L260" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M260" s="6" t="n">
+        <v>0.610256195068359</v>
+      </c>
       <c r="N260" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLMCPPVEA670NRUG</t>
@@ -19457,20 +19723,26 @@
       </c>
       <c r="H261" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I261" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J261" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K261" s="4" t="inlineStr"/>
-      <c r="L261" s="4" t="inlineStr"/>
-      <c r="M261" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I261" s="4" t="inlineStr"/>
+      <c r="J261" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="K261" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L261" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M261" s="6" t="n">
+        <v>121.4234463</v>
+      </c>
       <c r="N261" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLOCONVEA622NUPN</t>
@@ -19538,7 +19810,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J262" s="7" t="n">
+      <c r="J262" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K262" s="4" t="inlineStr"/>
@@ -19603,20 +19875,26 @@
       </c>
       <c r="H263" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I263" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J263" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K263" s="4" t="inlineStr"/>
-      <c r="L263" s="4" t="inlineStr"/>
-      <c r="M263" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I263" s="4" t="inlineStr"/>
+      <c r="J263" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="K263" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L263" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M263" s="6" t="n">
+        <v>144.0149859</v>
+      </c>
       <c r="N263" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLOGINVEA623NUPN</t>
@@ -19680,7 +19958,7 @@
         </is>
       </c>
       <c r="I264" s="4" t="inlineStr"/>
-      <c r="J264" s="7" t="n">
+      <c r="J264" s="5" t="n">
         <v>61</v>
       </c>
       <c r="K264" s="4" t="inlineStr">
@@ -19693,7 +19971,7 @@
           <t>2010-01-01</t>
         </is>
       </c>
-      <c r="M264" s="8" t="n">
+      <c r="M264" s="6" t="n">
         <v>119.0453568</v>
       </c>
       <c r="N264" s="4" t="inlineStr">
@@ -19759,7 +20037,7 @@
         </is>
       </c>
       <c r="I265" s="4" t="inlineStr"/>
-      <c r="J265" s="7" t="n">
+      <c r="J265" s="5" t="n">
         <v>74</v>
       </c>
       <c r="K265" s="4" t="inlineStr">
@@ -19772,7 +20050,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M265" s="8" t="n">
+      <c r="M265" s="6" t="n">
         <v>0.206251129508019</v>
       </c>
       <c r="N265" s="4" t="inlineStr">
@@ -19834,7 +20112,7 @@
         </is>
       </c>
       <c r="I266" s="4" t="inlineStr"/>
-      <c r="J266" s="7" t="n">
+      <c r="J266" s="5" t="n">
         <v>66</v>
       </c>
       <c r="K266" s="4" t="inlineStr">
@@ -19847,7 +20125,7 @@
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="M266" s="7" t="n">
+      <c r="M266" s="5" t="n">
         <v>28516896</v>
       </c>
       <c r="N266" s="4" t="inlineStr">
@@ -19913,7 +20191,7 @@
         </is>
       </c>
       <c r="I267" s="4" t="inlineStr"/>
-      <c r="J267" s="7" t="n">
+      <c r="J267" s="5" t="n">
         <v>74</v>
       </c>
       <c r="K267" s="4" t="inlineStr">
@@ -19926,7 +20204,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M267" s="8" t="n">
+      <c r="M267" s="6" t="n">
         <v>28.300854</v>
       </c>
       <c r="N267" s="4" t="inlineStr">
@@ -19992,7 +20270,7 @@
         </is>
       </c>
       <c r="I268" s="4" t="inlineStr"/>
-      <c r="J268" s="7" t="n">
+      <c r="J268" s="5" t="n">
         <v>61</v>
       </c>
       <c r="K268" s="4" t="inlineStr">
@@ -20005,7 +20283,7 @@
           <t>2010-01-01</t>
         </is>
       </c>
-      <c r="M268" s="8" t="n">
+      <c r="M268" s="6" t="n">
         <v>27223.228</v>
       </c>
       <c r="N268" s="4" t="inlineStr">
@@ -20071,7 +20349,7 @@
         </is>
       </c>
       <c r="I269" s="4" t="inlineStr"/>
-      <c r="J269" s="7" t="n">
+      <c r="J269" s="5" t="n">
         <v>61</v>
       </c>
       <c r="K269" s="4" t="inlineStr">
@@ -20084,7 +20362,7 @@
           <t>2010-01-01</t>
         </is>
       </c>
-      <c r="M269" s="8" t="n">
+      <c r="M269" s="6" t="n">
         <v>11777.99098</v>
       </c>
       <c r="N269" s="4" t="inlineStr">
@@ -20146,20 +20424,26 @@
       </c>
       <c r="H270" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I270" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J270" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K270" s="4" t="inlineStr"/>
-      <c r="L270" s="4" t="inlineStr"/>
-      <c r="M270" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I270" s="4" t="inlineStr"/>
+      <c r="J270" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="K270" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L270" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M270" s="6" t="n">
+        <v>320634.9337</v>
+      </c>
       <c r="N270" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PPPGDPVEA619NUPN</t>
@@ -20223,7 +20507,7 @@
         </is>
       </c>
       <c r="I271" s="4" t="inlineStr"/>
-      <c r="J271" s="7" t="n">
+      <c r="J271" s="5" t="n">
         <v>61</v>
       </c>
       <c r="K271" s="4" t="inlineStr">
@@ -20236,7 +20520,7 @@
           <t>2010-01-01</t>
         </is>
       </c>
-      <c r="M271" s="8" t="n">
+      <c r="M271" s="6" t="n">
         <v>3.155532204</v>
       </c>
       <c r="N271" s="4" t="inlineStr">
@@ -20302,7 +20586,7 @@
         </is>
       </c>
       <c r="I272" s="4" t="inlineStr"/>
-      <c r="J272" s="7" t="n">
+      <c r="J272" s="5" t="n">
         <v>21</v>
       </c>
       <c r="K272" s="4" t="inlineStr">
@@ -20315,7 +20599,7 @@
           <t>2022-01-01</t>
         </is>
       </c>
-      <c r="M272" s="7" t="n">
+      <c r="M272" s="5" t="n">
         <v>4890168</v>
       </c>
       <c r="N272" s="4" t="inlineStr">
@@ -20385,7 +20669,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J273" s="7" t="n">
+      <c r="J273" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K273" s="4" t="inlineStr"/>
@@ -20454,7 +20738,7 @@
         </is>
       </c>
       <c r="I274" s="4" t="inlineStr"/>
-      <c r="J274" s="7" t="n">
+      <c r="J274" s="5" t="n">
         <v>302</v>
       </c>
       <c r="K274" s="4" t="inlineStr">
@@ -20467,7 +20751,7 @@
           <t>2019-02-01</t>
         </is>
       </c>
-      <c r="M274" s="8" t="n">
+      <c r="M274" s="6" t="n">
         <v>0.68</v>
       </c>
       <c r="N274" s="4" t="inlineStr">
@@ -20533,7 +20817,7 @@
         </is>
       </c>
       <c r="I275" s="4" t="inlineStr"/>
-      <c r="J275" s="7" t="n">
+      <c r="J275" s="5" t="n">
         <v>61</v>
       </c>
       <c r="K275" s="4" t="inlineStr">
@@ -20546,7 +20830,7 @@
           <t>2010-01-01</t>
         </is>
       </c>
-      <c r="M275" s="8" t="n">
+      <c r="M275" s="6" t="n">
         <v>9070.606092</v>
       </c>
       <c r="N275" s="4" t="inlineStr">
@@ -20608,20 +20892,26 @@
       </c>
       <c r="H276" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I276" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J276" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K276" s="4" t="inlineStr"/>
-      <c r="L276" s="4" t="inlineStr"/>
-      <c r="M276" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I276" s="4" t="inlineStr"/>
+      <c r="J276" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="K276" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L276" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M276" s="6" t="n">
+        <v>10670.87232</v>
+      </c>
       <c r="N276" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RGDPEQVEA626NUPN</t>
@@ -20685,7 +20975,7 @@
         </is>
       </c>
       <c r="I277" s="4" t="inlineStr"/>
-      <c r="J277" s="7" t="n">
+      <c r="J277" s="5" t="n">
         <v>74</v>
       </c>
       <c r="K277" s="4" t="inlineStr">
@@ -20698,7 +20988,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M277" s="8" t="n">
+      <c r="M277" s="6" t="n">
         <v>2528.005859375</v>
       </c>
       <c r="N277" s="4" t="inlineStr">
@@ -20764,7 +21054,7 @@
         </is>
       </c>
       <c r="I278" s="4" t="inlineStr"/>
-      <c r="J278" s="7" t="n">
+      <c r="J278" s="5" t="n">
         <v>61</v>
       </c>
       <c r="K278" s="4" t="inlineStr">
@@ -20777,7 +21067,7 @@
           <t>2010-01-01</t>
         </is>
       </c>
-      <c r="M278" s="8" t="n">
+      <c r="M278" s="6" t="n">
         <v>9061.718438</v>
       </c>
       <c r="N278" s="4" t="inlineStr">
@@ -20843,7 +21133,7 @@
         </is>
       </c>
       <c r="I279" s="4" t="inlineStr"/>
-      <c r="J279" s="7" t="n">
+      <c r="J279" s="5" t="n">
         <v>61</v>
       </c>
       <c r="K279" s="4" t="inlineStr">
@@ -20856,7 +21146,7 @@
           <t>2010-01-01</t>
         </is>
       </c>
-      <c r="M279" s="8" t="n">
+      <c r="M279" s="6" t="n">
         <v>9070.929923</v>
       </c>
       <c r="N279" s="4" t="inlineStr">
@@ -20918,20 +21208,26 @@
       </c>
       <c r="H280" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I280" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J280" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K280" s="4" t="inlineStr"/>
-      <c r="L280" s="4" t="inlineStr"/>
-      <c r="M280" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I280" s="4" t="inlineStr"/>
+      <c r="J280" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="K280" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L280" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M280" s="6" t="n">
+        <v>19492.28703</v>
+      </c>
       <c r="N280" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RGDPLWVEA627NUPN</t>
@@ -20995,7 +21291,7 @@
         </is>
       </c>
       <c r="I281" s="4" t="inlineStr"/>
-      <c r="J281" s="7" t="n">
+      <c r="J281" s="5" t="n">
         <v>74</v>
       </c>
       <c r="K281" s="4" t="inlineStr">
@@ -21008,7 +21304,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M281" s="8" t="n">
+      <c r="M281" s="6" t="n">
         <v>5304.27978515625</v>
       </c>
       <c r="N281" s="4" t="inlineStr">
@@ -21074,7 +21370,7 @@
         </is>
       </c>
       <c r="I282" s="4" t="inlineStr"/>
-      <c r="J282" s="7" t="n">
+      <c r="J282" s="5" t="n">
         <v>74</v>
       </c>
       <c r="K282" s="4" t="inlineStr">
@@ -21087,7 +21383,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M282" s="8" t="n">
+      <c r="M282" s="6" t="n">
         <v>4501.99462890625</v>
       </c>
       <c r="N282" s="4" t="inlineStr">
@@ -21149,20 +21445,26 @@
       </c>
       <c r="H283" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I283" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J283" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K283" s="4" t="inlineStr"/>
-      <c r="L283" s="4" t="inlineStr"/>
-      <c r="M283" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I283" s="4" t="inlineStr"/>
+      <c r="J283" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="K283" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L283" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M283" s="6" t="n">
+        <v>25811.10218</v>
+      </c>
       <c r="N283" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RGDPTEVEA629NUPN</t>
@@ -21222,20 +21524,26 @@
       </c>
       <c r="H284" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I284" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J284" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K284" s="4" t="inlineStr"/>
-      <c r="L284" s="4" t="inlineStr"/>
-      <c r="M284" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I284" s="4" t="inlineStr"/>
+      <c r="J284" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="K284" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L284" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M284" s="6" t="n">
+        <v>13.36670232</v>
+      </c>
       <c r="N284" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RGDPTHVEA630NUPN</t>
@@ -21303,7 +21611,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J285" s="7" t="n">
+      <c r="J285" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K285" s="4" t="inlineStr"/>
@@ -21368,20 +21676,26 @@
       </c>
       <c r="H286" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I286" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J286" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K286" s="4" t="inlineStr"/>
-      <c r="L286" s="4" t="inlineStr"/>
-      <c r="M286" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I286" s="4" t="inlineStr"/>
+      <c r="J286" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="K286" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L286" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M286" s="6" t="n">
+        <v>19511.40489</v>
+      </c>
       <c r="N286" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RGDPWOVEA627NUPN</t>
@@ -21449,7 +21763,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J287" s="7" t="n">
+      <c r="J287" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K287" s="4" t="inlineStr"/>
@@ -21522,7 +21836,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J288" s="7" t="n">
+      <c r="J288" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K288" s="4" t="inlineStr"/>
@@ -21591,7 +21905,7 @@
         </is>
       </c>
       <c r="I289" s="4" t="inlineStr"/>
-      <c r="J289" s="7" t="n">
+      <c r="J289" s="5" t="n">
         <v>74</v>
       </c>
       <c r="K289" s="4" t="inlineStr">
@@ -21604,7 +21918,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M289" s="8" t="n">
+      <c r="M289" s="6" t="n">
         <v>119927.1796875</v>
       </c>
       <c r="N289" s="4" t="inlineStr">
@@ -21670,7 +21984,7 @@
         </is>
       </c>
       <c r="I290" s="4" t="inlineStr"/>
-      <c r="J290" s="7" t="n">
+      <c r="J290" s="5" t="n">
         <v>70</v>
       </c>
       <c r="K290" s="4" t="inlineStr">
@@ -21683,7 +21997,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M290" s="8" t="n">
+      <c r="M290" s="6" t="n">
         <v>1.22892010211945</v>
       </c>
       <c r="N290" s="4" t="inlineStr">
@@ -21753,7 +22067,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J291" s="7" t="n">
+      <c r="J291" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K291" s="4" t="inlineStr"/>
@@ -21826,7 +22140,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J292" s="7" t="n">
+      <c r="J292" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K292" s="4" t="inlineStr"/>
@@ -21899,7 +22213,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J293" s="7" t="n">
+      <c r="J293" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K293" s="4" t="inlineStr"/>
@@ -21964,20 +22278,26 @@
       </c>
       <c r="H294" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I294" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J294" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K294" s="4" t="inlineStr"/>
-      <c r="L294" s="4" t="inlineStr"/>
-      <c r="M294" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I294" s="4" t="inlineStr"/>
+      <c r="J294" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="K294" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L294" s="4" t="inlineStr">
+        <is>
+          <t>2016-01-01</t>
+        </is>
+      </c>
+      <c r="M294" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="N294" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SDVENA475SCEN</t>
@@ -22041,7 +22361,7 @@
         </is>
       </c>
       <c r="I295" s="4" t="inlineStr"/>
-      <c r="J295" s="7" t="n">
+      <c r="J295" s="5" t="n">
         <v>9</v>
       </c>
       <c r="K295" s="4" t="inlineStr">
@@ -22054,7 +22374,7 @@
           <t>2022-01-01</t>
         </is>
       </c>
-      <c r="M295" s="8" t="n">
+      <c r="M295" s="6" t="n">
         <v>97.59999847412109</v>
       </c>
       <c r="N295" s="4" t="inlineStr">
@@ -22124,7 +22444,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J296" s="7" t="n">
+      <c r="J296" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K296" s="4" t="inlineStr"/>
@@ -22189,20 +22509,26 @@
       </c>
       <c r="H297" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I297" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J297" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K297" s="4" t="inlineStr"/>
-      <c r="L297" s="4" t="inlineStr"/>
-      <c r="M297" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I297" s="4" t="inlineStr"/>
+      <c r="J297" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="K297" s="4" t="inlineStr">
+        <is>
+          <t>1971-01-01</t>
+        </is>
+      </c>
+      <c r="L297" s="4" t="inlineStr">
+        <is>
+          <t>2017-01-01</t>
+        </is>
+      </c>
+      <c r="M297" s="6" t="n">
+        <v>1.0806200504303</v>
+      </c>
       <c r="N297" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SEENRSECOFMZSVEN</t>
@@ -22262,20 +22588,26 @@
       </c>
       <c r="H298" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I298" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J298" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K298" s="4" t="inlineStr"/>
-      <c r="L298" s="4" t="inlineStr"/>
-      <c r="M298" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I298" s="4" t="inlineStr"/>
+      <c r="J298" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K298" s="4" t="inlineStr">
+        <is>
+          <t>1986-01-01</t>
+        </is>
+      </c>
+      <c r="L298" s="4" t="inlineStr">
+        <is>
+          <t>2008-01-01</t>
+        </is>
+      </c>
+      <c r="M298" s="6" t="n">
+        <v>1.40991997718811</v>
+      </c>
       <c r="N298" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SEENRTERTFMZSVEN</t>
@@ -22339,7 +22671,7 @@
         </is>
       </c>
       <c r="I299" s="4" t="inlineStr"/>
-      <c r="J299" s="7" t="n">
+      <c r="J299" s="5" t="n">
         <v>13</v>
       </c>
       <c r="K299" s="4" t="inlineStr">
@@ -22352,7 +22684,7 @@
           <t>2006-01-01</t>
         </is>
       </c>
-      <c r="M299" s="8" t="n">
+      <c r="M299" s="6" t="n">
         <v>44.7</v>
       </c>
       <c r="N299" s="4" t="inlineStr">
@@ -22418,7 +22750,7 @@
         </is>
       </c>
       <c r="I300" s="4" t="inlineStr"/>
-      <c r="J300" s="7" t="n">
+      <c r="J300" s="5" t="n">
         <v>35</v>
       </c>
       <c r="K300" s="4" t="inlineStr">
@@ -22431,7 +22763,7 @@
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="M300" s="8" t="n">
+      <c r="M300" s="6" t="n">
         <v>49.171</v>
       </c>
       <c r="N300" s="4" t="inlineStr">
@@ -22497,7 +22829,7 @@
         </is>
       </c>
       <c r="I301" s="4" t="inlineStr"/>
-      <c r="J301" s="7" t="n">
+      <c r="J301" s="5" t="n">
         <v>35</v>
       </c>
       <c r="K301" s="4" t="inlineStr">
@@ -22510,7 +22842,7 @@
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="M301" s="8" t="n">
+      <c r="M301" s="6" t="n">
         <v>10.444</v>
       </c>
       <c r="N301" s="4" t="inlineStr">
@@ -22576,7 +22908,7 @@
         </is>
       </c>
       <c r="I302" s="4" t="inlineStr"/>
-      <c r="J302" s="7" t="n">
+      <c r="J302" s="5" t="n">
         <v>12</v>
       </c>
       <c r="K302" s="4" t="inlineStr">
@@ -22589,7 +22921,7 @@
           <t>2017-01-01</t>
         </is>
       </c>
-      <c r="M302" s="7" t="n">
+      <c r="M302" s="5" t="n">
         <v>-3266243</v>
       </c>
       <c r="N302" s="4" t="inlineStr">
@@ -22655,7 +22987,7 @@
         </is>
       </c>
       <c r="I303" s="4" t="inlineStr"/>
-      <c r="J303" s="7" t="n">
+      <c r="J303" s="5" t="n">
         <v>53</v>
       </c>
       <c r="K303" s="4" t="inlineStr">
@@ -22668,7 +23000,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M303" s="7" t="n">
+      <c r="M303" s="5" t="n">
         <v>29336</v>
       </c>
       <c r="N303" s="4" t="inlineStr">
@@ -22738,7 +23070,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J304" s="7" t="n">
+      <c r="J304" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K304" s="4" t="inlineStr"/>
@@ -22807,7 +23139,7 @@
         </is>
       </c>
       <c r="I305" s="4" t="inlineStr"/>
-      <c r="J305" s="7" t="n">
+      <c r="J305" s="5" t="n">
         <v>65</v>
       </c>
       <c r="K305" s="4" t="inlineStr">
@@ -22820,7 +23152,7 @@
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="M305" s="8" t="n">
+      <c r="M305" s="6" t="n">
         <v>73.18899999999999</v>
       </c>
       <c r="N305" s="4" t="inlineStr">
@@ -22886,7 +23218,7 @@
         </is>
       </c>
       <c r="I306" s="4" t="inlineStr"/>
-      <c r="J306" s="7" t="n">
+      <c r="J306" s="5" t="n">
         <v>65</v>
       </c>
       <c r="K306" s="4" t="inlineStr">
@@ -22899,7 +23231,7 @@
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="M306" s="8" t="n">
+      <c r="M306" s="6" t="n">
         <v>15.231</v>
       </c>
       <c r="N306" s="4" t="inlineStr">
@@ -22965,7 +23297,7 @@
         </is>
       </c>
       <c r="I307" s="4" t="inlineStr"/>
-      <c r="J307" s="7" t="n">
+      <c r="J307" s="5" t="n">
         <v>65</v>
       </c>
       <c r="K307" s="4" t="inlineStr">
@@ -22978,7 +23310,7 @@
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="M307" s="8" t="n">
+      <c r="M307" s="6" t="n">
         <v>21.2</v>
       </c>
       <c r="N307" s="4" t="inlineStr">
@@ -23044,7 +23376,7 @@
         </is>
       </c>
       <c r="I308" s="4" t="inlineStr"/>
-      <c r="J308" s="7" t="n">
+      <c r="J308" s="5" t="n">
         <v>65</v>
       </c>
       <c r="K308" s="4" t="inlineStr">
@@ -23057,7 +23389,7 @@
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="M308" s="8" t="n">
+      <c r="M308" s="6" t="n">
         <v>72.673</v>
       </c>
       <c r="N308" s="4" t="inlineStr">
@@ -23123,7 +23455,7 @@
         </is>
       </c>
       <c r="I309" s="4" t="inlineStr"/>
-      <c r="J309" s="7" t="n">
+      <c r="J309" s="5" t="n">
         <v>65</v>
       </c>
       <c r="K309" s="4" t="inlineStr">
@@ -23136,7 +23468,7 @@
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="M309" s="8" t="n">
+      <c r="M309" s="6" t="n">
         <v>2.077</v>
       </c>
       <c r="N309" s="4" t="inlineStr">
@@ -23198,20 +23530,26 @@
       </c>
       <c r="H310" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I310" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J310" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K310" s="4" t="inlineStr"/>
-      <c r="L310" s="4" t="inlineStr"/>
-      <c r="M310" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I310" s="4" t="inlineStr"/>
+      <c r="J310" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="K310" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L310" s="4" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M310" s="6" t="n">
+        <v>24.9159954154898</v>
+      </c>
       <c r="N310" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SPPOP0014TOZSVEN</t>
@@ -23279,7 +23617,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J311" s="7" t="n">
+      <c r="J311" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K311" s="4" t="inlineStr"/>
@@ -23348,7 +23686,7 @@
         </is>
       </c>
       <c r="I312" s="4" t="inlineStr"/>
-      <c r="J312" s="7" t="n">
+      <c r="J312" s="5" t="n">
         <v>66</v>
       </c>
       <c r="K312" s="4" t="inlineStr">
@@ -23361,7 +23699,7 @@
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="M312" s="8" t="n">
+      <c r="M312" s="6" t="n">
         <v>10.0182554931645</v>
       </c>
       <c r="N312" s="4" t="inlineStr">
@@ -23427,7 +23765,7 @@
         </is>
       </c>
       <c r="I313" s="4" t="inlineStr"/>
-      <c r="J313" s="7" t="n">
+      <c r="J313" s="5" t="n">
         <v>66</v>
       </c>
       <c r="K313" s="4" t="inlineStr">
@@ -23440,7 +23778,7 @@
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="M313" s="8" t="n">
+      <c r="M313" s="6" t="n">
         <v>15.397128883349</v>
       </c>
       <c r="N313" s="4" t="inlineStr">
@@ -23506,7 +23844,7 @@
         </is>
       </c>
       <c r="I314" s="4" t="inlineStr"/>
-      <c r="J314" s="7" t="n">
+      <c r="J314" s="5" t="n">
         <v>65</v>
       </c>
       <c r="K314" s="4" t="inlineStr">
@@ -23519,7 +23857,7 @@
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="M314" s="8" t="n">
+      <c r="M314" s="6" t="n">
         <v>0.39124515392802</v>
       </c>
       <c r="N314" s="4" t="inlineStr">
@@ -23589,7 +23927,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J315" s="7" t="n">
+      <c r="J315" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K315" s="4" t="inlineStr"/>
@@ -23662,7 +24000,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J316" s="7" t="n">
+      <c r="J316" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K316" s="4" t="inlineStr"/>
@@ -23735,7 +24073,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J317" s="7" t="n">
+      <c r="J317" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K317" s="4" t="inlineStr"/>
@@ -23808,7 +24146,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J318" s="7" t="n">
+      <c r="J318" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K318" s="4" t="inlineStr"/>
@@ -23881,7 +24219,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J319" s="7" t="n">
+      <c r="J319" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K319" s="4" t="inlineStr"/>
@@ -23954,7 +24292,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J320" s="7" t="n">
+      <c r="J320" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K320" s="4" t="inlineStr"/>
@@ -24027,7 +24365,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J321" s="7" t="n">
+      <c r="J321" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K321" s="4" t="inlineStr"/>
@@ -24100,7 +24438,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J322" s="7" t="n">
+      <c r="J322" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K322" s="4" t="inlineStr"/>
@@ -24173,7 +24511,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J323" s="7" t="n">
+      <c r="J323" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K323" s="4" t="inlineStr"/>
@@ -24246,7 +24584,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J324" s="7" t="n">
+      <c r="J324" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K324" s="4" t="inlineStr"/>
@@ -24319,7 +24657,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J325" s="7" t="n">
+      <c r="J325" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K325" s="4" t="inlineStr"/>
@@ -24388,7 +24726,7 @@
         </is>
       </c>
       <c r="I326" s="4" t="inlineStr"/>
-      <c r="J326" s="7" t="n">
+      <c r="J326" s="5" t="n">
         <v>387</v>
       </c>
       <c r="K326" s="4" t="inlineStr">
@@ -24401,7 +24739,7 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="M326" s="7" t="n">
+      <c r="M326" s="5" t="n">
         <v>7</v>
       </c>
       <c r="N326" s="4" t="inlineStr">
@@ -24471,7 +24809,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J327" s="7" t="n">
+      <c r="J327" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K327" s="4" t="inlineStr"/>
@@ -24544,7 +24882,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J328" s="7" t="n">
+      <c r="J328" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K328" s="4" t="inlineStr"/>
@@ -24617,7 +24955,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J329" s="7" t="n">
+      <c r="J329" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K329" s="4" t="inlineStr"/>
@@ -24690,7 +25028,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J330" s="7" t="n">
+      <c r="J330" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K330" s="4" t="inlineStr"/>
@@ -24763,7 +25101,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J331" s="7" t="n">
+      <c r="J331" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K331" s="4" t="inlineStr"/>
@@ -24836,7 +25174,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J332" s="7" t="n">
+      <c r="J332" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K332" s="4" t="inlineStr"/>
@@ -24909,7 +25247,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J333" s="7" t="n">
+      <c r="J333" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K333" s="4" t="inlineStr"/>
@@ -24982,7 +25320,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J334" s="7" t="n">
+      <c r="J334" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K334" s="4" t="inlineStr"/>
@@ -25047,20 +25385,26 @@
       </c>
       <c r="H335" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I335" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J335" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K335" s="4" t="inlineStr"/>
-      <c r="L335" s="4" t="inlineStr"/>
-      <c r="M335" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I335" s="4" t="inlineStr"/>
+      <c r="J335" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="K335" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L335" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M335" s="5" t="n">
+        <v>6</v>
+      </c>
       <c r="N335" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/UTVENA475SCEN</t>
@@ -25128,7 +25472,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J336" s="7" t="n">
+      <c r="J336" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K336" s="4" t="inlineStr"/>
@@ -25201,7 +25545,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J337" s="7" t="n">
+      <c r="J337" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K337" s="4" t="inlineStr"/>
@@ -25274,7 +25618,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J338" s="7" t="n">
+      <c r="J338" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K338" s="4" t="inlineStr"/>
@@ -25347,7 +25691,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J339" s="7" t="n">
+      <c r="J339" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K339" s="4" t="inlineStr"/>
@@ -25412,20 +25756,26 @@
       </c>
       <c r="H340" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I340" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J340" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K340" s="4" t="inlineStr"/>
-      <c r="L340" s="4" t="inlineStr"/>
-      <c r="M340" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I340" s="4" t="inlineStr"/>
+      <c r="J340" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="K340" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L340" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M340" s="5" t="n">
+        <v>10429</v>
+      </c>
       <c r="N340" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCACNUM</t>
@@ -25493,7 +25843,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J341" s="7" t="n">
+      <c r="J341" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K341" s="4" t="inlineStr"/>
@@ -25566,7 +25916,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J342" s="7" t="n">
+      <c r="J342" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K342" s="4" t="inlineStr"/>
@@ -25631,20 +25981,26 @@
       </c>
       <c r="H343" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I343" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J343" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K343" s="4" t="inlineStr"/>
-      <c r="L343" s="4" t="inlineStr"/>
-      <c r="M343" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I343" s="4" t="inlineStr"/>
+      <c r="J343" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="K343" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L343" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M343" s="5" t="n">
+        <v>31695711</v>
+      </c>
       <c r="N343" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCAODCNUM</t>
@@ -25712,7 +26068,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J344" s="7" t="n">
+      <c r="J344" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K344" s="4" t="inlineStr"/>
@@ -25785,7 +26141,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J345" s="7" t="n">
+      <c r="J345" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K345" s="4" t="inlineStr"/>
@@ -25854,7 +26210,7 @@
         </is>
       </c>
       <c r="I346" s="4" t="inlineStr"/>
-      <c r="J346" s="7" t="n">
+      <c r="J346" s="5" t="n">
         <v>11</v>
       </c>
       <c r="K346" s="4" t="inlineStr">
@@ -25867,7 +26223,7 @@
           <t>2014-01-01</t>
         </is>
       </c>
-      <c r="M346" s="7" t="n">
+      <c r="M346" s="5" t="n">
         <v>1769451</v>
       </c>
       <c r="N346" s="4" t="inlineStr">
@@ -25937,7 +26293,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J347" s="7" t="n">
+      <c r="J347" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K347" s="4" t="inlineStr"/>
@@ -26010,7 +26366,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J348" s="7" t="n">
+      <c r="J348" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K348" s="4" t="inlineStr"/>
@@ -26083,7 +26439,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J349" s="7" t="n">
+      <c r="J349" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K349" s="4" t="inlineStr"/>
@@ -26156,7 +26512,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J350" s="7" t="n">
+      <c r="J350" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K350" s="4" t="inlineStr"/>
@@ -26229,7 +26585,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J351" s="7" t="n">
+      <c r="J351" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K351" s="4" t="inlineStr"/>
@@ -26302,7 +26658,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J352" s="7" t="n">
+      <c r="J352" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K352" s="4" t="inlineStr"/>
@@ -26375,7 +26731,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J353" s="7" t="n">
+      <c r="J353" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K353" s="4" t="inlineStr"/>
@@ -26440,20 +26796,26 @@
       </c>
       <c r="H354" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I354" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J354" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K354" s="4" t="inlineStr"/>
-      <c r="L354" s="4" t="inlineStr"/>
-      <c r="M354" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I354" s="4" t="inlineStr"/>
+      <c r="J354" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="K354" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L354" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M354" s="6" t="n">
+        <v>0.130378096</v>
+      </c>
       <c r="N354" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCBODMFKNUM</t>
@@ -26521,7 +26883,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J355" s="7" t="n">
+      <c r="J355" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K355" s="4" t="inlineStr"/>
@@ -26594,7 +26956,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J356" s="7" t="n">
+      <c r="J356" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K356" s="4" t="inlineStr"/>
@@ -26667,7 +27029,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J357" s="7" t="n">
+      <c r="J357" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K357" s="4" t="inlineStr"/>
@@ -26740,7 +27102,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J358" s="7" t="n">
+      <c r="J358" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K358" s="4" t="inlineStr"/>
@@ -26805,20 +27167,26 @@
       </c>
       <c r="H359" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I359" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J359" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K359" s="4" t="inlineStr"/>
-      <c r="L359" s="4" t="inlineStr"/>
-      <c r="M359" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I359" s="4" t="inlineStr"/>
+      <c r="J359" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="K359" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L359" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M359" s="6" t="n">
+        <v>24601704.6666667</v>
+      </c>
       <c r="N359" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCDODCHPENUM</t>
@@ -26886,7 +27254,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J360" s="7" t="n">
+      <c r="J360" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K360" s="4" t="inlineStr"/>
@@ -26959,7 +27327,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J361" s="7" t="n">
+      <c r="J361" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K361" s="4" t="inlineStr"/>
@@ -27024,20 +27392,26 @@
       </c>
       <c r="H362" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I362" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J362" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K362" s="4" t="inlineStr"/>
-      <c r="L362" s="4" t="inlineStr"/>
-      <c r="M362" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I362" s="4" t="inlineStr"/>
+      <c r="J362" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="K362" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L362" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M362" s="6" t="n">
+        <v>66.83665774000001</v>
+      </c>
       <c r="N362" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCDODCSPNUM</t>
@@ -27105,7 +27479,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J363" s="7" t="n">
+      <c r="J363" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K363" s="4" t="inlineStr"/>
@@ -27178,7 +27552,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J364" s="7" t="n">
+      <c r="J364" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K364" s="4" t="inlineStr"/>
@@ -27247,7 +27621,7 @@
         </is>
       </c>
       <c r="I365" s="4" t="inlineStr"/>
-      <c r="J365" s="7" t="n">
+      <c r="J365" s="5" t="n">
         <v>11</v>
       </c>
       <c r="K365" s="4" t="inlineStr">
@@ -27260,7 +27634,7 @@
           <t>2015-01-01</t>
         </is>
       </c>
-      <c r="M365" s="7" t="n">
+      <c r="M365" s="5" t="n">
         <v>26</v>
       </c>
       <c r="N365" s="4" t="inlineStr">
@@ -27330,7 +27704,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J366" s="7" t="n">
+      <c r="J366" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K366" s="4" t="inlineStr"/>
@@ -27403,7 +27777,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J367" s="7" t="n">
+      <c r="J367" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K367" s="4" t="inlineStr"/>
@@ -27476,7 +27850,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J368" s="7" t="n">
+      <c r="J368" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K368" s="4" t="inlineStr"/>
@@ -27545,7 +27919,7 @@
         </is>
       </c>
       <c r="I369" s="4" t="inlineStr"/>
-      <c r="J369" s="7" t="n">
+      <c r="J369" s="5" t="n">
         <v>10</v>
       </c>
       <c r="K369" s="4" t="inlineStr">
@@ -27558,7 +27932,7 @@
           <t>2014-01-01</t>
         </is>
       </c>
-      <c r="M369" s="8" t="n">
+      <c r="M369" s="6" t="n">
         <v>68.50582168130001</v>
       </c>
       <c r="N369" s="4" t="inlineStr">
@@ -27628,7 +28002,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J370" s="7" t="n">
+      <c r="J370" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K370" s="4" t="inlineStr"/>
@@ -27701,7 +28075,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J371" s="7" t="n">
+      <c r="J371" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K371" s="4" t="inlineStr"/>
@@ -27774,7 +28148,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J372" s="7" t="n">
+      <c r="J372" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K372" s="4" t="inlineStr"/>
@@ -27847,7 +28221,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J373" s="7" t="n">
+      <c r="J373" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K373" s="4" t="inlineStr"/>
@@ -27920,7 +28294,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J374" s="7" t="n">
+      <c r="J374" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K374" s="4" t="inlineStr"/>
@@ -27993,7 +28367,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J375" s="7" t="n">
+      <c r="J375" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K375" s="4" t="inlineStr"/>
@@ -28062,7 +28436,7 @@
         </is>
       </c>
       <c r="I376" s="4" t="inlineStr"/>
-      <c r="J376" s="7" t="n">
+      <c r="J376" s="5" t="n">
         <v>11</v>
       </c>
       <c r="K376" s="4" t="inlineStr">
@@ -28075,7 +28449,7 @@
           <t>2015-01-01</t>
         </is>
       </c>
-      <c r="M376" s="8" t="n">
+      <c r="M376" s="6" t="n">
         <v>37322701822.99</v>
       </c>
       <c r="N376" s="4" t="inlineStr">
@@ -28145,7 +28519,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J377" s="7" t="n">
+      <c r="J377" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K377" s="4" t="inlineStr"/>
@@ -28218,7 +28592,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J378" s="7" t="n">
+      <c r="J378" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K378" s="4" t="inlineStr"/>
@@ -28291,7 +28665,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J379" s="7" t="n">
+      <c r="J379" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K379" s="4" t="inlineStr"/>
@@ -28356,20 +28730,26 @@
       </c>
       <c r="H380" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I380" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J380" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K380" s="4" t="inlineStr"/>
-      <c r="L380" s="4" t="inlineStr"/>
-      <c r="M380" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I380" s="4" t="inlineStr"/>
+      <c r="J380" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="K380" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L380" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M380" s="6" t="n">
+        <v>1078.0378178439</v>
+      </c>
       <c r="N380" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCNODCANUM</t>
@@ -28433,7 +28813,7 @@
         </is>
       </c>
       <c r="I381" s="4" t="inlineStr"/>
-      <c r="J381" s="7" t="n">
+      <c r="J381" s="5" t="n">
         <v>11</v>
       </c>
       <c r="K381" s="4" t="inlineStr">
@@ -28446,7 +28826,7 @@
           <t>2015-01-01</t>
         </is>
       </c>
-      <c r="M381" s="7" t="n">
+      <c r="M381" s="5" t="n">
         <v>23665733</v>
       </c>
       <c r="N381" s="4" t="inlineStr">
@@ -28516,7 +28896,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J382" s="7" t="n">
+      <c r="J382" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K382" s="4" t="inlineStr"/>
@@ -28589,7 +28969,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J383" s="7" t="n">
+      <c r="J383" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K383" s="4" t="inlineStr"/>
@@ -28662,7 +29042,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J384" s="7" t="n">
+      <c r="J384" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K384" s="4" t="inlineStr"/>
@@ -28735,7 +29115,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J385" s="7" t="n">
+      <c r="J385" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K385" s="4" t="inlineStr"/>
@@ -28800,20 +29180,26 @@
       </c>
       <c r="H386" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I386" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J386" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K386" s="4" t="inlineStr"/>
-      <c r="L386" s="4" t="inlineStr"/>
-      <c r="M386" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I386" s="4" t="inlineStr"/>
+      <c r="J386" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="K386" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L386" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M386" s="6" t="n">
+        <v>7404689.58333333</v>
+      </c>
       <c r="N386" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCRODCHPENUM</t>
@@ -28881,7 +29267,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J387" s="7" t="n">
+      <c r="J387" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K387" s="4" t="inlineStr"/>
@@ -28954,7 +29340,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J388" s="7" t="n">
+      <c r="J388" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K388" s="4" t="inlineStr"/>
@@ -29027,7 +29413,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J389" s="7" t="n">
+      <c r="J389" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K389" s="4" t="inlineStr"/>
@@ -29092,20 +29478,26 @@
       </c>
       <c r="H390" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I390" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J390" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K390" s="4" t="inlineStr"/>
-      <c r="L390" s="4" t="inlineStr"/>
-      <c r="M390" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I390" s="4" t="inlineStr"/>
+      <c r="J390" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K390" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L390" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M390" s="6" t="n">
+        <v>37.8908354029</v>
+      </c>
       <c r="N390" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCSODCGGDPPT</t>
@@ -29165,20 +29557,26 @@
       </c>
       <c r="H391" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I391" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J391" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K391" s="4" t="inlineStr"/>
-      <c r="L391" s="4" t="inlineStr"/>
-      <c r="M391" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I391" s="4" t="inlineStr"/>
+      <c r="J391" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K391" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L391" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M391" s="6" t="n">
+        <v>0.8716582127</v>
+      </c>
       <c r="N391" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCSODCSGGDPPT</t>
@@ -29246,7 +29644,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J392" s="7" t="n">
+      <c r="J392" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K392" s="4" t="inlineStr"/>
@@ -29319,7 +29717,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J393" s="7" t="n">
+      <c r="J393" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K393" s="4" t="inlineStr"/>
@@ -29392,7 +29790,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J394" s="7" t="n">
+      <c r="J394" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K394" s="4" t="inlineStr"/>
@@ -29465,7 +29863,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J395" s="7" t="n">
+      <c r="J395" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K395" s="4" t="inlineStr"/>
@@ -29530,20 +29928,26 @@
       </c>
       <c r="H396" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I396" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J396" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K396" s="4" t="inlineStr"/>
-      <c r="L396" s="4" t="inlineStr"/>
-      <c r="M396" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I396" s="4" t="inlineStr"/>
+      <c r="J396" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="K396" s="4" t="inlineStr">
+        <is>
+          <t>2008-01-01</t>
+        </is>
+      </c>
+      <c r="L396" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M396" s="5" t="n">
+        <v>10753000000</v>
+      </c>
       <c r="N396" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCSODMFSXDC</t>
@@ -29611,7 +30015,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J397" s="7" t="n">
+      <c r="J397" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K397" s="4" t="inlineStr"/>
@@ -29676,20 +30080,26 @@
       </c>
       <c r="H398" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I398" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J398" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K398" s="4" t="inlineStr"/>
-      <c r="L398" s="4" t="inlineStr"/>
-      <c r="M398" s="4" t="n"/>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I398" s="4" t="inlineStr"/>
+      <c r="J398" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="K398" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L398" s="4" t="inlineStr">
+        <is>
+          <t>2016-01-01</t>
+        </is>
+      </c>
+      <c r="M398" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N398" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VIVENA475SCEN</t>
@@ -29757,7 +30167,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J399" s="7" t="n">
+      <c r="J399" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K399" s="4" t="inlineStr"/>
@@ -29830,7 +30240,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J400" s="7" t="n">
+      <c r="J400" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K400" s="4" t="inlineStr"/>
@@ -29903,7 +30313,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J401" s="7" t="n">
+      <c r="J401" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K401" s="4" t="inlineStr"/>
@@ -29976,7 +30386,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J402" s="7" t="n">
+      <c r="J402" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K402" s="4" t="inlineStr"/>
@@ -30049,7 +30459,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J403" s="7" t="n">
+      <c r="J403" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K403" s="4" t="inlineStr"/>
@@ -30122,7 +30532,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J404" s="7" t="n">
+      <c r="J404" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K404" s="4" t="inlineStr"/>
@@ -30195,7 +30605,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J405" s="7" t="n">
+      <c r="J405" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K405" s="4" t="inlineStr"/>
@@ -30268,7 +30678,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J406" s="7" t="n">
+      <c r="J406" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K406" s="4" t="inlineStr"/>
@@ -30337,7 +30747,7 @@
         </is>
       </c>
       <c r="I407" s="4" t="inlineStr"/>
-      <c r="J407" s="7" t="n">
+      <c r="J407" s="5" t="n">
         <v>291</v>
       </c>
       <c r="K407" s="4" t="inlineStr">
@@ -30350,7 +30760,7 @@
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="M407" s="8" t="n">
+      <c r="M407" s="6" t="n">
         <v>1.178428</v>
       </c>
       <c r="N407" s="4" t="inlineStr">
@@ -30412,20 +30822,26 @@
       </c>
       <c r="H408" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I408" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
-      <c r="J408" s="7" t="n">
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I408" s="4" t="inlineStr"/>
+      <c r="J408" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="K408" s="4" t="inlineStr">
+        <is>
+          <t>1996-01-01</t>
+        </is>
+      </c>
+      <c r="L408" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M408" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K408" s="4" t="inlineStr"/>
-      <c r="L408" s="4" t="inlineStr"/>
-      <c r="M408" s="4" t="n"/>
       <c r="N408" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/WUPIVEN</t>
@@ -30493,7 +30909,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J409" s="7" t="n">
+      <c r="J409" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K409" s="4" t="inlineStr"/>
@@ -30562,7 +30978,7 @@
         </is>
       </c>
       <c r="I410" s="4" t="inlineStr"/>
-      <c r="J410" s="7" t="n">
+      <c r="J410" s="5" t="n">
         <v>19</v>
       </c>
       <c r="K410" s="4" t="inlineStr">
@@ -30575,7 +30991,7 @@
           <t>2020-01-01</t>
         </is>
       </c>
-      <c r="M410" s="7" t="n">
+      <c r="M410" s="5" t="n">
         <v>3</v>
       </c>
       <c r="N410" s="4" t="inlineStr">
@@ -30645,7 +31061,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J411" s="7" t="n">
+      <c r="J411" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K411" s="4" t="inlineStr"/>
@@ -30718,7 +31134,7 @@
           <t>HTTP Error 403: Forbidden</t>
         </is>
       </c>
-      <c r="J412" s="7" t="n">
+      <c r="J412" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K412" s="4" t="inlineStr"/>
@@ -30787,7 +31203,7 @@
         </is>
       </c>
       <c r="I413" s="4" t="inlineStr"/>
-      <c r="J413" s="7" t="n">
+      <c r="J413" s="5" t="n">
         <v>74</v>
       </c>
       <c r="K413" s="4" t="inlineStr">
@@ -30800,7 +31216,7 @@
           <t>2023-01-01</t>
         </is>
       </c>
-      <c r="M413" s="8" t="n">
+      <c r="M413" s="6" t="n">
         <v>8.67714612014831</v>
       </c>
       <c r="N413" s="4" t="inlineStr">
@@ -30861,19 +31277,19 @@
     <row r="4" ht="16" customHeight="1"/>
     <row r="5" ht="8" customHeight="1"/>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Campo</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Organización</t>
         </is>
@@ -30885,7 +31301,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
@@ -30897,19 +31313,19 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Fecha generación</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
@@ -30921,7 +31337,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>URL fuente</t>
         </is>
@@ -30933,7 +31349,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>País</t>
         </is>
@@ -30945,33 +31361,33 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Número de series catalogadas</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="5" t="n">
         <v>407</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Número de series con datos</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
-        <v>92</v>
+      <c r="B14" s="5" t="n">
+        <v>151</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Número de registros</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
-        <v>13983</v>
+      <c r="B15" s="5" t="n">
+        <v>17027</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/fred/catalog/catalogo_dataset_web_ove_fred.xlsx
+++ b/assets/data/fred/catalog/catalogo_dataset_web_ove_fred.xlsx
@@ -1397,11 +1397,11 @@
       </c>
       <c r="I16" s="4" t="inlineStr"/>
       <c r="J16" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>1960-01-01</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="I102" s="4" t="inlineStr"/>
       <c r="J102" s="5" t="n">
-        <v>6653</v>
+        <v>6658</v>
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
@@ -8184,11 +8184,11 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="M102" s="6" t="n">
-        <v>736.0368999999999</v>
+        <v>744.7631</v>
       </c>
       <c r="N102" s="4" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="I104" s="4" t="inlineStr"/>
       <c r="J104" s="5" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
@@ -8342,11 +8342,11 @@
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M104" s="6" t="n">
-        <v>497.812779</v>
+        <v>567.7612820000001</v>
       </c>
       <c r="N104" s="4" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
       </c>
       <c r="I181" s="4" t="inlineStr"/>
       <c r="J181" s="5" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
@@ -14425,11 +14425,11 @@
       </c>
       <c r="L181" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M181" s="6" t="n">
-        <v>1525.18625</v>
+        <v>1815.327851</v>
       </c>
       <c r="N181" s="4" t="inlineStr">
         <is>
@@ -32108,7 +32108,7 @@
       </c>
       <c r="I405" s="4" t="inlineStr"/>
       <c r="J405" s="5" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K405" s="4" t="inlineStr">
         <is>
@@ -32117,11 +32117,11 @@
       </c>
       <c r="L405" s="4" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M405" s="6" t="n">
-        <v>20.79578</v>
+        <v>14.40196</v>
       </c>
       <c r="N405" s="4" t="inlineStr">
         <is>
@@ -32187,7 +32187,7 @@
       </c>
       <c r="I406" s="4" t="inlineStr"/>
       <c r="J406" s="5" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K406" s="4" t="inlineStr">
         <is>
@@ -32196,11 +32196,11 @@
       </c>
       <c r="L406" s="4" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M406" s="6" t="n">
-        <v>0.3119964</v>
+        <v>0.269383</v>
       </c>
       <c r="N406" s="4" t="inlineStr">
         <is>
@@ -32266,7 +32266,7 @@
       </c>
       <c r="I407" s="4" t="inlineStr"/>
       <c r="J407" s="5" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K407" s="4" t="inlineStr">
         <is>
@@ -32275,11 +32275,11 @@
       </c>
       <c r="L407" s="4" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M407" s="6" t="n">
-        <v>1.178428</v>
+        <v>0.6480882</v>
       </c>
       <c r="N407" s="4" t="inlineStr">
         <is>
@@ -32345,7 +32345,7 @@
       </c>
       <c r="I408" s="4" t="inlineStr"/>
       <c r="J408" s="5" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K408" s="4" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
       </c>
       <c r="L408" s="4" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M408" s="5" t="n">
@@ -32856,7 +32856,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
@@ -32923,7 +32923,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>35147</v>
+        <v>35160</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/fred/catalog/catalogo_dataset_web_ove_fred.xlsx
+++ b/assets/data/fred/catalog/catalogo_dataset_web_ove_fred.xlsx
@@ -1806,20 +1806,26 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr"/>
       <c r="J22" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="4" t="inlineStr"/>
-      <c r="L22" s="4" t="inlineStr"/>
-      <c r="M22" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M22" s="6" t="n">
+        <v>4.853227332</v>
+      </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CGPPPGVEA156NUPN</t>
@@ -2183,26 +2189,20 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J27" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>2023-01-01</t>
-        </is>
-      </c>
-      <c r="M27" s="6" t="n">
-        <v>0.449208825826645</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K27" s="4" t="inlineStr"/>
+      <c r="L27" s="4" t="inlineStr"/>
+      <c r="M27" s="4" t="n"/>
       <c r="N27" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CSHCCPVEA156NRUG</t>
@@ -2414,26 +2414,20 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J30" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>2023-01-01</t>
-        </is>
-      </c>
-      <c r="M30" s="6" t="n">
-        <v>-0.301709741353989</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K30" s="4" t="inlineStr"/>
+      <c r="L30" s="4" t="inlineStr"/>
+      <c r="M30" s="4" t="n"/>
       <c r="N30" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CSHMCPVEA156NRUG</t>
@@ -2639,20 +2633,26 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr"/>
       <c r="J33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="4" t="inlineStr"/>
-      <c r="L33" s="4" t="inlineStr"/>
-      <c r="M33" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M33" s="6" t="n">
+        <v>62.2520714</v>
+      </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CSPPPGVEA156NUPN</t>
@@ -3752,20 +3752,26 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr"/>
       <c r="J48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="4" t="inlineStr"/>
-      <c r="L48" s="4" t="inlineStr"/>
-      <c r="M48" s="4" t="n"/>
+        <v>48</v>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>1963-01-01</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M48" s="6" t="n">
+        <v>0.193082</v>
+      </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDI03VEA156NWDB</t>
@@ -3825,26 +3831,20 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I49" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J49" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="K49" s="4" t="inlineStr">
-        <is>
-          <t>1960-01-01</t>
-        </is>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>2013-01-01</t>
-        </is>
-      </c>
-      <c r="M49" s="6" t="n">
-        <v>69.07484000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K49" s="4" t="inlineStr"/>
+      <c r="L49" s="4" t="inlineStr"/>
+      <c r="M49" s="4" t="n"/>
       <c r="N49" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDI04VEA156NWDB</t>
@@ -4129,20 +4129,26 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I53" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr"/>
       <c r="J53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="4" t="inlineStr"/>
-      <c r="L53" s="4" t="inlineStr"/>
-      <c r="M53" s="4" t="n"/>
+        <v>30</v>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>1990-01-01</t>
+        </is>
+      </c>
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="M53" s="6" t="n">
+        <v>0.0001330999999999</v>
+      </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDI09VEA156NWDB</t>
@@ -4275,20 +4281,26 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I55" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr"/>
       <c r="J55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="4" t="inlineStr"/>
-      <c r="L55" s="4" t="inlineStr"/>
-      <c r="M55" s="4" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>2016-01-01</t>
+        </is>
+      </c>
+      <c r="M55" s="6" t="n">
+        <v>6.290333400000001</v>
+      </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDI11VEA156NWDB</t>
@@ -4348,26 +4360,20 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I56" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J56" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="K56" s="4" t="inlineStr">
-        <is>
-          <t>1960-01-01</t>
-        </is>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M56" s="6" t="n">
-        <v>39.51449</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K56" s="4" t="inlineStr"/>
+      <c r="L56" s="4" t="inlineStr"/>
+      <c r="M56" s="4" t="n"/>
       <c r="N56" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDI12VEA156NWDB</t>
@@ -4585,20 +4591,26 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I59" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr"/>
       <c r="J59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" s="4" t="inlineStr"/>
-      <c r="L59" s="4" t="inlineStr"/>
-      <c r="M59" s="4" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>1996-01-01</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M59" s="6" t="n">
+        <v>1.253404</v>
+      </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDM03VEA156NWDB</t>
@@ -4658,20 +4670,26 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I60" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr"/>
       <c r="J60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" s="4" t="inlineStr"/>
-      <c r="L60" s="4" t="inlineStr"/>
-      <c r="M60" s="4" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>1996-01-01</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M60" s="6" t="n">
+        <v>20.26552</v>
+      </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDM04VEA156NWDB</t>
@@ -4731,20 +4749,26 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I61" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr"/>
       <c r="J61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" s="4" t="inlineStr"/>
-      <c r="L61" s="4" t="inlineStr"/>
-      <c r="M61" s="4" t="n"/>
+        <v>41</v>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>1980-01-01</t>
+        </is>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="M61" s="6" t="n">
+        <v>9.759254</v>
+      </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDM05VEA156NWDB</t>
@@ -4962,20 +4986,26 @@
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I64" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr"/>
       <c r="J64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" s="4" t="inlineStr"/>
-      <c r="L64" s="4" t="inlineStr"/>
-      <c r="M64" s="4" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>2016-01-01</t>
+        </is>
+      </c>
+      <c r="M64" s="6" t="n">
+        <v>0.0069774</v>
+      </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDM08VEA156NWDB</t>
@@ -5266,26 +5296,20 @@
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I68" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J68" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="K68" s="4" t="inlineStr">
-        <is>
-          <t>1990-01-01</t>
-        </is>
-      </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>2017-01-01</t>
-        </is>
-      </c>
-      <c r="M68" s="6" t="n">
-        <v>6.326667</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K68" s="4" t="inlineStr"/>
+      <c r="L68" s="4" t="inlineStr"/>
+      <c r="M68" s="4" t="n"/>
       <c r="N68" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDEI02VEA156NWDB</t>
@@ -5418,26 +5442,20 @@
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I70" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J70" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K70" s="4" t="inlineStr">
-        <is>
-          <t>2000-01-01</t>
-        </is>
-      </c>
-      <c r="L70" s="4" t="inlineStr">
-        <is>
-          <t>2021-01-01</t>
-        </is>
-      </c>
-      <c r="M70" s="6" t="n">
-        <v>6.681727</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K70" s="4" t="inlineStr"/>
+      <c r="L70" s="4" t="inlineStr"/>
+      <c r="M70" s="4" t="n"/>
       <c r="N70" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDEI04VEA156NWDB</t>
@@ -6470,20 +6488,26 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I84" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr"/>
       <c r="J84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" s="4" t="inlineStr"/>
-      <c r="L84" s="4" t="inlineStr"/>
-      <c r="M84" s="4" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>1972-01-01</t>
+        </is>
+      </c>
+      <c r="L84" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M84" s="6" t="n">
+        <v>-0.5978945</v>
+      </c>
       <c r="N84" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOI08VEA156NWDB</t>
@@ -6543,20 +6567,26 @@
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I85" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr"/>
       <c r="J85" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" s="4" t="inlineStr"/>
-      <c r="L85" s="4" t="inlineStr"/>
-      <c r="M85" s="4" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="K85" s="4" t="inlineStr">
+        <is>
+          <t>1972-01-01</t>
+        </is>
+      </c>
+      <c r="L85" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M85" s="6" t="n">
+        <v>10.83362</v>
+      </c>
       <c r="N85" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOI09VEA156NWDB</t>
@@ -6768,20 +6798,26 @@
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I88" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr"/>
       <c r="J88" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" s="4" t="inlineStr"/>
-      <c r="L88" s="4" t="inlineStr"/>
-      <c r="M88" s="4" t="n"/>
+        <v>38</v>
+      </c>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>1983-01-01</t>
+        </is>
+      </c>
+      <c r="L88" s="4" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="M88" s="6" t="n">
+        <v>5.584377</v>
+      </c>
       <c r="N88" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOI12VEA156NWDB</t>
@@ -6987,26 +7023,20 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I91" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J91" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="K91" s="4" t="inlineStr">
-        <is>
-          <t>1990-01-01</t>
-        </is>
-      </c>
-      <c r="L91" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M91" s="6" t="n">
-        <v>1.231569</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K91" s="4" t="inlineStr"/>
+      <c r="L91" s="4" t="inlineStr"/>
+      <c r="M91" s="4" t="n"/>
       <c r="N91" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOM01VEA644NWDB</t>
@@ -7066,26 +7096,20 @@
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I92" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J92" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K92" s="4" t="inlineStr">
-        <is>
-          <t>2000-01-01</t>
-        </is>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>2021-01-01</t>
-        </is>
-      </c>
-      <c r="M92" s="6" t="n">
-        <v>12.70259</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K92" s="4" t="inlineStr"/>
+      <c r="L92" s="4" t="inlineStr"/>
+      <c r="M92" s="4" t="n"/>
       <c r="N92" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDSI01VEA645NWDB</t>
@@ -7145,26 +7169,20 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I93" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J93" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="K93" s="4" t="inlineStr">
-        <is>
-          <t>1998-01-01</t>
-        </is>
-      </c>
-      <c r="L93" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M93" s="6" t="n">
-        <v>0.83999997</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K93" s="4" t="inlineStr"/>
+      <c r="L93" s="4" t="inlineStr"/>
+      <c r="M93" s="4" t="n"/>
       <c r="N93" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDSI02VEA156NWDB</t>
@@ -7224,26 +7242,20 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I94" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J94" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="K94" s="4" t="inlineStr">
-        <is>
-          <t>1998-01-01</t>
-        </is>
-      </c>
-      <c r="L94" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M94" s="6" t="n">
-        <v>10.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K94" s="4" t="inlineStr"/>
+      <c r="L94" s="4" t="inlineStr"/>
+      <c r="M94" s="4" t="n"/>
       <c r="N94" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDSI03VEA156NWDB</t>
@@ -7303,26 +7315,20 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I95" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J95" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="K95" s="4" t="inlineStr">
-        <is>
-          <t>1960-01-01</t>
-        </is>
-      </c>
-      <c r="L95" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M95" s="6" t="n">
-        <v>63.24106999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K95" s="4" t="inlineStr"/>
+      <c r="L95" s="4" t="inlineStr"/>
+      <c r="M95" s="4" t="n"/>
       <c r="N95" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDSI04VEA156NWDB</t>
@@ -7827,7 +7833,7 @@
       </c>
       <c r="I102" s="4" t="inlineStr"/>
       <c r="J102" s="5" t="n">
-        <v>6663</v>
+        <v>6668</v>
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
@@ -7836,11 +7842,11 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M102" s="6" t="n">
-        <v>754.8165</v>
+        <v>769.1437</v>
       </c>
       <c r="N102" s="4" t="inlineStr">
         <is>
@@ -8356,7 +8362,7 @@
       </c>
       <c r="I109" s="4" t="inlineStr"/>
       <c r="J109" s="5" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
@@ -8365,11 +8371,11 @@
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N109" s="4" t="inlineStr">
         <is>
@@ -8727,7 +8733,7 @@
       </c>
       <c r="I114" s="4" t="inlineStr"/>
       <c r="J114" s="5" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K114" s="4" t="inlineStr">
         <is>
@@ -8736,11 +8742,11 @@
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M114" s="5" t="n">
-        <v>4050</v>
+        <v>3974</v>
       </c>
       <c r="N114" s="4" t="inlineStr">
         <is>
@@ -9166,26 +9172,20 @@
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I120" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I120" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J120" s="5" t="n">
-        <v>498</v>
-      </c>
-      <c r="K120" s="4" t="inlineStr">
-        <is>
-          <t>1984-12-01</t>
-        </is>
-      </c>
-      <c r="L120" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="M120" s="5" t="n">
-        <v>386</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K120" s="4" t="inlineStr"/>
+      <c r="L120" s="4" t="inlineStr"/>
+      <c r="M120" s="4" t="n"/>
       <c r="N120" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORLTTREASPOS32719</t>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="I122" s="4" t="inlineStr"/>
       <c r="J122" s="5" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M122" s="5" t="n">
@@ -9397,26 +9397,20 @@
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I123" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I123" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J123" s="5" t="n">
-        <v>280</v>
-      </c>
-      <c r="K123" s="4" t="inlineStr">
-        <is>
-          <t>2003-02-01</t>
-        </is>
-      </c>
-      <c r="L123" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="M123" s="5" t="n">
-        <v>286</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K123" s="4" t="inlineStr"/>
+      <c r="L123" s="4" t="inlineStr"/>
+      <c r="M123" s="4" t="n"/>
       <c r="N123" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORSTTREASPOS32719</t>
@@ -10814,26 +10808,20 @@
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I142" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I142" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J142" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K142" s="4" t="inlineStr">
-        <is>
-          <t>2019-01-01</t>
-        </is>
-      </c>
-      <c r="L142" s="4" t="inlineStr">
-        <is>
-          <t>2019-01-01</t>
-        </is>
-      </c>
-      <c r="M142" s="5" t="n">
-        <v>188</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K142" s="4" t="inlineStr"/>
+      <c r="L142" s="4" t="inlineStr"/>
+      <c r="M142" s="4" t="n"/>
       <c r="N142" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/ICBUSEASEXQVEN</t>
@@ -11939,26 +11927,20 @@
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I157" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I157" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J157" s="5" t="n">
-        <v>214</v>
-      </c>
-      <c r="K157" s="4" t="inlineStr">
-        <is>
-          <t>1972-10-01</t>
-        </is>
-      </c>
-      <c r="L157" s="4" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M157" s="5" t="n">
-        <v>15950</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K157" s="4" t="inlineStr"/>
+      <c r="L157" s="4" t="inlineStr"/>
+      <c r="M157" s="4" t="n"/>
       <c r="N157" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSGAMRIAOVE</t>
@@ -12462,26 +12444,20 @@
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I164" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I164" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J164" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="K164" s="4" t="inlineStr">
-        <is>
-          <t>1993-07-01</t>
-        </is>
-      </c>
-      <c r="L164" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M164" s="6" t="n">
-        <v>-1.12602</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K164" s="4" t="inlineStr"/>
+      <c r="L164" s="4" t="inlineStr"/>
+      <c r="M164" s="4" t="n"/>
       <c r="N164" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSGGGAMNINIVE</t>
@@ -13277,26 +13253,20 @@
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I175" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I175" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J175" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="K175" s="4" t="inlineStr">
-        <is>
-          <t>1990-10-01</t>
-        </is>
-      </c>
-      <c r="L175" s="4" t="inlineStr">
-        <is>
-          <t>1997-04-01</t>
-        </is>
-      </c>
-      <c r="M175" s="6" t="n">
-        <v>0.015</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K175" s="4" t="inlineStr"/>
+      <c r="L175" s="4" t="inlineStr"/>
+      <c r="M175" s="4" t="n"/>
       <c r="N175" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IMMINIAIAOVE</t>
@@ -13356,26 +13326,20 @@
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I176" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I176" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J176" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K176" s="4" t="inlineStr">
-        <is>
-          <t>1993-10-01</t>
-        </is>
-      </c>
-      <c r="L176" s="4" t="inlineStr">
-        <is>
-          <t>1997-01-01</t>
-        </is>
-      </c>
-      <c r="M176" s="6" t="n">
-        <v>0.015</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K176" s="4" t="inlineStr"/>
+      <c r="L176" s="4" t="inlineStr"/>
+      <c r="M176" s="4" t="n"/>
       <c r="N176" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IMMINIAIGIVE</t>
@@ -13435,26 +13399,20 @@
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I177" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I177" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J177" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="K177" s="4" t="inlineStr">
-        <is>
-          <t>1993-10-01</t>
-        </is>
-      </c>
-      <c r="L177" s="4" t="inlineStr">
-        <is>
-          <t>1997-07-01</t>
-        </is>
-      </c>
-      <c r="M177" s="6" t="n">
-        <v>-0.015</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K177" s="4" t="inlineStr"/>
+      <c r="L177" s="4" t="inlineStr"/>
+      <c r="M177" s="4" t="n"/>
       <c r="N177" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IMMINIAINIVE</t>
@@ -14347,26 +14305,20 @@
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I189" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I189" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J189" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="K189" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L189" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M189" s="6" t="n">
-        <v>24.52833168</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K189" s="4" t="inlineStr"/>
+      <c r="L189" s="4" t="inlineStr"/>
+      <c r="M189" s="4" t="n"/>
       <c r="N189" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/KIPPPGVEA156NUPN</t>
@@ -16196,26 +16148,20 @@
       </c>
       <c r="H214" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I214" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I214" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J214" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="K214" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L214" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M214" s="5" t="n">
-        <v>3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K214" s="4" t="inlineStr"/>
+      <c r="L214" s="4" t="inlineStr"/>
+      <c r="M214" s="4" t="n"/>
       <c r="N214" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MTVENA475SCEN</t>
@@ -16938,26 +16884,20 @@
       </c>
       <c r="H224" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I224" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I224" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J224" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K224" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L224" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M224" s="5" t="n">
-        <v>3888969</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K224" s="4" t="inlineStr"/>
+      <c r="L224" s="4" t="inlineStr"/>
+      <c r="M224" s="4" t="n"/>
       <c r="N224" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NJVENA052SCEN</t>
@@ -17905,26 +17845,20 @@
       </c>
       <c r="H237" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I237" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I237" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J237" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="K237" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L237" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M237" s="6" t="n">
-        <v>45.86565346</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K237" s="4" t="inlineStr"/>
+      <c r="L237" s="4" t="inlineStr"/>
+      <c r="M237" s="4" t="n"/>
       <c r="N237" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/OPENCPVEA156NUPN</t>
@@ -18057,26 +17991,20 @@
       </c>
       <c r="H239" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I239" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I239" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J239" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="K239" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L239" s="4" t="inlineStr">
-        <is>
-          <t>2019-01-01</t>
-        </is>
-      </c>
-      <c r="M239" s="5" t="n">
-        <v>197417</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K239" s="4" t="inlineStr"/>
+      <c r="L239" s="4" t="inlineStr"/>
+      <c r="M239" s="4" t="n"/>
       <c r="N239" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/ORVENA052SCEN</t>
@@ -18507,26 +18435,20 @@
       </c>
       <c r="H245" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I245" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I245" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J245" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="K245" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L245" s="4" t="inlineStr">
-        <is>
-          <t>2020-01-01</t>
-        </is>
-      </c>
-      <c r="M245" s="5" t="n">
-        <v>3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K245" s="4" t="inlineStr"/>
+      <c r="L245" s="4" t="inlineStr"/>
+      <c r="M245" s="4" t="n"/>
       <c r="N245" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PATENT4NVEUTILITY</t>
@@ -18732,26 +18654,20 @@
       </c>
       <c r="H248" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I248" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I248" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J248" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="K248" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L248" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M248" s="6" t="n">
-        <v>11809.94057</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K248" s="4" t="inlineStr"/>
+      <c r="L248" s="4" t="inlineStr"/>
+      <c r="M248" s="4" t="n"/>
       <c r="N248" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PC2GDPVEA620NUPN</t>
@@ -18963,26 +18879,20 @@
       </c>
       <c r="H251" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I251" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I251" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J251" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="K251" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L251" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M251" s="6" t="n">
-        <v>25.36032612</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K251" s="4" t="inlineStr"/>
+      <c r="L251" s="4" t="inlineStr"/>
+      <c r="M251" s="4" t="n"/>
       <c r="N251" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PGD2USVEA621NUPN</t>
@@ -19735,26 +19645,20 @@
       </c>
       <c r="H261" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I261" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I261" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J261" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="K261" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L261" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M261" s="6" t="n">
-        <v>121.4234463</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K261" s="4" t="inlineStr"/>
+      <c r="L261" s="4" t="inlineStr"/>
+      <c r="M261" s="4" t="n"/>
       <c r="N261" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLOCONVEA622NUPN</t>
@@ -19814,20 +19718,26 @@
       </c>
       <c r="H262" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I262" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I262" s="4" t="inlineStr"/>
       <c r="J262" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K262" s="4" t="inlineStr"/>
-      <c r="L262" s="4" t="inlineStr"/>
-      <c r="M262" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K262" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L262" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M262" s="6" t="n">
+        <v>122.0413712</v>
+      </c>
       <c r="N262" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLOGDPVEA621NUPN</t>
@@ -20430,26 +20340,20 @@
       </c>
       <c r="H270" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I270" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I270" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J270" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="K270" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L270" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M270" s="6" t="n">
-        <v>320634.9337</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K270" s="4" t="inlineStr"/>
+      <c r="L270" s="4" t="inlineStr"/>
+      <c r="M270" s="4" t="n"/>
       <c r="N270" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PPPGDPVEA619NUPN</t>
@@ -21451,26 +21355,20 @@
       </c>
       <c r="H283" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I283" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I283" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J283" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="K283" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L283" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M283" s="6" t="n">
-        <v>25811.10218</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K283" s="4" t="inlineStr"/>
+      <c r="L283" s="4" t="inlineStr"/>
+      <c r="M283" s="4" t="n"/>
       <c r="N283" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RGDPTEVEA629NUPN</t>
@@ -21682,26 +21580,20 @@
       </c>
       <c r="H286" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I286" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I286" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J286" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="K286" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L286" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M286" s="6" t="n">
-        <v>19511.40489</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K286" s="4" t="inlineStr"/>
+      <c r="L286" s="4" t="inlineStr"/>
+      <c r="M286" s="4" t="n"/>
       <c r="N286" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RGDPWOVEA627NUPN</t>
@@ -22284,26 +22176,20 @@
       </c>
       <c r="H294" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I294" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I294" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J294" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="K294" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L294" s="4" t="inlineStr">
-        <is>
-          <t>2016-01-01</t>
-        </is>
-      </c>
-      <c r="M294" s="5" t="n">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K294" s="4" t="inlineStr"/>
+      <c r="L294" s="4" t="inlineStr"/>
+      <c r="M294" s="4" t="n"/>
       <c r="N294" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SDVENA475SCEN</t>
@@ -22515,26 +22401,20 @@
       </c>
       <c r="H297" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I297" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I297" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J297" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="K297" s="4" t="inlineStr">
-        <is>
-          <t>1971-01-01</t>
-        </is>
-      </c>
-      <c r="L297" s="4" t="inlineStr">
-        <is>
-          <t>2017-01-01</t>
-        </is>
-      </c>
-      <c r="M297" s="6" t="n">
-        <v>1.0806200504303</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K297" s="4" t="inlineStr"/>
+      <c r="L297" s="4" t="inlineStr"/>
+      <c r="M297" s="4" t="n"/>
       <c r="N297" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SEENRSECOFMZSVEN</t>
@@ -22594,26 +22474,20 @@
       </c>
       <c r="H298" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I298" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I298" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J298" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K298" s="4" t="inlineStr">
-        <is>
-          <t>1986-01-01</t>
-        </is>
-      </c>
-      <c r="L298" s="4" t="inlineStr">
-        <is>
-          <t>2008-01-01</t>
-        </is>
-      </c>
-      <c r="M298" s="6" t="n">
-        <v>1.40991997718811</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K298" s="4" t="inlineStr"/>
+      <c r="L298" s="4" t="inlineStr"/>
+      <c r="M298" s="4" t="n"/>
       <c r="N298" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SEENRTERTFMZSVEN</t>
@@ -23536,26 +23410,20 @@
       </c>
       <c r="H310" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I310" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I310" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J310" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="K310" s="4" t="inlineStr">
-        <is>
-          <t>1960-01-01</t>
-        </is>
-      </c>
-      <c r="L310" s="4" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
-      <c r="M310" s="6" t="n">
-        <v>24.9159954154898</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K310" s="4" t="inlineStr"/>
+      <c r="L310" s="4" t="inlineStr"/>
+      <c r="M310" s="4" t="n"/>
       <c r="N310" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SPPOP0014TOZSVEN</t>
@@ -24509,26 +24377,20 @@
       </c>
       <c r="H323" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I323" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I323" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J323" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="K323" s="4" t="inlineStr">
-        <is>
-          <t>2023-02-01</t>
-        </is>
-      </c>
-      <c r="L323" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="M323" s="5" t="n">
-        <v>2756</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K323" s="4" t="inlineStr"/>
+      <c r="L323" s="4" t="inlineStr"/>
+      <c r="M323" s="4" t="n"/>
       <c r="N323" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTCORPBONDPOS32719</t>
@@ -25099,20 +24961,26 @@
       </c>
       <c r="H331" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I331" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I331" s="4" t="inlineStr"/>
       <c r="J331" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K331" s="4" t="inlineStr"/>
-      <c r="L331" s="4" t="inlineStr"/>
-      <c r="M331" s="4" t="n"/>
+        <v>387</v>
+      </c>
+      <c r="K331" s="4" t="inlineStr">
+        <is>
+          <t>1994-04-01</t>
+        </is>
+      </c>
+      <c r="L331" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M331" s="5" t="n">
+        <v>14</v>
+      </c>
       <c r="N331" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTTOTALNET32719</t>
@@ -25245,20 +25113,26 @@
       </c>
       <c r="H333" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I333" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I333" s="4" t="inlineStr"/>
       <c r="J333" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K333" s="4" t="inlineStr"/>
-      <c r="L333" s="4" t="inlineStr"/>
-      <c r="M333" s="4" t="n"/>
+        <v>387</v>
+      </c>
+      <c r="K333" s="4" t="inlineStr">
+        <is>
+          <t>1994-04-01</t>
+        </is>
+      </c>
+      <c r="L333" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M333" s="5" t="n">
+        <v>-238</v>
+      </c>
       <c r="N333" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTTOTALVALCHG32719</t>
@@ -25391,26 +25265,20 @@
       </c>
       <c r="H335" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I335" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I335" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J335" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K335" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L335" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M335" s="5" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K335" s="4" t="inlineStr"/>
+      <c r="L335" s="4" t="inlineStr"/>
+      <c r="M335" s="4" t="n"/>
       <c r="N335" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/UTVENA475SCEN</t>
@@ -25762,26 +25630,20 @@
       </c>
       <c r="H340" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I340" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I340" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J340" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K340" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L340" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M340" s="5" t="n">
-        <v>10429</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K340" s="4" t="inlineStr"/>
+      <c r="L340" s="4" t="inlineStr"/>
+      <c r="M340" s="4" t="n"/>
       <c r="N340" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCACNUM</t>
@@ -25987,26 +25849,20 @@
       </c>
       <c r="H343" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I343" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I343" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J343" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K343" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L343" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M343" s="5" t="n">
-        <v>31695711</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K343" s="4" t="inlineStr"/>
+      <c r="L343" s="4" t="inlineStr"/>
+      <c r="M343" s="4" t="n"/>
       <c r="N343" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCAODCNUM</t>
@@ -26802,26 +26658,20 @@
       </c>
       <c r="H354" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I354" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I354" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J354" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K354" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L354" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M354" s="6" t="n">
-        <v>0.130378096</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K354" s="4" t="inlineStr"/>
+      <c r="L354" s="4" t="inlineStr"/>
+      <c r="M354" s="4" t="n"/>
       <c r="N354" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCBODMFKNUM</t>
@@ -27173,26 +27023,20 @@
       </c>
       <c r="H359" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I359" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I359" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J359" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K359" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L359" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M359" s="6" t="n">
-        <v>24601704.6666667</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K359" s="4" t="inlineStr"/>
+      <c r="L359" s="4" t="inlineStr"/>
+      <c r="M359" s="4" t="n"/>
       <c r="N359" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCDODCHPENUM</t>
@@ -27398,26 +27242,20 @@
       </c>
       <c r="H362" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I362" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I362" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J362" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K362" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L362" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M362" s="6" t="n">
-        <v>66.83665774000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K362" s="4" t="inlineStr"/>
+      <c r="L362" s="4" t="inlineStr"/>
+      <c r="M362" s="4" t="n"/>
       <c r="N362" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCDODCSPNUM</t>
@@ -27921,26 +27759,20 @@
       </c>
       <c r="H369" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I369" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I369" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J369" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="K369" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L369" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M369" s="6" t="n">
-        <v>68.50582168130001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K369" s="4" t="inlineStr"/>
+      <c r="L369" s="4" t="inlineStr"/>
+      <c r="M369" s="4" t="n"/>
       <c r="N369" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCLODCGGDPPT</t>
@@ -28438,26 +28270,20 @@
       </c>
       <c r="H376" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I376" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I376" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J376" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K376" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L376" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M376" s="6" t="n">
-        <v>37322701822.99</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K376" s="4" t="inlineStr"/>
+      <c r="L376" s="4" t="inlineStr"/>
+      <c r="M376" s="4" t="n"/>
       <c r="N376" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCLODMFXDC</t>
@@ -28736,26 +28562,20 @@
       </c>
       <c r="H380" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I380" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I380" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J380" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K380" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L380" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M380" s="6" t="n">
-        <v>1078.0378178439</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K380" s="4" t="inlineStr"/>
+      <c r="L380" s="4" t="inlineStr"/>
+      <c r="M380" s="4" t="n"/>
       <c r="N380" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCNODCANUM</t>
@@ -29186,26 +29006,20 @@
       </c>
       <c r="H386" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I386" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I386" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J386" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K386" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L386" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M386" s="6" t="n">
-        <v>7404689.58333333</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K386" s="4" t="inlineStr"/>
+      <c r="L386" s="4" t="inlineStr"/>
+      <c r="M386" s="4" t="n"/>
       <c r="N386" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCRODCHPENUM</t>
@@ -29484,26 +29298,20 @@
       </c>
       <c r="H390" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I390" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I390" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J390" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="K390" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L390" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M390" s="6" t="n">
-        <v>37.8908354029</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K390" s="4" t="inlineStr"/>
+      <c r="L390" s="4" t="inlineStr"/>
+      <c r="M390" s="4" t="n"/>
       <c r="N390" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCSODCGGDPPT</t>
@@ -29934,26 +29742,20 @@
       </c>
       <c r="H396" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I396" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I396" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J396" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="K396" s="4" t="inlineStr">
-        <is>
-          <t>2008-01-01</t>
-        </is>
-      </c>
-      <c r="L396" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M396" s="5" t="n">
-        <v>10753000000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K396" s="4" t="inlineStr"/>
+      <c r="L396" s="4" t="inlineStr"/>
+      <c r="M396" s="4" t="n"/>
       <c r="N396" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCSODMFSXDC</t>
@@ -30086,26 +29888,20 @@
       </c>
       <c r="H398" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I398" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I398" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J398" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="K398" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L398" s="4" t="inlineStr">
-        <is>
-          <t>2016-01-01</t>
-        </is>
-      </c>
-      <c r="M398" s="5" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K398" s="4" t="inlineStr"/>
+      <c r="L398" s="4" t="inlineStr"/>
+      <c r="M398" s="4" t="n"/>
       <c r="N398" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VIVENA475SCEN</t>
@@ -30828,26 +30624,20 @@
       </c>
       <c r="H408" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I408" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I408" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J408" s="5" t="n">
-        <v>122</v>
-      </c>
-      <c r="K408" s="4" t="inlineStr">
-        <is>
-          <t>1996-01-01</t>
-        </is>
-      </c>
-      <c r="L408" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="M408" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="K408" s="4" t="inlineStr"/>
+      <c r="L408" s="4" t="inlineStr"/>
+      <c r="M408" s="4" t="n"/>
       <c r="N408" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/WUPIVEN</t>
@@ -31326,7 +31116,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -31383,7 +31173,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>152</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15">
@@ -31393,7 +31183,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>17666</v>
+        <v>16391</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/fred/catalog/catalogo_dataset_web_ove_fred.xlsx
+++ b/assets/data/fred/catalog/catalogo_dataset_web_ove_fred.xlsx
@@ -2189,20 +2189,26 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr"/>
       <c r="J27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="4" t="inlineStr"/>
-      <c r="L27" s="4" t="inlineStr"/>
-      <c r="M27" s="4" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M27" s="6" t="n">
+        <v>0.449208825826645</v>
+      </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CSHCCPVEA156NRUG</t>
@@ -2414,20 +2420,26 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr"/>
       <c r="J30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="4" t="inlineStr"/>
-      <c r="L30" s="4" t="inlineStr"/>
-      <c r="M30" s="4" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>-0.301709741353989</v>
+      </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CSHMCPVEA156NRUG</t>
@@ -2487,20 +2499,26 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr"/>
       <c r="J31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="4" t="inlineStr"/>
-      <c r="L31" s="4" t="inlineStr"/>
-      <c r="M31" s="4" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M31" s="6" t="n">
+        <v>-0.0894852876663208</v>
+      </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CSHRCPVEA156NRUG</t>
@@ -3831,20 +3849,26 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I49" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr"/>
       <c r="J49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="4" t="inlineStr"/>
-      <c r="L49" s="4" t="inlineStr"/>
-      <c r="M49" s="4" t="n"/>
+        <v>54</v>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>2013-01-01</t>
+        </is>
+      </c>
+      <c r="M49" s="6" t="n">
+        <v>69.07484000000001</v>
+      </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDI04VEA156NWDB</t>
@@ -4208,20 +4232,26 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I54" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr"/>
       <c r="J54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="4" t="inlineStr"/>
-      <c r="L54" s="4" t="inlineStr"/>
-      <c r="M54" s="4" t="n"/>
+        <v>30</v>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>1990-01-01</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="M54" s="6" t="n">
+        <v>0.0031524</v>
+      </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDI10VEA156NWDB</t>
@@ -4360,20 +4390,26 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I56" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr"/>
       <c r="J56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="4" t="inlineStr"/>
-      <c r="L56" s="4" t="inlineStr"/>
-      <c r="M56" s="4" t="n"/>
+        <v>55</v>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M56" s="6" t="n">
+        <v>39.51449</v>
+      </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDI12VEA156NWDB</t>
@@ -5065,20 +5101,26 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I65" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr"/>
       <c r="J65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" s="4" t="inlineStr"/>
-      <c r="L65" s="4" t="inlineStr"/>
-      <c r="M65" s="4" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>2016-01-01</t>
+        </is>
+      </c>
+      <c r="M65" s="6" t="n">
+        <v>0.0009455000000000001</v>
+      </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDM09VEA156NWDB</t>
@@ -5296,20 +5338,26 @@
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I68" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr"/>
       <c r="J68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" s="4" t="inlineStr"/>
-      <c r="L68" s="4" t="inlineStr"/>
-      <c r="M68" s="4" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>1990-01-01</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>2017-01-01</t>
+        </is>
+      </c>
+      <c r="M68" s="6" t="n">
+        <v>6.326667</v>
+      </c>
       <c r="N68" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDEI02VEA156NWDB</t>
@@ -5442,20 +5490,26 @@
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I70" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr"/>
       <c r="J70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" s="4" t="inlineStr"/>
-      <c r="L70" s="4" t="inlineStr"/>
-      <c r="M70" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>2000-01-01</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="M70" s="6" t="n">
+        <v>6.681727</v>
+      </c>
       <c r="N70" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDEI04VEA156NWDB</t>
@@ -6336,20 +6390,26 @@
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I82" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr"/>
       <c r="J82" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" s="4" t="inlineStr"/>
-      <c r="L82" s="4" t="inlineStr"/>
-      <c r="M82" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>2000-01-01</t>
+        </is>
+      </c>
+      <c r="L82" s="4" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="M82" s="6" t="n">
+        <v>92.47150000000001</v>
+      </c>
       <c r="N82" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOI06VEA156NWDB</t>
@@ -7023,20 +7083,26 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I91" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="inlineStr"/>
       <c r="J91" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" s="4" t="inlineStr"/>
-      <c r="L91" s="4" t="inlineStr"/>
-      <c r="M91" s="4" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>1990-01-01</t>
+        </is>
+      </c>
+      <c r="L91" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M91" s="6" t="n">
+        <v>1.231569</v>
+      </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOM01VEA644NWDB</t>
@@ -7096,20 +7162,26 @@
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I92" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr"/>
       <c r="J92" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" s="4" t="inlineStr"/>
-      <c r="L92" s="4" t="inlineStr"/>
-      <c r="M92" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>2000-01-01</t>
+        </is>
+      </c>
+      <c r="L92" s="4" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="M92" s="6" t="n">
+        <v>12.70259</v>
+      </c>
       <c r="N92" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDSI01VEA645NWDB</t>
@@ -7169,20 +7241,26 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I93" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr"/>
       <c r="J93" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" s="4" t="inlineStr"/>
-      <c r="L93" s="4" t="inlineStr"/>
-      <c r="M93" s="4" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="K93" s="4" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="L93" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M93" s="6" t="n">
+        <v>0.83999997</v>
+      </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDSI02VEA156NWDB</t>
@@ -7242,20 +7320,26 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I94" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr"/>
       <c r="J94" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" s="4" t="inlineStr"/>
-      <c r="L94" s="4" t="inlineStr"/>
-      <c r="M94" s="4" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="L94" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M94" s="6" t="n">
+        <v>10.5</v>
+      </c>
       <c r="N94" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDSI03VEA156NWDB</t>
@@ -7315,20 +7399,26 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I95" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr"/>
       <c r="J95" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" s="4" t="inlineStr"/>
-      <c r="L95" s="4" t="inlineStr"/>
-      <c r="M95" s="4" t="n"/>
+        <v>55</v>
+      </c>
+      <c r="K95" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L95" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M95" s="6" t="n">
+        <v>63.24106999999999</v>
+      </c>
       <c r="N95" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDSI04VEA156NWDB</t>
@@ -7534,20 +7624,26 @@
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I98" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr"/>
       <c r="J98" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" s="4" t="inlineStr"/>
-      <c r="L98" s="4" t="inlineStr"/>
-      <c r="M98" s="4" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>1998-01-01</t>
+        </is>
+      </c>
+      <c r="L98" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M98" s="6" t="n">
+        <v>604.0700099999999</v>
+      </c>
       <c r="N98" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDSI07VEA156NWDB</t>
@@ -7833,7 +7929,7 @@
       </c>
       <c r="I102" s="4" t="inlineStr"/>
       <c r="J102" s="5" t="n">
-        <v>6668</v>
+        <v>6673</v>
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
@@ -7842,11 +7938,11 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="M102" s="6" t="n">
-        <v>769.1437</v>
+        <v>778.0023</v>
       </c>
       <c r="N102" s="4" t="inlineStr">
         <is>
@@ -9397,20 +9493,26 @@
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I123" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I123" s="4" t="inlineStr"/>
       <c r="J123" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" s="4" t="inlineStr"/>
-      <c r="L123" s="4" t="inlineStr"/>
-      <c r="M123" s="4" t="n"/>
+        <v>281</v>
+      </c>
+      <c r="K123" s="4" t="inlineStr">
+        <is>
+          <t>2003-02-01</t>
+        </is>
+      </c>
+      <c r="L123" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M123" s="5" t="n">
+        <v>297</v>
+      </c>
       <c r="N123" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORSTTREASPOS32719</t>
@@ -9470,20 +9572,26 @@
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I124" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I124" s="4" t="inlineStr"/>
       <c r="J124" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K124" s="4" t="inlineStr"/>
-      <c r="L124" s="4" t="inlineStr"/>
-      <c r="M124" s="4" t="n"/>
+        <v>280</v>
+      </c>
+      <c r="K124" s="4" t="inlineStr">
+        <is>
+          <t>2003-03-01</t>
+        </is>
+      </c>
+      <c r="L124" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M124" s="5" t="n">
+        <v>31</v>
+      </c>
       <c r="N124" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORTREASNET32719</t>
@@ -9543,20 +9651,26 @@
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I125" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I125" s="4" t="inlineStr"/>
       <c r="J125" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K125" s="4" t="inlineStr"/>
-      <c r="L125" s="4" t="inlineStr"/>
-      <c r="M125" s="4" t="n"/>
+        <v>281</v>
+      </c>
+      <c r="K125" s="4" t="inlineStr">
+        <is>
+          <t>2003-02-01</t>
+        </is>
+      </c>
+      <c r="L125" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M125" s="5" t="n">
+        <v>679</v>
+      </c>
       <c r="N125" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/FORTREASPOS32719</t>
@@ -10078,20 +10192,26 @@
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I132" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I132" s="4" t="inlineStr"/>
       <c r="J132" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K132" s="4" t="inlineStr"/>
-      <c r="L132" s="4" t="inlineStr"/>
-      <c r="M132" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="K132" s="4" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="L132" s="4" t="inlineStr">
+        <is>
+          <t>2009-01-01</t>
+        </is>
+      </c>
+      <c r="M132" s="5" t="n">
+        <v>72907</v>
+      </c>
       <c r="N132" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/HIVENA052SCEN</t>
@@ -10589,20 +10709,26 @@
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I139" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I139" s="4" t="inlineStr"/>
       <c r="J139" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K139" s="4" t="inlineStr"/>
-      <c r="L139" s="4" t="inlineStr"/>
-      <c r="M139" s="4" t="n"/>
+        <v>65</v>
+      </c>
+      <c r="K139" s="4" t="inlineStr">
+        <is>
+          <t>1972-10-01</t>
+        </is>
+      </c>
+      <c r="L139" s="4" t="inlineStr">
+        <is>
+          <t>2011-10-01</t>
+        </is>
+      </c>
+      <c r="M139" s="6" t="n">
+        <v>7.7885</v>
+      </c>
       <c r="N139" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IBANRIAIVE</t>
@@ -10808,20 +10934,26 @@
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I142" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I142" s="4" t="inlineStr"/>
       <c r="J142" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K142" s="4" t="inlineStr"/>
-      <c r="L142" s="4" t="inlineStr"/>
-      <c r="M142" s="4" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="K142" s="4" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="L142" s="4" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="M142" s="5" t="n">
+        <v>188</v>
+      </c>
       <c r="N142" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/ICBUSEASEXQVEN</t>
@@ -11927,20 +12059,26 @@
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I157" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I157" s="4" t="inlineStr"/>
       <c r="J157" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K157" s="4" t="inlineStr"/>
-      <c r="L157" s="4" t="inlineStr"/>
-      <c r="M157" s="4" t="n"/>
+        <v>214</v>
+      </c>
+      <c r="K157" s="4" t="inlineStr">
+        <is>
+          <t>1972-10-01</t>
+        </is>
+      </c>
+      <c r="L157" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M157" s="5" t="n">
+        <v>15950</v>
+      </c>
       <c r="N157" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSGAMRIAOVE</t>
@@ -12444,20 +12582,26 @@
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I164" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I164" s="4" t="inlineStr"/>
       <c r="J164" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K164" s="4" t="inlineStr"/>
-      <c r="L164" s="4" t="inlineStr"/>
-      <c r="M164" s="4" t="n"/>
+        <v>63</v>
+      </c>
+      <c r="K164" s="4" t="inlineStr">
+        <is>
+          <t>1993-07-01</t>
+        </is>
+      </c>
+      <c r="L164" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M164" s="6" t="n">
+        <v>-1.12602</v>
+      </c>
       <c r="N164" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDSGGGAMNINIVE</t>
@@ -12961,20 +13105,26 @@
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I171" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I171" s="4" t="inlineStr"/>
       <c r="J171" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K171" s="4" t="inlineStr"/>
-      <c r="L171" s="4" t="inlineStr"/>
-      <c r="M171" s="4" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="K171" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L171" s="4" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="M171" s="5" t="n">
+        <v>13776</v>
+      </c>
       <c r="N171" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDVENA052SCEN</t>
@@ -13253,20 +13403,26 @@
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I175" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I175" s="4" t="inlineStr"/>
       <c r="J175" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K175" s="4" t="inlineStr"/>
-      <c r="L175" s="4" t="inlineStr"/>
-      <c r="M175" s="4" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="K175" s="4" t="inlineStr">
+        <is>
+          <t>1990-10-01</t>
+        </is>
+      </c>
+      <c r="L175" s="4" t="inlineStr">
+        <is>
+          <t>1997-04-01</t>
+        </is>
+      </c>
+      <c r="M175" s="6" t="n">
+        <v>0.015</v>
+      </c>
       <c r="N175" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IMMINIAIAOVE</t>
@@ -13326,20 +13482,26 @@
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I176" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I176" s="4" t="inlineStr"/>
       <c r="J176" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K176" s="4" t="inlineStr"/>
-      <c r="L176" s="4" t="inlineStr"/>
-      <c r="M176" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K176" s="4" t="inlineStr">
+        <is>
+          <t>1993-10-01</t>
+        </is>
+      </c>
+      <c r="L176" s="4" t="inlineStr">
+        <is>
+          <t>1997-01-01</t>
+        </is>
+      </c>
+      <c r="M176" s="6" t="n">
+        <v>0.015</v>
+      </c>
       <c r="N176" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IMMINIAIGIVE</t>
@@ -13399,20 +13561,26 @@
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I177" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I177" s="4" t="inlineStr"/>
       <c r="J177" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K177" s="4" t="inlineStr"/>
-      <c r="L177" s="4" t="inlineStr"/>
-      <c r="M177" s="4" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="K177" s="4" t="inlineStr">
+        <is>
+          <t>1993-10-01</t>
+        </is>
+      </c>
+      <c r="L177" s="4" t="inlineStr">
+        <is>
+          <t>1997-07-01</t>
+        </is>
+      </c>
+      <c r="M177" s="6" t="n">
+        <v>-0.015</v>
+      </c>
       <c r="N177" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IMMINIAINIVE</t>
@@ -13472,20 +13640,26 @@
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I178" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I178" s="4" t="inlineStr"/>
       <c r="J178" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K178" s="4" t="inlineStr"/>
-      <c r="L178" s="4" t="inlineStr"/>
-      <c r="M178" s="4" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="K178" s="4" t="inlineStr">
+        <is>
+          <t>1990-10-01</t>
+        </is>
+      </c>
+      <c r="L178" s="4" t="inlineStr">
+        <is>
+          <t>1997-04-01</t>
+        </is>
+      </c>
+      <c r="M178" s="6" t="n">
+        <v>0.015</v>
+      </c>
       <c r="N178" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IMMIRIAOVE</t>
@@ -14305,20 +14479,26 @@
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I189" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I189" s="4" t="inlineStr"/>
       <c r="J189" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K189" s="4" t="inlineStr"/>
-      <c r="L189" s="4" t="inlineStr"/>
-      <c r="M189" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K189" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L189" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M189" s="6" t="n">
+        <v>24.52833168</v>
+      </c>
       <c r="N189" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/KIPPPGVEA156NUPN</t>
@@ -14895,20 +15075,26 @@
       </c>
       <c r="H197" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I197" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I197" s="4" t="inlineStr"/>
       <c r="J197" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K197" s="4" t="inlineStr"/>
-      <c r="L197" s="4" t="inlineStr"/>
-      <c r="M197" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K197" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L197" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M197" s="5" t="n">
+        <v>1854340</v>
+      </c>
       <c r="N197" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MAVENA052SCEN</t>
@@ -14968,20 +15154,26 @@
       </c>
       <c r="H198" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I198" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I198" s="4" t="inlineStr"/>
       <c r="J198" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K198" s="4" t="inlineStr"/>
-      <c r="L198" s="4" t="inlineStr"/>
-      <c r="M198" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K198" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L198" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M198" s="5" t="n">
+        <v>18</v>
+      </c>
       <c r="N198" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MAVENA475SCEN</t>
@@ -15406,20 +15598,26 @@
       </c>
       <c r="H204" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I204" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I204" s="4" t="inlineStr"/>
       <c r="J204" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K204" s="4" t="inlineStr"/>
-      <c r="L204" s="4" t="inlineStr"/>
-      <c r="M204" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K204" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L204" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M204" s="5" t="n">
+        <v>30</v>
+      </c>
       <c r="N204" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MIVENA475SCEN</t>
@@ -15783,20 +15981,26 @@
       </c>
       <c r="H209" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I209" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I209" s="4" t="inlineStr"/>
       <c r="J209" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K209" s="4" t="inlineStr"/>
-      <c r="L209" s="4" t="inlineStr"/>
-      <c r="M209" s="4" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="K209" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L209" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M209" s="5" t="n">
+        <v>758051</v>
+      </c>
       <c r="N209" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MOVENA052SCEN</t>
@@ -15856,20 +16060,26 @@
       </c>
       <c r="H210" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I210" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I210" s="4" t="inlineStr"/>
       <c r="J210" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K210" s="4" t="inlineStr"/>
-      <c r="L210" s="4" t="inlineStr"/>
-      <c r="M210" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K210" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L210" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M210" s="5" t="n">
+        <v>14</v>
+      </c>
       <c r="N210" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MOVENA475SCEN</t>
@@ -16002,20 +16212,26 @@
       </c>
       <c r="H212" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I212" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I212" s="4" t="inlineStr"/>
       <c r="J212" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K212" s="4" t="inlineStr"/>
-      <c r="L212" s="4" t="inlineStr"/>
-      <c r="M212" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K212" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L212" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M212" s="5" t="n">
+        <v>9</v>
+      </c>
       <c r="N212" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MSVENA475SCEN</t>
@@ -16075,20 +16291,26 @@
       </c>
       <c r="H213" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I213" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I213" s="4" t="inlineStr"/>
       <c r="J213" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K213" s="4" t="inlineStr"/>
-      <c r="L213" s="4" t="inlineStr"/>
-      <c r="M213" s="4" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="K213" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L213" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M213" s="5" t="n">
+        <v>206865</v>
+      </c>
       <c r="N213" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MTVENA052SCEN</t>
@@ -16148,20 +16370,26 @@
       </c>
       <c r="H214" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I214" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I214" s="4" t="inlineStr"/>
       <c r="J214" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K214" s="4" t="inlineStr"/>
-      <c r="L214" s="4" t="inlineStr"/>
-      <c r="M214" s="4" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="K214" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L214" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M214" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="N214" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MTVENA475SCEN</t>
@@ -16373,20 +16601,26 @@
       </c>
       <c r="H217" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I217" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I217" s="4" t="inlineStr"/>
       <c r="J217" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K217" s="4" t="inlineStr"/>
-      <c r="L217" s="4" t="inlineStr"/>
-      <c r="M217" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K217" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L217" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M217" s="5" t="n">
+        <v>41</v>
+      </c>
       <c r="N217" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NCVENA475SCEN</t>
@@ -16884,20 +17118,26 @@
       </c>
       <c r="H224" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I224" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I224" s="4" t="inlineStr"/>
       <c r="J224" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K224" s="4" t="inlineStr"/>
-      <c r="L224" s="4" t="inlineStr"/>
-      <c r="M224" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K224" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L224" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M224" s="5" t="n">
+        <v>3888969</v>
+      </c>
       <c r="N224" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NJVENA052SCEN</t>
@@ -17182,20 +17422,26 @@
       </c>
       <c r="H228" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I228" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I228" s="4" t="inlineStr"/>
       <c r="J228" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K228" s="4" t="inlineStr"/>
-      <c r="L228" s="4" t="inlineStr"/>
-      <c r="M228" s="4" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="K228" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L228" s="4" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+      <c r="M228" s="5" t="n">
+        <v>144707</v>
+      </c>
       <c r="N228" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NVVENA052SCEN</t>
@@ -17626,20 +17872,26 @@
       </c>
       <c r="H234" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I234" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I234" s="4" t="inlineStr"/>
       <c r="J234" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K234" s="4" t="inlineStr"/>
-      <c r="L234" s="4" t="inlineStr"/>
-      <c r="M234" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K234" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L234" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M234" s="5" t="n">
+        <v>43</v>
+      </c>
       <c r="N234" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/OHVENA475SCEN</t>
@@ -17845,20 +18097,26 @@
       </c>
       <c r="H237" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I237" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I237" s="4" t="inlineStr"/>
       <c r="J237" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K237" s="4" t="inlineStr"/>
-      <c r="L237" s="4" t="inlineStr"/>
-      <c r="M237" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K237" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L237" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M237" s="6" t="n">
+        <v>45.86565346</v>
+      </c>
       <c r="N237" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/OPENCPVEA156NUPN</t>
@@ -17991,20 +18249,26 @@
       </c>
       <c r="H239" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I239" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I239" s="4" t="inlineStr"/>
       <c r="J239" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K239" s="4" t="inlineStr"/>
-      <c r="L239" s="4" t="inlineStr"/>
-      <c r="M239" s="4" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="K239" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L239" s="4" t="inlineStr">
+        <is>
+          <t>2019-01-01</t>
+        </is>
+      </c>
+      <c r="M239" s="5" t="n">
+        <v>197417</v>
+      </c>
       <c r="N239" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/ORVENA052SCEN</t>
@@ -18137,20 +18401,26 @@
       </c>
       <c r="H241" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I241" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I241" s="4" t="inlineStr"/>
       <c r="J241" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="K241" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L241" s="4" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="M241" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K241" s="4" t="inlineStr"/>
-      <c r="L241" s="4" t="inlineStr"/>
-      <c r="M241" s="4" t="n"/>
       <c r="N241" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PATENT4NVEDESIGN</t>
@@ -18210,20 +18480,26 @@
       </c>
       <c r="H242" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I242" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I242" s="4" t="inlineStr"/>
       <c r="J242" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="K242" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L242" s="4" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="M242" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K242" s="4" t="inlineStr"/>
-      <c r="L242" s="4" t="inlineStr"/>
-      <c r="M242" s="4" t="n"/>
       <c r="N242" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PATENT4NVEPLANT</t>
@@ -18435,20 +18711,26 @@
       </c>
       <c r="H245" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I245" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I245" s="4" t="inlineStr"/>
       <c r="J245" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K245" s="4" t="inlineStr"/>
-      <c r="L245" s="4" t="inlineStr"/>
-      <c r="M245" s="4" t="n"/>
+        <v>29</v>
+      </c>
+      <c r="K245" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L245" s="4" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+      <c r="M245" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="N245" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PATENT4NVEUTILITY</t>
@@ -18654,20 +18936,26 @@
       </c>
       <c r="H248" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I248" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I248" s="4" t="inlineStr"/>
       <c r="J248" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K248" s="4" t="inlineStr"/>
-      <c r="L248" s="4" t="inlineStr"/>
-      <c r="M248" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K248" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L248" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M248" s="6" t="n">
+        <v>11809.94057</v>
+      </c>
       <c r="N248" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PC2GDPVEA620NUPN</t>
@@ -18806,20 +19094,26 @@
       </c>
       <c r="H250" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I250" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I250" s="4" t="inlineStr"/>
       <c r="J250" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K250" s="4" t="inlineStr"/>
-      <c r="L250" s="4" t="inlineStr"/>
-      <c r="M250" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K250" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L250" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M250" s="6" t="n">
+        <v>10445.85073</v>
+      </c>
       <c r="N250" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PCDGDPVEA620NUPN</t>
@@ -18879,20 +19173,26 @@
       </c>
       <c r="H251" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I251" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I251" s="4" t="inlineStr"/>
       <c r="J251" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K251" s="4" t="inlineStr"/>
-      <c r="L251" s="4" t="inlineStr"/>
-      <c r="M251" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K251" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L251" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M251" s="6" t="n">
+        <v>25.36032612</v>
+      </c>
       <c r="N251" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PGD2USVEA621NUPN</t>
@@ -19268,20 +19568,26 @@
       </c>
       <c r="H256" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I256" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I256" s="4" t="inlineStr"/>
       <c r="J256" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K256" s="4" t="inlineStr"/>
-      <c r="L256" s="4" t="inlineStr"/>
-      <c r="M256" s="4" t="n"/>
+        <v>62</v>
+      </c>
+      <c r="K256" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L256" s="4" t="inlineStr">
+        <is>
+          <t>2011-01-01</t>
+        </is>
+      </c>
+      <c r="M256" s="6" t="n">
+        <v>1.0502430201</v>
+      </c>
       <c r="N256" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLGDPEVEA670NRUG</t>
@@ -19341,20 +19647,26 @@
       </c>
       <c r="H257" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I257" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I257" s="4" t="inlineStr"/>
       <c r="J257" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K257" s="4" t="inlineStr"/>
-      <c r="L257" s="4" t="inlineStr"/>
-      <c r="M257" s="4" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K257" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L257" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M257" s="6" t="n">
+        <v>31.6201782226563</v>
+      </c>
       <c r="N257" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLGDPOVEA670NRUG</t>
@@ -19414,20 +19726,26 @@
       </c>
       <c r="H258" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I258" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I258" s="4" t="inlineStr"/>
       <c r="J258" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K258" s="4" t="inlineStr"/>
-      <c r="L258" s="4" t="inlineStr"/>
-      <c r="M258" s="4" t="n"/>
+        <v>74</v>
+      </c>
+      <c r="K258" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L258" s="4" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="M258" s="6" t="n">
+        <v>40.4344416781944</v>
+      </c>
       <c r="N258" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLICPPVEA670NRUG</t>
@@ -19645,20 +19963,26 @@
       </c>
       <c r="H261" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I261" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I261" s="4" t="inlineStr"/>
       <c r="J261" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K261" s="4" t="inlineStr"/>
-      <c r="L261" s="4" t="inlineStr"/>
-      <c r="M261" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K261" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L261" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M261" s="6" t="n">
+        <v>121.4234463</v>
+      </c>
       <c r="N261" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLOCONVEA622NUPN</t>
@@ -19797,20 +20121,26 @@
       </c>
       <c r="H263" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I263" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I263" s="4" t="inlineStr"/>
       <c r="J263" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K263" s="4" t="inlineStr"/>
-      <c r="L263" s="4" t="inlineStr"/>
-      <c r="M263" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K263" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L263" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M263" s="6" t="n">
+        <v>144.0149859</v>
+      </c>
       <c r="N263" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLOGINVEA623NUPN</t>
@@ -20340,20 +20670,26 @@
       </c>
       <c r="H270" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I270" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I270" s="4" t="inlineStr"/>
       <c r="J270" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K270" s="4" t="inlineStr"/>
-      <c r="L270" s="4" t="inlineStr"/>
-      <c r="M270" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K270" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L270" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M270" s="6" t="n">
+        <v>320634.9337</v>
+      </c>
       <c r="N270" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PPPGDPVEA619NUPN</t>
@@ -20571,20 +20907,26 @@
       </c>
       <c r="H273" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I273" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I273" s="4" t="inlineStr"/>
       <c r="J273" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K273" s="4" t="inlineStr"/>
-      <c r="L273" s="4" t="inlineStr"/>
-      <c r="M273" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K273" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L273" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M273" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="N273" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PRVENA475SCEN</t>
@@ -21355,20 +21697,26 @@
       </c>
       <c r="H283" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I283" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I283" s="4" t="inlineStr"/>
       <c r="J283" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K283" s="4" t="inlineStr"/>
-      <c r="L283" s="4" t="inlineStr"/>
-      <c r="M283" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K283" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L283" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M283" s="6" t="n">
+        <v>25811.10218</v>
+      </c>
       <c r="N283" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RGDPTEVEA629NUPN</t>
@@ -21580,20 +21928,26 @@
       </c>
       <c r="H286" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I286" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I286" s="4" t="inlineStr"/>
       <c r="J286" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K286" s="4" t="inlineStr"/>
-      <c r="L286" s="4" t="inlineStr"/>
-      <c r="M286" s="4" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="K286" s="4" t="inlineStr">
+        <is>
+          <t>1950-01-01</t>
+        </is>
+      </c>
+      <c r="L286" s="4" t="inlineStr">
+        <is>
+          <t>2010-01-01</t>
+        </is>
+      </c>
+      <c r="M286" s="6" t="n">
+        <v>19511.40489</v>
+      </c>
       <c r="N286" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/RGDPWOVEA627NUPN</t>
@@ -21957,20 +22311,26 @@
       </c>
       <c r="H291" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I291" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I291" s="4" t="inlineStr"/>
       <c r="J291" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K291" s="4" t="inlineStr"/>
-      <c r="L291" s="4" t="inlineStr"/>
-      <c r="M291" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K291" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L291" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M291" s="5" t="n">
+        <v>15077425</v>
+      </c>
       <c r="N291" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SCVENA052SCEN</t>
@@ -22030,20 +22390,26 @@
       </c>
       <c r="H292" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I292" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I292" s="4" t="inlineStr"/>
       <c r="J292" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K292" s="4" t="inlineStr"/>
-      <c r="L292" s="4" t="inlineStr"/>
-      <c r="M292" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K292" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L292" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M292" s="5" t="n">
+        <v>23</v>
+      </c>
       <c r="N292" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SCVENA475SCEN</t>
@@ -22176,20 +22542,26 @@
       </c>
       <c r="H294" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I294" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I294" s="4" t="inlineStr"/>
       <c r="J294" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K294" s="4" t="inlineStr"/>
-      <c r="L294" s="4" t="inlineStr"/>
-      <c r="M294" s="4" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="K294" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L294" s="4" t="inlineStr">
+        <is>
+          <t>2016-01-01</t>
+        </is>
+      </c>
+      <c r="M294" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="N294" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SDVENA475SCEN</t>
@@ -22401,20 +22773,26 @@
       </c>
       <c r="H297" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I297" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I297" s="4" t="inlineStr"/>
       <c r="J297" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K297" s="4" t="inlineStr"/>
-      <c r="L297" s="4" t="inlineStr"/>
-      <c r="M297" s="4" t="n"/>
+        <v>33</v>
+      </c>
+      <c r="K297" s="4" t="inlineStr">
+        <is>
+          <t>1971-01-01</t>
+        </is>
+      </c>
+      <c r="L297" s="4" t="inlineStr">
+        <is>
+          <t>2017-01-01</t>
+        </is>
+      </c>
+      <c r="M297" s="6" t="n">
+        <v>1.0806200504303</v>
+      </c>
       <c r="N297" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SEENRSECOFMZSVEN</t>
@@ -22474,20 +22852,26 @@
       </c>
       <c r="H298" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I298" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I298" s="4" t="inlineStr"/>
       <c r="J298" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K298" s="4" t="inlineStr"/>
-      <c r="L298" s="4" t="inlineStr"/>
-      <c r="M298" s="4" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="K298" s="4" t="inlineStr">
+        <is>
+          <t>1986-01-01</t>
+        </is>
+      </c>
+      <c r="L298" s="4" t="inlineStr">
+        <is>
+          <t>2008-01-01</t>
+        </is>
+      </c>
+      <c r="M298" s="6" t="n">
+        <v>1.40991997718811</v>
+      </c>
       <c r="N298" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SEENRTERTFMZSVEN</t>
@@ -22942,20 +23326,26 @@
       </c>
       <c r="H304" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I304" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I304" s="4" t="inlineStr"/>
       <c r="J304" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K304" s="4" t="inlineStr"/>
-      <c r="L304" s="4" t="inlineStr"/>
-      <c r="M304" s="4" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="K304" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L304" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M304" s="5" t="n">
+        <v>1404448</v>
+      </c>
       <c r="N304" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SMPOPTOTLVEN</t>
@@ -23410,20 +23800,26 @@
       </c>
       <c r="H310" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I310" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I310" s="4" t="inlineStr"/>
       <c r="J310" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K310" s="4" t="inlineStr"/>
-      <c r="L310" s="4" t="inlineStr"/>
-      <c r="M310" s="4" t="n"/>
+        <v>66</v>
+      </c>
+      <c r="K310" s="4" t="inlineStr">
+        <is>
+          <t>1960-01-01</t>
+        </is>
+      </c>
+      <c r="L310" s="4" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M310" s="6" t="n">
+        <v>24.9159954154898</v>
+      </c>
       <c r="N310" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SPPOP0014TOZSVEN</t>
@@ -23939,20 +24335,26 @@
       </c>
       <c r="H317" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I317" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I317" s="4" t="inlineStr"/>
       <c r="J317" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K317" s="4" t="inlineStr"/>
-      <c r="L317" s="4" t="inlineStr"/>
-      <c r="M317" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K317" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L317" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M317" s="5" t="n">
+        <v>297118823</v>
+      </c>
       <c r="N317" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/TXVENA052SCEN</t>
@@ -24012,20 +24414,26 @@
       </c>
       <c r="H318" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I318" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I318" s="4" t="inlineStr"/>
       <c r="J318" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K318" s="4" t="inlineStr"/>
-      <c r="L318" s="4" t="inlineStr"/>
-      <c r="M318" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K318" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L318" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M318" s="5" t="n">
+        <v>169</v>
+      </c>
       <c r="N318" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/TXVENA475SCEN</t>
@@ -25265,20 +25673,26 @@
       </c>
       <c r="H335" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I335" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I335" s="4" t="inlineStr"/>
       <c r="J335" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K335" s="4" t="inlineStr"/>
-      <c r="L335" s="4" t="inlineStr"/>
-      <c r="M335" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K335" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L335" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M335" s="5" t="n">
+        <v>6</v>
+      </c>
       <c r="N335" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/UTVENA475SCEN</t>
@@ -25411,20 +25825,26 @@
       </c>
       <c r="H337" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I337" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I337" s="4" t="inlineStr"/>
       <c r="J337" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K337" s="4" t="inlineStr"/>
-      <c r="L337" s="4" t="inlineStr"/>
-      <c r="M337" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K337" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L337" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M337" s="5" t="n">
+        <v>19</v>
+      </c>
       <c r="N337" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VAVENA475SCEN</t>
@@ -25630,20 +26050,26 @@
       </c>
       <c r="H340" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I340" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I340" s="4" t="inlineStr"/>
       <c r="J340" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K340" s="4" t="inlineStr"/>
-      <c r="L340" s="4" t="inlineStr"/>
-      <c r="M340" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K340" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L340" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M340" s="5" t="n">
+        <v>10429</v>
+      </c>
       <c r="N340" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCACNUM</t>
@@ -25849,20 +26275,26 @@
       </c>
       <c r="H343" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I343" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I343" s="4" t="inlineStr"/>
       <c r="J343" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K343" s="4" t="inlineStr"/>
-      <c r="L343" s="4" t="inlineStr"/>
-      <c r="M343" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K343" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L343" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M343" s="5" t="n">
+        <v>31695711</v>
+      </c>
       <c r="N343" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCAODCNUM</t>
@@ -25995,20 +26427,26 @@
       </c>
       <c r="H345" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I345" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I345" s="4" t="inlineStr"/>
       <c r="J345" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K345" s="4" t="inlineStr"/>
-      <c r="L345" s="4" t="inlineStr"/>
-      <c r="M345" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K345" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L345" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M345" s="5" t="n">
+        <v>270382</v>
+      </c>
       <c r="N345" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCAODMFNUM</t>
@@ -26585,20 +27023,26 @@
       </c>
       <c r="H353" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I353" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I353" s="4" t="inlineStr"/>
       <c r="J353" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K353" s="4" t="inlineStr"/>
-      <c r="L353" s="4" t="inlineStr"/>
-      <c r="M353" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K353" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L353" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M353" s="5" t="n">
+        <v>32</v>
+      </c>
       <c r="N353" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCBODDNUM</t>
@@ -26658,20 +27102,26 @@
       </c>
       <c r="H354" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I354" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I354" s="4" t="inlineStr"/>
       <c r="J354" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K354" s="4" t="inlineStr"/>
-      <c r="L354" s="4" t="inlineStr"/>
-      <c r="M354" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K354" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L354" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M354" s="6" t="n">
+        <v>0.130378096</v>
+      </c>
       <c r="N354" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCBODMFKNUM</t>
@@ -26877,20 +27327,26 @@
       </c>
       <c r="H357" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I357" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I357" s="4" t="inlineStr"/>
       <c r="J357" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K357" s="4" t="inlineStr"/>
-      <c r="L357" s="4" t="inlineStr"/>
-      <c r="M357" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K357" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L357" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M357" s="6" t="n">
+        <v>1889.1919863706</v>
+      </c>
       <c r="N357" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCDODCANUM</t>
@@ -27023,20 +27479,26 @@
       </c>
       <c r="H359" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I359" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I359" s="4" t="inlineStr"/>
       <c r="J359" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K359" s="4" t="inlineStr"/>
-      <c r="L359" s="4" t="inlineStr"/>
-      <c r="M359" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K359" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L359" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M359" s="6" t="n">
+        <v>24601704.6666667</v>
+      </c>
       <c r="N359" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCDODCHPENUM</t>
@@ -27096,20 +27558,26 @@
       </c>
       <c r="H360" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I360" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I360" s="4" t="inlineStr"/>
       <c r="J360" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K360" s="4" t="inlineStr"/>
-      <c r="L360" s="4" t="inlineStr"/>
-      <c r="M360" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K360" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L360" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M360" s="5" t="n">
+        <v>41472676</v>
+      </c>
       <c r="N360" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCDODCPENUM</t>
@@ -27169,20 +27637,26 @@
       </c>
       <c r="H361" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I361" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I361" s="4" t="inlineStr"/>
       <c r="J361" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K361" s="4" t="inlineStr"/>
-      <c r="L361" s="4" t="inlineStr"/>
-      <c r="M361" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K361" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L361" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M361" s="6" t="n">
+        <v>481500.416666667</v>
+      </c>
       <c r="N361" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCDODCSPENUM</t>
@@ -27242,20 +27716,26 @@
       </c>
       <c r="H362" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I362" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I362" s="4" t="inlineStr"/>
       <c r="J362" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K362" s="4" t="inlineStr"/>
-      <c r="L362" s="4" t="inlineStr"/>
-      <c r="M362" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K362" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L362" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M362" s="6" t="n">
+        <v>66.83665774000001</v>
+      </c>
       <c r="N362" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCDODCSPNUM</t>
@@ -27540,20 +28020,26 @@
       </c>
       <c r="H366" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I366" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I366" s="4" t="inlineStr"/>
       <c r="J366" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K366" s="4" t="inlineStr"/>
-      <c r="L366" s="4" t="inlineStr"/>
-      <c r="M366" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K366" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L366" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M366" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="N366" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCIODDNUM</t>
@@ -27759,20 +28245,26 @@
       </c>
       <c r="H369" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I369" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I369" s="4" t="inlineStr"/>
       <c r="J369" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K369" s="4" t="inlineStr"/>
-      <c r="L369" s="4" t="inlineStr"/>
-      <c r="M369" s="4" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="K369" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L369" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M369" s="6" t="n">
+        <v>68.50582168130001</v>
+      </c>
       <c r="N369" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCLODCGGDPPT</t>
@@ -27978,20 +28470,26 @@
       </c>
       <c r="H372" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I372" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I372" s="4" t="inlineStr"/>
       <c r="J372" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K372" s="4" t="inlineStr"/>
-      <c r="L372" s="4" t="inlineStr"/>
-      <c r="M372" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K372" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L372" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M372" s="6" t="n">
+        <v>21.4396202031903</v>
+      </c>
       <c r="N372" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCLODCSGGDPPT</t>
@@ -28270,20 +28768,26 @@
       </c>
       <c r="H376" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I376" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I376" s="4" t="inlineStr"/>
       <c r="J376" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K376" s="4" t="inlineStr"/>
-      <c r="L376" s="4" t="inlineStr"/>
-      <c r="M376" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K376" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L376" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M376" s="6" t="n">
+        <v>37322701822.99</v>
+      </c>
       <c r="N376" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCLODMFXDC</t>
@@ -28562,20 +29066,26 @@
       </c>
       <c r="H380" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I380" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I380" s="4" t="inlineStr"/>
       <c r="J380" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K380" s="4" t="inlineStr"/>
-      <c r="L380" s="4" t="inlineStr"/>
-      <c r="M380" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K380" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L380" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M380" s="6" t="n">
+        <v>1078.0378178439</v>
+      </c>
       <c r="N380" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCNODCANUM</t>
@@ -28787,20 +29297,26 @@
       </c>
       <c r="H383" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I383" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I383" s="4" t="inlineStr"/>
       <c r="J383" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K383" s="4" t="inlineStr"/>
-      <c r="L383" s="4" t="inlineStr"/>
-      <c r="M383" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K383" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L383" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M383" s="5" t="n">
+        <v>42341</v>
+      </c>
       <c r="N383" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCNODMFNUM</t>
@@ -28933,20 +29449,26 @@
       </c>
       <c r="H385" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I385" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I385" s="4" t="inlineStr"/>
       <c r="J385" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K385" s="4" t="inlineStr"/>
-      <c r="L385" s="4" t="inlineStr"/>
-      <c r="M385" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K385" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L385" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M385" s="6" t="n">
+        <v>336.987464420657</v>
+      </c>
       <c r="N385" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCRODCHANUM</t>
@@ -29006,20 +29528,26 @@
       </c>
       <c r="H386" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I386" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I386" s="4" t="inlineStr"/>
       <c r="J386" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K386" s="4" t="inlineStr"/>
-      <c r="L386" s="4" t="inlineStr"/>
-      <c r="M386" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K386" s="4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="L386" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M386" s="6" t="n">
+        <v>7404689.58333333</v>
+      </c>
       <c r="N386" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCRODCHPENUM</t>
@@ -29298,20 +29826,26 @@
       </c>
       <c r="H390" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I390" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I390" s="4" t="inlineStr"/>
       <c r="J390" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K390" s="4" t="inlineStr"/>
-      <c r="L390" s="4" t="inlineStr"/>
-      <c r="M390" s="4" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="K390" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L390" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M390" s="6" t="n">
+        <v>37.8908354029</v>
+      </c>
       <c r="N390" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCSODCGGDPPT</t>
@@ -29523,20 +30057,26 @@
       </c>
       <c r="H393" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I393" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I393" s="4" t="inlineStr"/>
       <c r="J393" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K393" s="4" t="inlineStr"/>
-      <c r="L393" s="4" t="inlineStr"/>
-      <c r="M393" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K393" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L393" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M393" s="6" t="n">
+        <v>2437538671645.28</v>
+      </c>
       <c r="N393" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCSODCXDC</t>
@@ -29742,20 +30282,26 @@
       </c>
       <c r="H396" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I396" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I396" s="4" t="inlineStr"/>
       <c r="J396" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K396" s="4" t="inlineStr"/>
-      <c r="L396" s="4" t="inlineStr"/>
-      <c r="M396" s="4" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="K396" s="4" t="inlineStr">
+        <is>
+          <t>2008-01-01</t>
+        </is>
+      </c>
+      <c r="L396" s="4" t="inlineStr">
+        <is>
+          <t>2014-01-01</t>
+        </is>
+      </c>
+      <c r="M396" s="5" t="n">
+        <v>10753000000</v>
+      </c>
       <c r="N396" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCSODMFSXDC</t>
@@ -29815,20 +30361,26 @@
       </c>
       <c r="H397" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I397" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I397" s="4" t="inlineStr"/>
       <c r="J397" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K397" s="4" t="inlineStr"/>
-      <c r="L397" s="4" t="inlineStr"/>
-      <c r="M397" s="4" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="K397" s="4" t="inlineStr">
+        <is>
+          <t>2005-01-01</t>
+        </is>
+      </c>
+      <c r="L397" s="4" t="inlineStr">
+        <is>
+          <t>2015-01-01</t>
+        </is>
+      </c>
+      <c r="M397" s="6" t="n">
+        <v>27106310381.76</v>
+      </c>
       <c r="N397" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCSODMFXDC</t>
@@ -29888,20 +30440,26 @@
       </c>
       <c r="H398" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I398" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I398" s="4" t="inlineStr"/>
       <c r="J398" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K398" s="4" t="inlineStr"/>
-      <c r="L398" s="4" t="inlineStr"/>
-      <c r="M398" s="4" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="K398" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L398" s="4" t="inlineStr">
+        <is>
+          <t>2016-01-01</t>
+        </is>
+      </c>
+      <c r="M398" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="N398" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VIVENA475SCEN</t>
@@ -30180,20 +30738,26 @@
       </c>
       <c r="H402" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I402" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I402" s="4" t="inlineStr"/>
       <c r="J402" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K402" s="4" t="inlineStr"/>
-      <c r="L402" s="4" t="inlineStr"/>
-      <c r="M402" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K402" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L402" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M402" s="5" t="n">
+        <v>11</v>
+      </c>
       <c r="N402" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/WAVENA475SCEN</t>
@@ -30253,20 +30817,26 @@
       </c>
       <c r="H403" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I403" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I403" s="4" t="inlineStr"/>
       <c r="J403" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K403" s="4" t="inlineStr"/>
-      <c r="L403" s="4" t="inlineStr"/>
-      <c r="M403" s="4" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="K403" s="4" t="inlineStr">
+        <is>
+          <t>1992-01-01</t>
+        </is>
+      </c>
+      <c r="L403" s="4" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="M403" s="5" t="n">
+        <v>2392941</v>
+      </c>
       <c r="N403" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/WIVENA052SCEN</t>
@@ -30624,20 +31194,26 @@
       </c>
       <c r="H408" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I408" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I408" s="4" t="inlineStr"/>
       <c r="J408" s="5" t="n">
+        <v>122</v>
+      </c>
+      <c r="K408" s="4" t="inlineStr">
+        <is>
+          <t>1996-01-01</t>
+        </is>
+      </c>
+      <c r="L408" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M408" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K408" s="4" t="inlineStr"/>
-      <c r="L408" s="4" t="inlineStr"/>
-      <c r="M408" s="4" t="n"/>
       <c r="N408" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/WUPIVEN</t>
@@ -31116,7 +31692,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
@@ -31173,7 +31749,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>117</v>
+        <v>213</v>
       </c>
     </row>
     <row r="15">
@@ -31183,7 +31759,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>16391</v>
+        <v>20131</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/fred/catalog/catalogo_dataset_web_ove_fred.xlsx
+++ b/assets/data/fred/catalog/catalogo_dataset_web_ove_fred.xlsx
@@ -4232,26 +4232,20 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I54" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J54" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="K54" s="4" t="inlineStr">
-        <is>
-          <t>1990-01-01</t>
-        </is>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>2019-01-01</t>
-        </is>
-      </c>
-      <c r="M54" s="6" t="n">
-        <v>0.0031524</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K54" s="4" t="inlineStr"/>
+      <c r="L54" s="4" t="inlineStr"/>
+      <c r="M54" s="4" t="n"/>
       <c r="N54" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDI10VEA156NWDB</t>
@@ -5101,26 +5095,20 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I65" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J65" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="K65" s="4" t="inlineStr">
-        <is>
-          <t>1999-01-01</t>
-        </is>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t>2016-01-01</t>
-        </is>
-      </c>
-      <c r="M65" s="6" t="n">
-        <v>0.0009455000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K65" s="4" t="inlineStr"/>
+      <c r="L65" s="4" t="inlineStr"/>
+      <c r="M65" s="4" t="n"/>
       <c r="N65" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDDM09VEA156NWDB</t>
@@ -6390,26 +6378,20 @@
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I82" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J82" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K82" s="4" t="inlineStr">
-        <is>
-          <t>2000-01-01</t>
-        </is>
-      </c>
-      <c r="L82" s="4" t="inlineStr">
-        <is>
-          <t>2021-01-01</t>
-        </is>
-      </c>
-      <c r="M82" s="6" t="n">
-        <v>92.47150000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K82" s="4" t="inlineStr"/>
+      <c r="L82" s="4" t="inlineStr"/>
+      <c r="M82" s="4" t="n"/>
       <c r="N82" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDOI06VEA156NWDB</t>
@@ -7624,26 +7606,20 @@
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I98" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J98" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="K98" s="4" t="inlineStr">
-        <is>
-          <t>1998-01-01</t>
-        </is>
-      </c>
-      <c r="L98" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M98" s="6" t="n">
-        <v>604.0700099999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K98" s="4" t="inlineStr"/>
+      <c r="L98" s="4" t="inlineStr"/>
+      <c r="M98" s="4" t="n"/>
       <c r="N98" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/DDSI07VEA156NWDB</t>
@@ -7929,7 +7905,7 @@
       </c>
       <c r="I102" s="4" t="inlineStr"/>
       <c r="J102" s="5" t="n">
-        <v>6673</v>
+        <v>6678</v>
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
@@ -7938,11 +7914,11 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="M102" s="6" t="n">
-        <v>778.0023</v>
+        <v>789.6875</v>
       </c>
       <c r="N102" s="4" t="inlineStr">
         <is>
@@ -10192,26 +10168,20 @@
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I132" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I132" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J132" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K132" s="4" t="inlineStr">
-        <is>
-          <t>2009-01-01</t>
-        </is>
-      </c>
-      <c r="L132" s="4" t="inlineStr">
-        <is>
-          <t>2009-01-01</t>
-        </is>
-      </c>
-      <c r="M132" s="5" t="n">
-        <v>72907</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K132" s="4" t="inlineStr"/>
+      <c r="L132" s="4" t="inlineStr"/>
+      <c r="M132" s="4" t="n"/>
       <c r="N132" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/HIVENA052SCEN</t>
@@ -10709,26 +10679,20 @@
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I139" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I139" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J139" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="K139" s="4" t="inlineStr">
-        <is>
-          <t>1972-10-01</t>
-        </is>
-      </c>
-      <c r="L139" s="4" t="inlineStr">
-        <is>
-          <t>2011-10-01</t>
-        </is>
-      </c>
-      <c r="M139" s="6" t="n">
-        <v>7.7885</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K139" s="4" t="inlineStr"/>
+      <c r="L139" s="4" t="inlineStr"/>
+      <c r="M139" s="4" t="n"/>
       <c r="N139" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IBANRIAIVE</t>
@@ -13105,26 +13069,20 @@
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I171" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I171" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J171" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="K171" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L171" s="4" t="inlineStr">
-        <is>
-          <t>2019-01-01</t>
-        </is>
-      </c>
-      <c r="M171" s="5" t="n">
-        <v>13776</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K171" s="4" t="inlineStr"/>
+      <c r="L171" s="4" t="inlineStr"/>
+      <c r="M171" s="4" t="n"/>
       <c r="N171" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IDVENA052SCEN</t>
@@ -15154,26 +15112,20 @@
       </c>
       <c r="H198" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I198" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I198" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J198" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K198" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L198" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M198" s="5" t="n">
-        <v>18</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K198" s="4" t="inlineStr"/>
+      <c r="L198" s="4" t="inlineStr"/>
+      <c r="M198" s="4" t="n"/>
       <c r="N198" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MAVENA475SCEN</t>
@@ -15598,26 +15550,20 @@
       </c>
       <c r="H204" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I204" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I204" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J204" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K204" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L204" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M204" s="5" t="n">
-        <v>30</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K204" s="4" t="inlineStr"/>
+      <c r="L204" s="4" t="inlineStr"/>
+      <c r="M204" s="4" t="n"/>
       <c r="N204" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MIVENA475SCEN</t>
@@ -15981,26 +15927,20 @@
       </c>
       <c r="H209" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I209" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I209" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J209" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="K209" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L209" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M209" s="5" t="n">
-        <v>758051</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K209" s="4" t="inlineStr"/>
+      <c r="L209" s="4" t="inlineStr"/>
+      <c r="M209" s="4" t="n"/>
       <c r="N209" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MOVENA052SCEN</t>
@@ -16060,26 +16000,20 @@
       </c>
       <c r="H210" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I210" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I210" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J210" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K210" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L210" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M210" s="5" t="n">
-        <v>14</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K210" s="4" t="inlineStr"/>
+      <c r="L210" s="4" t="inlineStr"/>
+      <c r="M210" s="4" t="n"/>
       <c r="N210" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MOVENA475SCEN</t>
@@ -16212,26 +16146,20 @@
       </c>
       <c r="H212" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I212" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I212" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J212" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K212" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L212" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M212" s="5" t="n">
-        <v>9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K212" s="4" t="inlineStr"/>
+      <c r="L212" s="4" t="inlineStr"/>
+      <c r="M212" s="4" t="n"/>
       <c r="N212" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MSVENA475SCEN</t>
@@ -18401,26 +18329,20 @@
       </c>
       <c r="H241" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I241" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I241" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J241" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="K241" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L241" s="4" t="inlineStr">
-        <is>
-          <t>2020-01-01</t>
-        </is>
-      </c>
-      <c r="M241" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="K241" s="4" t="inlineStr"/>
+      <c r="L241" s="4" t="inlineStr"/>
+      <c r="M241" s="4" t="n"/>
       <c r="N241" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PATENT4NVEDESIGN</t>
@@ -19647,26 +19569,20 @@
       </c>
       <c r="H257" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I257" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I257" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J257" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="K257" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L257" s="4" t="inlineStr">
-        <is>
-          <t>2023-01-01</t>
-        </is>
-      </c>
-      <c r="M257" s="6" t="n">
-        <v>31.6201782226563</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K257" s="4" t="inlineStr"/>
+      <c r="L257" s="4" t="inlineStr"/>
+      <c r="M257" s="4" t="n"/>
       <c r="N257" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLGDPOVEA670NRUG</t>
@@ -20907,26 +20823,20 @@
       </c>
       <c r="H273" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I273" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I273" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J273" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K273" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L273" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M273" s="5" t="n">
-        <v>10</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K273" s="4" t="inlineStr"/>
+      <c r="L273" s="4" t="inlineStr"/>
+      <c r="M273" s="4" t="n"/>
       <c r="N273" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PRVENA475SCEN</t>
@@ -22311,26 +22221,20 @@
       </c>
       <c r="H291" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I291" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I291" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J291" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K291" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L291" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M291" s="5" t="n">
-        <v>15077425</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K291" s="4" t="inlineStr"/>
+      <c r="L291" s="4" t="inlineStr"/>
+      <c r="M291" s="4" t="n"/>
       <c r="N291" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SCVENA052SCEN</t>
@@ -22390,26 +22294,20 @@
       </c>
       <c r="H292" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I292" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I292" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J292" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K292" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L292" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M292" s="5" t="n">
-        <v>23</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K292" s="4" t="inlineStr"/>
+      <c r="L292" s="4" t="inlineStr"/>
+      <c r="M292" s="4" t="n"/>
       <c r="N292" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SCVENA475SCEN</t>
@@ -23326,26 +23224,20 @@
       </c>
       <c r="H304" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I304" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I304" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J304" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="K304" s="4" t="inlineStr">
-        <is>
-          <t>1960-01-01</t>
-        </is>
-      </c>
-      <c r="L304" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M304" s="5" t="n">
-        <v>1404448</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K304" s="4" t="inlineStr"/>
+      <c r="L304" s="4" t="inlineStr"/>
+      <c r="M304" s="4" t="n"/>
       <c r="N304" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/SMPOPTOTLVEN</t>
@@ -24414,26 +24306,20 @@
       </c>
       <c r="H318" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I318" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I318" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J318" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K318" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L318" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M318" s="5" t="n">
-        <v>169</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K318" s="4" t="inlineStr"/>
+      <c r="L318" s="4" t="inlineStr"/>
+      <c r="M318" s="4" t="n"/>
       <c r="N318" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/TXVENA475SCEN</t>
@@ -27023,26 +26909,20 @@
       </c>
       <c r="H353" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I353" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I353" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J353" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K353" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L353" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M353" s="5" t="n">
-        <v>32</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K353" s="4" t="inlineStr"/>
+      <c r="L353" s="4" t="inlineStr"/>
+      <c r="M353" s="4" t="n"/>
       <c r="N353" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCBODDNUM</t>
@@ -27327,26 +27207,20 @@
       </c>
       <c r="H357" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I357" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I357" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J357" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K357" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L357" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M357" s="6" t="n">
-        <v>1889.1919863706</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K357" s="4" t="inlineStr"/>
+      <c r="L357" s="4" t="inlineStr"/>
+      <c r="M357" s="4" t="n"/>
       <c r="N357" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCDODCANUM</t>
@@ -27558,26 +27432,20 @@
       </c>
       <c r="H360" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I360" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I360" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J360" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K360" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L360" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M360" s="5" t="n">
-        <v>41472676</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K360" s="4" t="inlineStr"/>
+      <c r="L360" s="4" t="inlineStr"/>
+      <c r="M360" s="4" t="n"/>
       <c r="N360" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCDODCPENUM</t>
@@ -30361,26 +30229,20 @@
       </c>
       <c r="H397" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I397" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I397" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J397" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K397" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L397" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M397" s="6" t="n">
-        <v>27106310381.76</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K397" s="4" t="inlineStr"/>
+      <c r="L397" s="4" t="inlineStr"/>
+      <c r="M397" s="4" t="n"/>
       <c r="N397" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCSODMFXDC</t>
@@ -30738,26 +30600,20 @@
       </c>
       <c r="H402" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I402" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I402" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J402" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K402" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L402" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M402" s="5" t="n">
-        <v>11</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K402" s="4" t="inlineStr"/>
+      <c r="L402" s="4" t="inlineStr"/>
+      <c r="M402" s="4" t="n"/>
       <c r="N402" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/WAVENA475SCEN</t>
@@ -30817,26 +30673,20 @@
       </c>
       <c r="H403" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I403" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I403" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J403" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K403" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L403" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M403" s="5" t="n">
-        <v>2392941</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K403" s="4" t="inlineStr"/>
+      <c r="L403" s="4" t="inlineStr"/>
+      <c r="M403" s="4" t="n"/>
       <c r="N403" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/WIVENA052SCEN</t>
@@ -31692,7 +31542,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -31749,7 +31599,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>213</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15">
@@ -31759,7 +31609,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>20131</v>
+        <v>19566</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/fred/catalog/catalogo_dataset_web_ove_fred.xlsx
+++ b/assets/data/fred/catalog/catalogo_dataset_web_ove_fred.xlsx
@@ -2499,26 +2499,20 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J31" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>2023-01-01</t>
-        </is>
-      </c>
-      <c r="M31" s="6" t="n">
-        <v>-0.0894852876663208</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K31" s="4" t="inlineStr"/>
+      <c r="L31" s="4" t="inlineStr"/>
+      <c r="M31" s="4" t="n"/>
       <c r="N31" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/CSHRCPVEA156NRUG</t>
@@ -8063,7 +8057,7 @@
       </c>
       <c r="I104" s="4" t="inlineStr"/>
       <c r="J104" s="5" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
@@ -8072,11 +8066,11 @@
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M104" s="6" t="n">
-        <v>567.7612820000001</v>
+        <v>501.024042</v>
       </c>
       <c r="N104" s="4" t="inlineStr">
         <is>
@@ -13598,26 +13592,20 @@
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I178" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I178" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J178" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="K178" s="4" t="inlineStr">
-        <is>
-          <t>1990-10-01</t>
-        </is>
-      </c>
-      <c r="L178" s="4" t="inlineStr">
-        <is>
-          <t>1997-04-01</t>
-        </is>
-      </c>
-      <c r="M178" s="6" t="n">
-        <v>0.015</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K178" s="4" t="inlineStr"/>
+      <c r="L178" s="4" t="inlineStr"/>
+      <c r="M178" s="4" t="n"/>
       <c r="N178" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/IMMIRIAOVE</t>
@@ -13828,7 +13816,7 @@
       </c>
       <c r="I181" s="4" t="inlineStr"/>
       <c r="J181" s="5" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
@@ -13837,11 +13825,11 @@
       </c>
       <c r="L181" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M181" s="6" t="n">
-        <v>1815.327851</v>
+        <v>1661.795998</v>
       </c>
       <c r="N181" s="4" t="inlineStr">
         <is>
@@ -15033,26 +15021,20 @@
       </c>
       <c r="H197" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I197" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I197" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J197" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K197" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L197" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M197" s="5" t="n">
-        <v>1854340</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K197" s="4" t="inlineStr"/>
+      <c r="L197" s="4" t="inlineStr"/>
+      <c r="M197" s="4" t="n"/>
       <c r="N197" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MAVENA052SCEN</t>
@@ -16219,26 +16201,20 @@
       </c>
       <c r="H213" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I213" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I213" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J213" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="K213" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L213" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M213" s="5" t="n">
-        <v>206865</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K213" s="4" t="inlineStr"/>
+      <c r="L213" s="4" t="inlineStr"/>
+      <c r="M213" s="4" t="n"/>
       <c r="N213" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/MTVENA052SCEN</t>
@@ -16529,26 +16505,20 @@
       </c>
       <c r="H217" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I217" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I217" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J217" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K217" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L217" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M217" s="5" t="n">
-        <v>41</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K217" s="4" t="inlineStr"/>
+      <c r="L217" s="4" t="inlineStr"/>
+      <c r="M217" s="4" t="n"/>
       <c r="N217" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NCVENA475SCEN</t>
@@ -17350,26 +17320,20 @@
       </c>
       <c r="H228" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I228" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I228" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J228" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="K228" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L228" s="4" t="inlineStr">
-        <is>
-          <t>2021-01-01</t>
-        </is>
-      </c>
-      <c r="M228" s="5" t="n">
-        <v>144707</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K228" s="4" t="inlineStr"/>
+      <c r="L228" s="4" t="inlineStr"/>
+      <c r="M228" s="4" t="n"/>
       <c r="N228" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/NVVENA052SCEN</t>
@@ -17800,26 +17764,20 @@
       </c>
       <c r="H234" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I234" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I234" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J234" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K234" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L234" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M234" s="5" t="n">
-        <v>43</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K234" s="4" t="inlineStr"/>
+      <c r="L234" s="4" t="inlineStr"/>
+      <c r="M234" s="4" t="n"/>
       <c r="N234" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/OHVENA475SCEN</t>
@@ -18402,26 +18360,20 @@
       </c>
       <c r="H242" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I242" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I242" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J242" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="K242" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L242" s="4" t="inlineStr">
-        <is>
-          <t>2020-01-01</t>
-        </is>
-      </c>
-      <c r="M242" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="K242" s="4" t="inlineStr"/>
+      <c r="L242" s="4" t="inlineStr"/>
+      <c r="M242" s="4" t="n"/>
       <c r="N242" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PATENT4NVEPLANT</t>
@@ -19016,26 +18968,20 @@
       </c>
       <c r="H250" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I250" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I250" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J250" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="K250" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L250" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M250" s="6" t="n">
-        <v>10445.85073</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K250" s="4" t="inlineStr"/>
+      <c r="L250" s="4" t="inlineStr"/>
+      <c r="M250" s="4" t="n"/>
       <c r="N250" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PCDGDPVEA620NUPN</t>
@@ -19642,26 +19588,20 @@
       </c>
       <c r="H258" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I258" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I258" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J258" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="K258" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L258" s="4" t="inlineStr">
-        <is>
-          <t>2023-01-01</t>
-        </is>
-      </c>
-      <c r="M258" s="6" t="n">
-        <v>40.4344416781944</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K258" s="4" t="inlineStr"/>
+      <c r="L258" s="4" t="inlineStr"/>
+      <c r="M258" s="4" t="n"/>
       <c r="N258" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLICPPVEA670NRUG</t>
@@ -20037,26 +19977,20 @@
       </c>
       <c r="H263" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I263" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I263" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J263" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="K263" s="4" t="inlineStr">
-        <is>
-          <t>1950-01-01</t>
-        </is>
-      </c>
-      <c r="L263" s="4" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="M263" s="6" t="n">
-        <v>144.0149859</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K263" s="4" t="inlineStr"/>
+      <c r="L263" s="4" t="inlineStr"/>
+      <c r="M263" s="4" t="n"/>
       <c r="N263" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/PLOGINVEA623NUPN</t>
@@ -24227,26 +24161,20 @@
       </c>
       <c r="H317" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I317" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I317" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J317" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K317" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L317" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M317" s="5" t="n">
-        <v>297118823</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K317" s="4" t="inlineStr"/>
+      <c r="L317" s="4" t="inlineStr"/>
+      <c r="M317" s="4" t="n"/>
       <c r="N317" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/TXVENA052SCEN</t>
@@ -24671,20 +24599,26 @@
       </c>
       <c r="H323" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I323" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I323" s="4" t="inlineStr"/>
       <c r="J323" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K323" s="4" t="inlineStr"/>
-      <c r="L323" s="4" t="inlineStr"/>
-      <c r="M323" s="4" t="n"/>
+        <v>41</v>
+      </c>
+      <c r="K323" s="4" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="L323" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M323" s="5" t="n">
+        <v>2594</v>
+      </c>
       <c r="N323" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTCORPBONDPOS32719</t>
@@ -24817,20 +24751,26 @@
       </c>
       <c r="H325" s="4" t="inlineStr">
         <is>
-          <t>No descargada</t>
-        </is>
-      </c>
-      <c r="I325" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 403: Forbidden</t>
-        </is>
-      </c>
+          <t>Con datos</t>
+        </is>
+      </c>
+      <c r="I325" s="4" t="inlineStr"/>
       <c r="J325" s="5" t="n">
+        <v>387</v>
+      </c>
+      <c r="K325" s="4" t="inlineStr">
+        <is>
+          <t>1994-04-01</t>
+        </is>
+      </c>
+      <c r="L325" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M325" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K325" s="4" t="inlineStr"/>
-      <c r="L325" s="4" t="inlineStr"/>
-      <c r="M325" s="4" t="n"/>
       <c r="N325" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/USLTEQTYNET32719</t>
@@ -25711,26 +25651,20 @@
       </c>
       <c r="H337" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I337" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I337" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J337" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="K337" s="4" t="inlineStr">
-        <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="L337" s="4" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="M337" s="5" t="n">
-        <v>19</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K337" s="4" t="inlineStr"/>
+      <c r="L337" s="4" t="inlineStr"/>
+      <c r="M337" s="4" t="n"/>
       <c r="N337" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VAVENA475SCEN</t>
@@ -26313,26 +26247,20 @@
       </c>
       <c r="H345" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I345" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I345" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J345" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K345" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L345" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M345" s="5" t="n">
-        <v>270382</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K345" s="4" t="inlineStr"/>
+      <c r="L345" s="4" t="inlineStr"/>
+      <c r="M345" s="4" t="n"/>
       <c r="N345" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCAODMFNUM</t>
@@ -27505,26 +27433,20 @@
       </c>
       <c r="H361" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I361" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I361" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J361" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K361" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L361" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M361" s="6" t="n">
-        <v>481500.416666667</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K361" s="4" t="inlineStr"/>
+      <c r="L361" s="4" t="inlineStr"/>
+      <c r="M361" s="4" t="n"/>
       <c r="N361" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCDODCSPENUM</t>
@@ -27888,26 +27810,20 @@
       </c>
       <c r="H366" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I366" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I366" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J366" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K366" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L366" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M366" s="5" t="n">
-        <v>5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K366" s="4" t="inlineStr"/>
+      <c r="L366" s="4" t="inlineStr"/>
+      <c r="M366" s="4" t="n"/>
       <c r="N366" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCIODDNUM</t>
@@ -29165,26 +29081,20 @@
       </c>
       <c r="H383" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I383" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I383" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J383" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K383" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L383" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M383" s="5" t="n">
-        <v>42341</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K383" s="4" t="inlineStr"/>
+      <c r="L383" s="4" t="inlineStr"/>
+      <c r="M383" s="4" t="n"/>
       <c r="N383" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCNODMFNUM</t>
@@ -29317,26 +29227,20 @@
       </c>
       <c r="H385" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I385" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I385" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J385" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K385" s="4" t="inlineStr">
-        <is>
-          <t>2004-01-01</t>
-        </is>
-      </c>
-      <c r="L385" s="4" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="M385" s="6" t="n">
-        <v>336.987464420657</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K385" s="4" t="inlineStr"/>
+      <c r="L385" s="4" t="inlineStr"/>
+      <c r="M385" s="4" t="n"/>
       <c r="N385" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCRODCHANUM</t>
@@ -29925,26 +29829,20 @@
       </c>
       <c r="H393" s="4" t="inlineStr">
         <is>
-          <t>Con datos</t>
-        </is>
-      </c>
-      <c r="I393" s="4" t="inlineStr"/>
+          <t>No descargada</t>
+        </is>
+      </c>
+      <c r="I393" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 403: Forbidden</t>
+        </is>
+      </c>
       <c r="J393" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K393" s="4" t="inlineStr">
-        <is>
-          <t>2005-01-01</t>
-        </is>
-      </c>
-      <c r="L393" s="4" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="M393" s="6" t="n">
-        <v>2437538671645.28</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K393" s="4" t="inlineStr"/>
+      <c r="L393" s="4" t="inlineStr"/>
+      <c r="M393" s="4" t="n"/>
       <c r="N393" s="4" t="inlineStr">
         <is>
           <t>https://fred.stlouisfed.org/series/VENFCSODCXDC</t>
@@ -31542,7 +31440,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
@@ -31599,7 +31497,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>188</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15">
@@ -31609,7 +31507,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>19566</v>
+        <v>19477</v>
       </c>
     </row>
   </sheetData>
